--- a/database/event/4828/event_4828_evp_summary.xlsx
+++ b/database/event/4828/event_4828_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.9009</v>
+        <v>6.8954</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5760999999999999</v>
+        <v>0.5756</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3664</v>
+        <v>2.3032</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9009</v>
+        <v>6.8954</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4761</v>
+        <v>1.4706</v>
       </c>
       <c r="G2" t="n">
         <v>5.4248</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4761</v>
+        <v>1.4706</v>
       </c>
       <c r="I2" t="n">
         <v>1.483</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.691</v>
+        <v>6.6824</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5586</v>
+        <v>0.5578</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2817</v>
+        <v>2.2184</v>
       </c>
       <c r="E3" t="n">
-        <v>6.691</v>
+        <v>6.6824</v>
       </c>
       <c r="F3" t="n">
-        <v>2.292</v>
+        <v>2.2834</v>
       </c>
       <c r="G3" t="n">
         <v>4.399</v>
       </c>
       <c r="H3" t="n">
-        <v>2.292</v>
+        <v>2.2834</v>
       </c>
       <c r="I3" t="n">
         <v>2.3027</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.684</v>
+        <v>6.6751</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5572</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2788</v>
+        <v>2.2155</v>
       </c>
       <c r="E4" t="n">
-        <v>6.684</v>
+        <v>6.6751</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3925</v>
+        <v>2.3836</v>
       </c>
       <c r="G4" t="n">
         <v>4.2915</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3925</v>
+        <v>2.3836</v>
       </c>
       <c r="I4" t="n">
         <v>2.4036</v>
@@ -640,7 +640,7 @@
         <v>0.4704</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8548</v>
+        <v>1.8008</v>
       </c>
       <c r="E5" t="n">
         <v>5.6343</v>
@@ -686,7 +686,7 @@
         <v>0.4433</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7237</v>
+        <v>1.6716</v>
       </c>
       <c r="E6" t="n">
         <v>5.3099</v>
@@ -732,7 +732,7 @@
         <v>0.3447</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2468</v>
+        <v>1.2012</v>
       </c>
       <c r="E7" t="n">
         <v>4.1293</v>
@@ -778,7 +778,7 @@
         <v>0.3037</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0484</v>
+        <v>1.0055</v>
       </c>
       <c r="E8" t="n">
         <v>3.6382</v>
@@ -824,7 +824,7 @@
         <v>0.286</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9626</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="E9" t="n">
         <v>3.4258</v>
@@ -870,7 +870,7 @@
         <v>0.2484</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7806</v>
+        <v>0.7413999999999999</v>
       </c>
       <c r="E10" t="n">
         <v>2.9753</v>
@@ -916,7 +916,7 @@
         <v>0.189</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4931</v>
+        <v>0.4579</v>
       </c>
       <c r="E11" t="n">
         <v>2.2637</v>
@@ -962,7 +962,7 @@
         <v>0.1598</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3521</v>
+        <v>0.3189</v>
       </c>
       <c r="E12" t="n">
         <v>1.9146</v>
@@ -1008,7 +1008,7 @@
         <v>0.1455</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2829</v>
+        <v>0.2506</v>
       </c>
       <c r="E13" t="n">
         <v>1.7432</v>
@@ -1054,7 +1054,7 @@
         <v>0.1416</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2637</v>
+        <v>0.2317</v>
       </c>
       <c r="E14" t="n">
         <v>1.6958</v>
@@ -1100,7 +1100,7 @@
         <v>0.1401</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2567</v>
+        <v>0.2248</v>
       </c>
       <c r="E15" t="n">
         <v>1.6784</v>
@@ -1146,7 +1146,7 @@
         <v>0.1213</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1657</v>
+        <v>0.135</v>
       </c>
       <c r="E16" t="n">
         <v>1.4531</v>
@@ -1192,7 +1192,7 @@
         <v>0.1101</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1112</v>
+        <v>0.0813</v>
       </c>
       <c r="E17" t="n">
         <v>1.3183</v>
@@ -1238,7 +1238,7 @@
         <v>0.0936</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0314</v>
+        <v>0.0026</v>
       </c>
       <c r="E18" t="n">
         <v>1.1208</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0986</v>
+        <v>1.0952</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0917</v>
+        <v>0.0914</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0224</v>
+        <v>-0.0076</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0986</v>
+        <v>1.0952</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9188</v>
+        <v>0.9154</v>
       </c>
       <c r="G19" t="n">
         <v>0.1798</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9188</v>
+        <v>0.9154</v>
       </c>
       <c r="I19" t="n">
         <v>0.9231</v>
@@ -1330,7 +1330,7 @@
         <v>0.0725</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0979</v>
       </c>
       <c r="E20" t="n">
         <v>0.8685</v>
@@ -1376,7 +1376,7 @@
         <v>0.0704</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0808</v>
+        <v>-0.1081</v>
       </c>
       <c r="E21" t="n">
         <v>0.8429</v>
@@ -1422,7 +1422,7 @@
         <v>0.0205</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.322</v>
+        <v>-0.3459</v>
       </c>
       <c r="E22" t="n">
         <v>0.2459</v>
@@ -1468,7 +1468,7 @@
         <v>0.0124</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3613</v>
+        <v>-0.3846</v>
       </c>
       <c r="E23" t="n">
         <v>0.1488</v>
@@ -1514,7 +1514,7 @@
         <v>0.0122</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3622</v>
+        <v>-0.3855</v>
       </c>
       <c r="E24" t="n">
         <v>0.1465</v>
@@ -1560,7 +1560,7 @@
         <v>0.0075</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3853</v>
+        <v>-0.4083</v>
       </c>
       <c r="E25" t="n">
         <v>0.0893</v>
@@ -1606,7 +1606,7 @@
         <v>0.0002</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4205</v>
+        <v>-0.4431</v>
       </c>
       <c r="E26" t="n">
         <v>0.0021</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0011</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4268</v>
+        <v>-0.4492</v>
       </c>
       <c r="E27" t="n">
         <v>-0.0134</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0331</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5814</v>
+        <v>-0.6018</v>
       </c>
       <c r="E28" t="n">
         <v>-0.3962</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0514</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6701</v>
+        <v>-0.6892</v>
       </c>
       <c r="E29" t="n">
         <v>-0.6156</v>
@@ -1790,7 +1790,7 @@
         <v>-0.064</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7308</v>
+        <v>-0.7491</v>
       </c>
       <c r="E30" t="n">
         <v>-0.7661</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0669</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.745</v>
+        <v>-0.7631</v>
       </c>
       <c r="E31" t="n">
         <v>-0.8012</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0785</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8015</v>
+        <v>-0.8188</v>
       </c>
       <c r="E32" t="n">
         <v>-0.9409</v>
@@ -1928,7 +1928,7 @@
         <v>-0.09710000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8914</v>
+        <v>-0.9075</v>
       </c>
       <c r="E33" t="n">
         <v>-1.1636</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1326</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0632</v>
+        <v>-1.0768</v>
       </c>
       <c r="E34" t="n">
         <v>-1.5887</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1409</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1033</v>
+        <v>-1.1164</v>
       </c>
       <c r="E35" t="n">
         <v>-1.6881</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1413</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1052</v>
+        <v>-1.1183</v>
       </c>
       <c r="E36" t="n">
         <v>-1.6927</v>
@@ -2112,7 +2112,7 @@
         <v>-0.145</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1229</v>
+        <v>-1.1358</v>
       </c>
       <c r="E37" t="n">
         <v>-1.7366</v>
@@ -2158,7 +2158,7 @@
         <v>-0.148</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1378</v>
+        <v>-1.1504</v>
       </c>
       <c r="E38" t="n">
         <v>-1.7734</v>
@@ -2204,7 +2204,7 @@
         <v>-0.1696</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.242</v>
+        <v>-1.2533</v>
       </c>
       <c r="E39" t="n">
         <v>-2.0315</v>
@@ -2250,7 +2250,7 @@
         <v>-0.1706</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2467</v>
+        <v>-1.2579</v>
       </c>
       <c r="E40" t="n">
         <v>-2.0431</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.9712</v>
+        <v>-4.9602</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.415</v>
+        <v>-0.4141</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.4296</v>
+        <v>-2.4201</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.9712</v>
+        <v>-4.9602</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.9399</v>
+        <v>-2.9289</v>
       </c>
       <c r="G41" t="n">
         <v>-2.0313</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.9399</v>
+        <v>-2.9289</v>
       </c>
       <c r="I41" t="n">
         <v>-2.9536</v>

--- a/database/event/4828/event_4828_evp_summary.xlsx
+++ b/database/event/4828/event_4828_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.8954</v>
+        <v>6.679</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5756</v>
+        <v>0.5576</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3032</v>
+        <v>2.3772</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8954</v>
+        <v>6.679</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4706</v>
+        <v>2.0509</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4248</v>
+        <v>4.6281</v>
       </c>
       <c r="H2" t="n">
-        <v>1.4706</v>
+        <v>2.0509</v>
       </c>
       <c r="I2" t="n">
-        <v>1.483</v>
+        <v>2.1352</v>
       </c>
       <c r="J2" t="n">
-        <v>5.4248</v>
+        <v>4.6281</v>
       </c>
       <c r="K2" t="n">
         <v>152</v>
@@ -529,7 +529,7 @@
         <v>214</v>
       </c>
       <c r="M2" t="n">
-        <v>6.9078</v>
+        <v>6.7633</v>
       </c>
       <c r="N2" t="n">
         <v>366</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.6824</v>
+        <v>6.4517</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5578</v>
+        <v>0.5386</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2184</v>
+        <v>2.2746</v>
       </c>
       <c r="E3" t="n">
-        <v>6.6824</v>
+        <v>6.4517</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2834</v>
+        <v>2.8341</v>
       </c>
       <c r="G3" t="n">
-        <v>4.399</v>
+        <v>3.6176</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2834</v>
+        <v>2.8634</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3027</v>
+        <v>2.9812</v>
       </c>
       <c r="J3" t="n">
-        <v>4.399</v>
+        <v>3.6176</v>
       </c>
       <c r="K3" t="n">
         <v>152</v>
@@ -575,7 +575,7 @@
         <v>214</v>
       </c>
       <c r="M3" t="n">
-        <v>6.701700000000001</v>
+        <v>6.5988</v>
       </c>
       <c r="N3" t="n">
         <v>366</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.6751</v>
+        <v>6.0316</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5572</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2155</v>
+        <v>2.085</v>
       </c>
       <c r="E4" t="n">
-        <v>6.6751</v>
+        <v>6.0316</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3836</v>
+        <v>2.3165</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2915</v>
+        <v>3.7151</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3836</v>
+        <v>2.3165</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4036</v>
+        <v>2.4118</v>
       </c>
       <c r="J4" t="n">
-        <v>4.2915</v>
+        <v>3.7151</v>
       </c>
       <c r="K4" t="n">
         <v>152</v>
@@ -621,7 +621,7 @@
         <v>214</v>
       </c>
       <c r="M4" t="n">
-        <v>6.6951</v>
+        <v>6.1269</v>
       </c>
       <c r="N4" t="n">
         <v>366</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6343</v>
+        <v>4.8326</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4704</v>
+        <v>0.4034</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8008</v>
+        <v>1.5437</v>
       </c>
       <c r="E5" t="n">
-        <v>5.6343</v>
+        <v>4.8326</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1576</v>
+        <v>1.2304</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4767</v>
+        <v>3.6022</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1576</v>
+        <v>1.2304</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1576</v>
+        <v>1.2304</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4767</v>
+        <v>3.6022</v>
       </c>
       <c r="K5" t="n">
         <v>107</v>
@@ -667,7 +667,7 @@
         <v>185</v>
       </c>
       <c r="M5" t="n">
-        <v>5.6343</v>
+        <v>4.832599999999999</v>
       </c>
       <c r="N5" t="n">
         <v>292</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.3099</v>
+        <v>4.7348</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4433</v>
+        <v>0.3953</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6716</v>
+        <v>1.4995</v>
       </c>
       <c r="E6" t="n">
-        <v>5.3099</v>
+        <v>4.7348</v>
       </c>
       <c r="F6" t="n">
-        <v>4.2536</v>
+        <v>3.7158</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0563</v>
+        <v>1.019</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5526</v>
+        <v>7.6059</v>
       </c>
       <c r="I6" t="n">
-        <v>3.69</v>
+        <v>3.9547</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0563</v>
+        <v>1.019</v>
       </c>
       <c r="K6" t="n">
         <v>144</v>
@@ -713,7 +713,7 @@
         <v>59</v>
       </c>
       <c r="M6" t="n">
-        <v>4.7463</v>
+        <v>4.9737</v>
       </c>
       <c r="N6" t="n">
         <v>203</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1293</v>
+        <v>3.6615</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3447</v>
+        <v>0.3057</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2012</v>
+        <v>1.015</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1293</v>
+        <v>3.6615</v>
       </c>
       <c r="F7" t="n">
-        <v>4.0909</v>
+        <v>3.5631</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0384</v>
+        <v>0.0984</v>
       </c>
       <c r="H7" t="n">
-        <v>4.0909</v>
+        <v>7.0677</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3158</v>
+        <v>3.6749</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0384</v>
+        <v>0.0984</v>
       </c>
       <c r="K7" t="n">
         <v>151</v>
@@ -759,7 +759,7 @@
         <v>49</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3542</v>
+        <v>3.7733</v>
       </c>
       <c r="N7" t="n">
         <v>200</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6382</v>
+        <v>3.5711</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3037</v>
+        <v>0.2981</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0055</v>
+        <v>0.9742</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6382</v>
+        <v>3.5711</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0083</v>
+        <v>2.9173</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6299</v>
+        <v>0.6538</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0083</v>
+        <v>4.7925</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4383</v>
+        <v>2.4919</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6299</v>
+        <v>0.6538</v>
       </c>
       <c r="K8" t="n">
         <v>144</v>
@@ -805,7 +805,7 @@
         <v>59</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0682</v>
+        <v>3.1457</v>
       </c>
       <c r="N8" t="n">
         <v>203</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.4258</v>
+        <v>3.528</v>
       </c>
       <c r="C9" t="n">
-        <v>0.286</v>
+        <v>0.2945</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.9547</v>
       </c>
       <c r="E9" t="n">
-        <v>3.4258</v>
+        <v>3.528</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0667</v>
+        <v>1.4842</v>
       </c>
       <c r="G9" t="n">
-        <v>2.3591</v>
+        <v>2.0438</v>
       </c>
       <c r="H9" t="n">
-        <v>1.0667</v>
+        <v>1.4842</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0667</v>
+        <v>1.4842</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3591</v>
+        <v>2.0438</v>
       </c>
       <c r="K9" t="n">
         <v>107</v>
@@ -851,7 +851,7 @@
         <v>185</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4258</v>
+        <v>3.528</v>
       </c>
       <c r="N9" t="n">
         <v>292</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9753</v>
+        <v>3.0277</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2484</v>
+        <v>0.2528</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.7288</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9753</v>
+        <v>3.0277</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7075</v>
+        <v>1.8582</v>
       </c>
       <c r="G10" t="n">
-        <v>1.2678</v>
+        <v>1.1695</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7075</v>
+        <v>1.8582</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7075</v>
+        <v>1.8582</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2678</v>
+        <v>1.1695</v>
       </c>
       <c r="K10" t="n">
         <v>107</v>
@@ -897,7 +897,7 @@
         <v>185</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9753</v>
+        <v>3.0277</v>
       </c>
       <c r="N10" t="n">
         <v>292</v>
@@ -906,81 +906,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>jedqr</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2637</v>
+        <v>2.6778</v>
       </c>
       <c r="C11" t="n">
-        <v>0.189</v>
+        <v>0.2235</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4579</v>
+        <v>0.5709</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2637</v>
+        <v>2.6778</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1774</v>
+        <v>2.3821</v>
       </c>
       <c r="G11" t="n">
-        <v>1.0863</v>
+        <v>0.2957</v>
       </c>
       <c r="H11" t="n">
-        <v>1.1774</v>
+        <v>2.9066</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1774</v>
+        <v>1.5113</v>
       </c>
       <c r="J11" t="n">
-        <v>1.0863</v>
+        <v>0.2957</v>
       </c>
       <c r="K11" t="n">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L11" t="n">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2637</v>
+        <v>1.807</v>
       </c>
       <c r="N11" t="n">
-        <v>181</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9146</v>
+        <v>2.441</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1598</v>
+        <v>0.2038</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3189</v>
+        <v>0.464</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9146</v>
+        <v>2.441</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6325</v>
+        <v>2.4794</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2821</v>
+        <v>-0.0384</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6325</v>
+        <v>3.2495</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3232</v>
+        <v>1.6896</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2821</v>
+        <v>-0.0384</v>
       </c>
       <c r="K12" t="n">
         <v>151</v>
@@ -989,7 +989,7 @@
         <v>49</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6053</v>
+        <v>1.6512</v>
       </c>
       <c r="N12" t="n">
         <v>200</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7432</v>
+        <v>2.3824</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1455</v>
+        <v>0.1989</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2506</v>
+        <v>0.4375</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7432</v>
+        <v>2.3824</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3491</v>
+        <v>1.9716</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3941</v>
+        <v>0.4108</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3491</v>
+        <v>1.9716</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3491</v>
+        <v>1.9716</v>
       </c>
       <c r="J13" t="n">
-        <v>0.3941</v>
+        <v>0.4108</v>
       </c>
       <c r="K13" t="n">
         <v>118</v>
@@ -1035,7 +1035,7 @@
         <v>55</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7432</v>
+        <v>2.3824</v>
       </c>
       <c r="N13" t="n">
         <v>173</v>
@@ -1044,599 +1044,599 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>jedqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.6958</v>
+        <v>2.2039</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1416</v>
+        <v>0.184</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2317</v>
+        <v>0.3569</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6958</v>
+        <v>2.2039</v>
       </c>
       <c r="F14" t="n">
-        <v>1.6958</v>
+        <v>1.3823</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.8216</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6958</v>
+        <v>1.3823</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6958</v>
+        <v>1.3823</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.8216</v>
       </c>
       <c r="K14" t="n">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M14" t="n">
-        <v>1.6958</v>
+        <v>2.2039</v>
       </c>
       <c r="N14" t="n">
-        <v>133</v>
+        <v>181</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6784</v>
+        <v>1.9637</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1401</v>
+        <v>0.1639</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2248</v>
+        <v>0.2485</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6784</v>
+        <v>1.9637</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8685</v>
+        <v>1.9637</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1901</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8685</v>
+        <v>1.9637</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5145</v>
+        <v>1.9637</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1901</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="L15" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.3244</v>
+        <v>1.9637</v>
       </c>
       <c r="N15" t="n">
-        <v>200</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Vegi</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4531</v>
+        <v>1.8486</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1213</v>
+        <v>0.1543</v>
       </c>
       <c r="D16" t="n">
-        <v>0.135</v>
+        <v>0.1965</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4531</v>
+        <v>1.8486</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7077</v>
+        <v>2.2834</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7454</v>
+        <v>-0.4348</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7077</v>
+        <v>2.5591</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7077</v>
+        <v>1.3306</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7454</v>
+        <v>-0.4348</v>
       </c>
       <c r="K16" t="n">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="L16" t="n">
-        <v>185</v>
+        <v>59</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4531</v>
+        <v>0.8957999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>292</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3183</v>
+        <v>1.6351</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1101</v>
+        <v>0.1365</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0813</v>
+        <v>0.1002</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3183</v>
+        <v>1.6351</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3472</v>
+        <v>1.028</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0289</v>
+        <v>0.6071</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3472</v>
+        <v>1.028</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3472</v>
+        <v>1.0703</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0289</v>
+        <v>0.6071</v>
       </c>
       <c r="K17" t="n">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="L17" t="n">
-        <v>55</v>
+        <v>214</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3183</v>
+        <v>1.6774</v>
       </c>
       <c r="N17" t="n">
-        <v>173</v>
+        <v>366</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lekr0</t>
+          <t>Vegi</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1208</v>
+        <v>1.6197</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0936</v>
+        <v>0.1352</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0026</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1208</v>
+        <v>1.6197</v>
       </c>
       <c r="F18" t="n">
-        <v>1.285</v>
+        <v>0.9957</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1642</v>
+        <v>0.624</v>
       </c>
       <c r="H18" t="n">
-        <v>1.285</v>
+        <v>0.9957</v>
       </c>
       <c r="I18" t="n">
-        <v>1.285</v>
+        <v>0.9957</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1642</v>
+        <v>0.624</v>
       </c>
       <c r="K18" t="n">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="L18" t="n">
-        <v>55</v>
+        <v>185</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1208</v>
+        <v>1.6197</v>
       </c>
       <c r="N18" t="n">
-        <v>173</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.0952</v>
+        <v>1.5382</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0914</v>
+        <v>0.1284</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0076</v>
+        <v>0.0564</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0952</v>
+        <v>1.5382</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9154</v>
+        <v>1.4551</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1798</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9154</v>
+        <v>1.4551</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9231</v>
+        <v>1.4551</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1798</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="L19" t="n">
-        <v>214</v>
+        <v>55</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1029</v>
+        <v>1.5382</v>
       </c>
       <c r="N19" t="n">
-        <v>366</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mynio</t>
+          <t>Lekr0</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8685</v>
+        <v>1.4297</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0725</v>
+        <v>0.1194</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0979</v>
+        <v>0.0074</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8685</v>
+        <v>1.4297</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7187</v>
+        <v>1.3928</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1498</v>
+        <v>0.0369</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7187</v>
+        <v>1.3928</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7187</v>
+        <v>1.3928</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1498</v>
+        <v>0.0369</v>
       </c>
       <c r="K20" t="n">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="L20" t="n">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8685</v>
+        <v>1.4297</v>
       </c>
       <c r="N20" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>mynio</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8429</v>
+        <v>1.2763</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0704</v>
+        <v>0.1065</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1081</v>
+        <v>-0.0618</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8429</v>
+        <v>1.2763</v>
       </c>
       <c r="F21" t="n">
-        <v>1.5376</v>
+        <v>1.0653</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6947</v>
+        <v>0.211</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5376</v>
+        <v>1.0653</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2463</v>
+        <v>1.0653</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6947</v>
+        <v>0.211</v>
       </c>
       <c r="K21" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="L21" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5516</v>
+        <v>1.2763</v>
       </c>
       <c r="N21" t="n">
-        <v>203</v>
+        <v>181</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>conoR</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2459</v>
+        <v>0.9123</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0205</v>
+        <v>0.0762</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3459</v>
+        <v>-0.2262</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2459</v>
+        <v>0.9123</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2459</v>
+        <v>1.2849</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-0.3726</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2459</v>
+        <v>1.2849</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2459</v>
+        <v>0.6681</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>-0.3726</v>
       </c>
       <c r="K22" t="n">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2459</v>
+        <v>0.2955</v>
       </c>
       <c r="N22" t="n">
-        <v>106</v>
+        <v>203</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>morelz</t>
+          <t>conoR</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1488</v>
+        <v>0.6659</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0124</v>
+        <v>0.0556</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3846</v>
+        <v>-0.3374</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1488</v>
+        <v>0.6659</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1488</v>
+        <v>0.6659</v>
       </c>
       <c r="G23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.1488</v>
+        <v>0.6659</v>
       </c>
       <c r="I23" t="n">
-        <v>1.1488</v>
+        <v>0.6659</v>
       </c>
       <c r="J23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L23" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1488</v>
+        <v>0.6659</v>
       </c>
       <c r="N23" t="n">
-        <v>181</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DEV7L</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1465</v>
+        <v>0.6102</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0122</v>
+        <v>0.0509</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3855</v>
+        <v>-0.3625</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1465</v>
+        <v>0.6102</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1465</v>
+        <v>1.218</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.6078</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1465</v>
+        <v>1.218</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1465</v>
+        <v>1.218</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.6078</v>
       </c>
       <c r="K24" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1465</v>
+        <v>0.6102</v>
       </c>
       <c r="N24" t="n">
-        <v>106</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>morelz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0893</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0075</v>
+        <v>0.049</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4083</v>
+        <v>-0.3729</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0893</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7084</v>
+        <v>1.2786</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6191</v>
+        <v>-0.6914</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7084</v>
+        <v>1.2786</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5742</v>
+        <v>1.2786</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6191</v>
+        <v>-0.6914</v>
       </c>
       <c r="K25" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="L25" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.04489999999999994</v>
+        <v>0.5871999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>203</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>DEV7L</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0021</v>
+        <v>0.4045</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0002</v>
+        <v>0.0338</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4431</v>
+        <v>-0.4554</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0021</v>
+        <v>0.4045</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9381</v>
+        <v>0.4045</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.9360000000000001</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9381</v>
+        <v>0.4045</v>
       </c>
       <c r="I26" t="n">
-        <v>0.9381</v>
+        <v>0.4045</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.9360000000000001</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="L26" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.002099999999999991</v>
+        <v>0.4045</v>
       </c>
       <c r="N26" t="n">
-        <v>173</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27">
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0134</v>
+        <v>0.3025</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0011</v>
+        <v>0.0253</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4492</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0134</v>
+        <v>0.3025</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1706</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1572</v>
+        <v>0.2363</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1706</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1706</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1572</v>
+        <v>0.2363</v>
       </c>
       <c r="K27" t="n">
         <v>118</v>
@@ -1679,7 +1679,7 @@
         <v>55</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0134</v>
+        <v>0.3025</v>
       </c>
       <c r="N27" t="n">
         <v>173</v>
@@ -1688,32 +1688,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fredi</t>
+          <t>juho</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.3962</v>
+        <v>-0.054</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0331</v>
+        <v>-0.0045</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6018</v>
+        <v>-0.6624</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.3962</v>
+        <v>-0.054</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.3962</v>
+        <v>-0.054</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.3962</v>
+        <v>-0.054</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.3962</v>
+        <v>-0.054</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.3962</v>
+        <v>-0.054</v>
       </c>
       <c r="N28" t="n">
         <v>106</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>juho</t>
+          <t>kaper</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.6156</v>
+        <v>-0.2258</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0514</v>
+        <v>-0.0188</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6892</v>
+        <v>-0.74</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.6156</v>
+        <v>-0.2258</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.6156</v>
+        <v>0.5527</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>-0.7785</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6156</v>
+        <v>0.5527</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.6156</v>
+        <v>0.5527</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-0.7785</v>
       </c>
       <c r="K29" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6156</v>
+        <v>-0.2258</v>
       </c>
       <c r="N29" t="n">
-        <v>106</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>kaper</t>
+          <t>fredi</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.7661</v>
+        <v>-0.2676</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.064</v>
+        <v>-0.0223</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7491</v>
+        <v>-0.7588</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.7661</v>
+        <v>-0.2676</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2339</v>
+        <v>-0.2676</v>
       </c>
       <c r="G30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2339</v>
+        <v>-0.2676</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2339</v>
+        <v>-0.2676</v>
       </c>
       <c r="J30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L30" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.7661</v>
+        <v>-0.2676</v>
       </c>
       <c r="N30" t="n">
-        <v>181</v>
+        <v>106</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.8012</v>
+        <v>-0.372</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0669</v>
+        <v>-0.0311</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7631</v>
+        <v>-0.806</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.8012</v>
+        <v>-0.372</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8012</v>
+        <v>-0.372</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8012</v>
+        <v>-0.372</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8012</v>
+        <v>-0.372</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.8012</v>
+        <v>-0.372</v>
       </c>
       <c r="N31" t="n">
         <v>133</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.9409</v>
+        <v>-0.5917</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0785</v>
+        <v>-0.0494</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8188</v>
+        <v>-0.9051</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.9409</v>
+        <v>-0.5917</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.2897</v>
+        <v>-0.9849</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3488</v>
+        <v>0.3932</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.2897</v>
+        <v>-0.9849</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.0453</v>
+        <v>-0.5121</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3488</v>
+        <v>0.3932</v>
       </c>
       <c r="K32" t="n">
         <v>144</v>
@@ -1909,7 +1909,7 @@
         <v>59</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.6964999999999999</v>
+        <v>-0.1189</v>
       </c>
       <c r="N32" t="n">
         <v>203</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.1636</v>
+        <v>-0.7589</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.09710000000000001</v>
+        <v>-0.0634</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9075</v>
+        <v>-0.9806</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.1636</v>
+        <v>-0.7589</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.1636</v>
+        <v>-0.7589</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.1636</v>
+        <v>-0.7589</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.1636</v>
+        <v>-0.7589</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.1636</v>
+        <v>-0.7589</v>
       </c>
       <c r="N33" t="n">
         <v>133</v>
@@ -1964,323 +1964,323 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>hussaR</t>
+          <t>SZPERO</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.5887</v>
+        <v>-1.0282</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1326</v>
+        <v>-0.0858</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.0768</v>
+        <v>-1.1022</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.5887</v>
+        <v>-1.0282</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.5887</v>
+        <v>-0.4903</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.5379</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.5887</v>
+        <v>-0.4903</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.5887</v>
+        <v>-0.4903</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.5379</v>
       </c>
       <c r="K34" t="n">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.5887</v>
+        <v>-1.0282</v>
       </c>
       <c r="N34" t="n">
-        <v>133</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>chrisJ</t>
+          <t>hussaR</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.6881</v>
+        <v>-1.041</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1409</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1164</v>
+        <v>-1.108</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.6881</v>
+        <v>-1.041</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.6881</v>
+        <v>-1.041</v>
       </c>
       <c r="G35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.6881</v>
+        <v>-1.041</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5577</v>
+        <v>-1.041</v>
       </c>
       <c r="J35" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="L35" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.5577</v>
+        <v>-1.041</v>
       </c>
       <c r="N35" t="n">
-        <v>200</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SZPERO</t>
+          <t>arbie</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.6927</v>
+        <v>-1.0914</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1413</v>
+        <v>-0.0911</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1183</v>
+        <v>-1.1307</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.6927</v>
+        <v>-1.0914</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-1.0914</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.8888</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-1.0914</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-1.0914</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8888</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L36" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.6927</v>
+        <v>-1.0914</v>
       </c>
       <c r="N36" t="n">
-        <v>181</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>arbie</t>
+          <t>BLUEE</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.7366</v>
+        <v>-1.3694</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.145</v>
+        <v>-0.1143</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1358</v>
+        <v>-1.2562</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.7366</v>
+        <v>-1.3694</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.7366</v>
+        <v>-1.3694</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.7366</v>
+        <v>-1.3694</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.7366</v>
+        <v>-1.3694</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.7366</v>
+        <v>-1.3694</v>
       </c>
       <c r="N37" t="n">
-        <v>133</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BLUEE</t>
+          <t>chrisJ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.7734</v>
+        <v>-1.3754</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.148</v>
+        <v>-0.1148</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1504</v>
+        <v>-1.2589</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.7734</v>
+        <v>-1.3754</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.7734</v>
+        <v>-0.6172</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.7582</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.7734</v>
+        <v>-0.6172</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.7734</v>
+        <v>-0.3209</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.7582</v>
       </c>
       <c r="K38" t="n">
-        <v>106</v>
+        <v>151</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.7734</v>
+        <v>-1.0791</v>
       </c>
       <c r="N38" t="n">
-        <v>106</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>phr</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-2.0315</v>
+        <v>-1.4063</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1696</v>
+        <v>-0.1174</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2533</v>
+        <v>-1.2729</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.0315</v>
+        <v>-1.4063</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5881</v>
+        <v>-0.6313</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.4434</v>
+        <v>-0.775</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5881</v>
+        <v>-0.6313</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2872</v>
+        <v>-0.6313</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.4434</v>
+        <v>-0.775</v>
       </c>
       <c r="K39" t="n">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L39" t="n">
-        <v>49</v>
+        <v>185</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.7306</v>
+        <v>-1.4063</v>
       </c>
       <c r="N39" t="n">
-        <v>200</v>
+        <v>292</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>phr</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.0431</v>
+        <v>-2.4619</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1706</v>
+        <v>-0.2055</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2579</v>
+        <v>-1.7494</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.0431</v>
+        <v>-2.4619</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.0818</v>
+        <v>-2.2906</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.9613</v>
+        <v>-0.1713</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.0818</v>
+        <v>-2.2906</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.0818</v>
+        <v>-1.191</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9613</v>
+        <v>-0.1713</v>
       </c>
       <c r="K40" t="n">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L40" t="n">
-        <v>185</v>
+        <v>49</v>
       </c>
       <c r="M40" t="n">
-        <v>-2.0431</v>
+        <v>-1.3623</v>
       </c>
       <c r="N40" t="n">
-        <v>292</v>
+        <v>200</v>
       </c>
     </row>
     <row r="41">
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.9602</v>
+        <v>-4.3129</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.4141</v>
+        <v>-0.36</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.4201</v>
+        <v>-2.5851</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.9602</v>
+        <v>-4.3129</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.9289</v>
+        <v>-2.444</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.0313</v>
+        <v>-1.8689</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.9289</v>
+        <v>-2.444</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.9536</v>
+        <v>-2.5445</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.0313</v>
+        <v>-1.8689</v>
       </c>
       <c r="K41" t="n">
         <v>152</v>
@@ -2323,7 +2323,7 @@
         <v>214</v>
       </c>
       <c r="M41" t="n">
-        <v>-4.9849</v>
+        <v>-4.4134</v>
       </c>
       <c r="N41" t="n">
         <v>366</v>
@@ -2429,10 +2429,10 @@
         <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2041</v>
+        <v>0.1666</v>
       </c>
       <c r="J2" t="n">
-        <v>5.7148</v>
+        <v>4.6648</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.07</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1466</v>
+        <v>0.1233</v>
       </c>
       <c r="J3" t="n">
-        <v>4.1048</v>
+        <v>3.4524</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1241</v>
+        <v>0.1084</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4748</v>
+        <v>3.0352</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0979</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7412</v>
+        <v>2.6096</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0033</v>
+        <v>0.0212</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0924</v>
+        <v>0.5936</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5154</v>
+        <v>0.4707</v>
       </c>
       <c r="J7" t="n">
-        <v>14.4312</v>
+        <v>13.1796</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.29</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4892</v>
+        <v>0.4445</v>
       </c>
       <c r="J8" t="n">
-        <v>13.6976</v>
+        <v>12.446</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3648</v>
+        <v>0.3236</v>
       </c>
       <c r="J9" t="n">
-        <v>10.2144</v>
+        <v>9.0608</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.381</v>
+        <v>-0.2351</v>
       </c>
       <c r="J10" t="n">
-        <v>-10.668</v>
+        <v>-6.5828</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.66</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5799</v>
+        <v>-0.3795</v>
       </c>
       <c r="J11" t="n">
-        <v>-16.2372</v>
+        <v>-10.626</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.24</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4352</v>
+        <v>0.5065</v>
       </c>
       <c r="J12" t="n">
-        <v>11.3152</v>
+        <v>13.169</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.18</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3495</v>
+        <v>0.3975</v>
       </c>
       <c r="J13" t="n">
-        <v>9.087</v>
+        <v>10.335</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.187</v>
+        <v>0.2018</v>
       </c>
       <c r="J14" t="n">
-        <v>4.862</v>
+        <v>5.2468</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.93</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1792</v>
+        <v>-0.1015</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.6592</v>
+        <v>-2.639</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.64</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5988</v>
+        <v>-0.3939</v>
       </c>
       <c r="J16" t="n">
-        <v>-15.5688</v>
+        <v>-10.2414</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.51</v>
       </c>
       <c r="I17" t="n">
-        <v>1.317</v>
+        <v>1.1976</v>
       </c>
       <c r="J17" t="n">
-        <v>34.242</v>
+        <v>31.1376</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.21</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>17.1288</v>
+        <v>16.211</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.93</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3342</v>
+        <v>-0.2755</v>
       </c>
       <c r="J19" t="n">
-        <v>-8.6892</v>
+        <v>-7.163</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.87</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5081</v>
+        <v>-0.45</v>
       </c>
       <c r="J20" t="n">
-        <v>-13.2106</v>
+        <v>-11.7</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.76</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7844</v>
+        <v>-0.7401</v>
       </c>
       <c r="J21" t="n">
-        <v>-20.3944</v>
+        <v>-19.2426</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.14</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3243</v>
+        <v>0.3533</v>
       </c>
       <c r="J22" t="n">
-        <v>8.7561</v>
+        <v>9.539099999999999</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.03</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1291</v>
+        <v>0.1116</v>
       </c>
       <c r="J23" t="n">
-        <v>3.4857</v>
+        <v>3.0132</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.95</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0815</v>
+        <v>-0.0688</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.2005</v>
+        <v>-1.8576</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.87</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2482</v>
+        <v>-0.1573</v>
       </c>
       <c r="J25" t="n">
-        <v>-6.7014</v>
+        <v>-4.2471</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.59</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6448</v>
+        <v>-0.4291</v>
       </c>
       <c r="J26" t="n">
-        <v>-17.4096</v>
+        <v>-11.5857</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.46</v>
       </c>
       <c r="I27" t="n">
-        <v>1.1573</v>
+        <v>1.0976</v>
       </c>
       <c r="J27" t="n">
-        <v>31.2471</v>
+        <v>29.6352</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.44</v>
       </c>
       <c r="I28" t="n">
-        <v>1.1161</v>
+        <v>1.0714</v>
       </c>
       <c r="J28" t="n">
-        <v>30.1347</v>
+        <v>28.9278</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.22</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6142</v>
+        <v>0.6137</v>
       </c>
       <c r="J29" t="n">
-        <v>16.5834</v>
+        <v>16.5699</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3797</v>
+        <v>-0.3058</v>
       </c>
       <c r="J30" t="n">
-        <v>-10.2519</v>
+        <v>-8.256600000000001</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7455000000000001</v>
+        <v>-0.6931</v>
       </c>
       <c r="J31" t="n">
-        <v>-20.1285</v>
+        <v>-18.7137</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.3</v>
       </c>
       <c r="I32" t="n">
-        <v>0.505</v>
+        <v>0.4911</v>
       </c>
       <c r="J32" t="n">
-        <v>15.15</v>
+        <v>14.733</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.27</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4653</v>
+        <v>0.4607</v>
       </c>
       <c r="J33" t="n">
-        <v>13.959</v>
+        <v>13.821</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.21</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3821</v>
+        <v>0.3983</v>
       </c>
       <c r="J34" t="n">
-        <v>11.463</v>
+        <v>11.949</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.79</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4077</v>
+        <v>-0.2542</v>
       </c>
       <c r="J35" t="n">
-        <v>-12.231</v>
+        <v>-7.626</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.66</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5788</v>
+        <v>-0.3787</v>
       </c>
       <c r="J36" t="n">
-        <v>-17.364</v>
+        <v>-11.361</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.17</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5444</v>
+        <v>0.4405</v>
       </c>
       <c r="J37" t="n">
-        <v>16.332</v>
+        <v>13.215</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.13</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4332</v>
+        <v>0.3785</v>
       </c>
       <c r="J38" t="n">
-        <v>12.996</v>
+        <v>11.355</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.09</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3089</v>
+        <v>0.2995</v>
       </c>
       <c r="J39" t="n">
-        <v>9.266999999999999</v>
+        <v>8.984999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.04</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1177</v>
+        <v>0.1499</v>
       </c>
       <c r="J40" t="n">
-        <v>3.531</v>
+        <v>4.497</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3111</v>
+        <v>-0.2493</v>
       </c>
       <c r="J41" t="n">
-        <v>-9.333</v>
+        <v>-7.479</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.34</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5513</v>
+        <v>0.5279</v>
       </c>
       <c r="J42" t="n">
-        <v>15.9877</v>
+        <v>15.3091</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.08</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1646</v>
+        <v>0.1931</v>
       </c>
       <c r="J43" t="n">
-        <v>4.7734</v>
+        <v>5.5999</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0333</v>
+        <v>-0.0051</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.9657</v>
+        <v>-0.1479</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1159</v>
+        <v>-0.0561</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.3611</v>
+        <v>-1.6269</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.92</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2114</v>
+        <v>-0.1184</v>
       </c>
       <c r="J46" t="n">
-        <v>-6.1306</v>
+        <v>-3.4336</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.51</v>
       </c>
       <c r="I47" t="n">
-        <v>1.2816</v>
+        <v>0.902</v>
       </c>
       <c r="J47" t="n">
-        <v>37.1664</v>
+        <v>26.158</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.22</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6439</v>
+        <v>0.5061</v>
       </c>
       <c r="J48" t="n">
-        <v>18.6731</v>
+        <v>14.6769</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2847</v>
+        <v>0.3185</v>
       </c>
       <c r="J49" t="n">
-        <v>8.2563</v>
+        <v>9.236499999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.04</v>
       </c>
       <c r="I50" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.1386</v>
       </c>
       <c r="J50" t="n">
-        <v>2.5201</v>
+        <v>4.0194</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.74</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8493000000000001</v>
+        <v>-0.8079</v>
       </c>
       <c r="J51" t="n">
-        <v>-24.6297</v>
+        <v>-23.4291</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.04</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2373</v>
+        <v>0.2329</v>
       </c>
       <c r="J52" t="n">
-        <v>4.5087</v>
+        <v>4.4251</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.82</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2123</v>
+        <v>-0.1812</v>
       </c>
       <c r="J53" t="n">
-        <v>-4.0337</v>
+        <v>-3.4428</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.7</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.4241</v>
+        <v>-0.2983</v>
       </c>
       <c r="J54" t="n">
-        <v>-8.0579</v>
+        <v>-5.6677</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.63</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.3628</v>
       </c>
       <c r="J55" t="n">
-        <v>-10.1992</v>
+        <v>-6.8932</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.36</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8875999999999999</v>
+        <v>-0.6147</v>
       </c>
       <c r="J56" t="n">
-        <v>-16.8644</v>
+        <v>-11.6793</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.91</v>
       </c>
       <c r="I57" t="n">
-        <v>1.801</v>
+        <v>1.3017</v>
       </c>
       <c r="J57" t="n">
-        <v>34.219</v>
+        <v>24.7323</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.54</v>
       </c>
       <c r="I58" t="n">
-        <v>1.1855</v>
+        <v>0.8728</v>
       </c>
       <c r="J58" t="n">
-        <v>22.5245</v>
+        <v>16.5832</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.53</v>
       </c>
       <c r="I59" t="n">
-        <v>1.1648</v>
+        <v>0.8609</v>
       </c>
       <c r="J59" t="n">
-        <v>22.1312</v>
+        <v>16.3571</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.31</v>
       </c>
       <c r="I60" t="n">
-        <v>0.655</v>
+        <v>0.591</v>
       </c>
       <c r="J60" t="n">
-        <v>12.445</v>
+        <v>11.229</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.92</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.478</v>
+        <v>-0.3979</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.082000000000001</v>
+        <v>-7.5601</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.25</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4442</v>
+        <v>0.4434</v>
       </c>
       <c r="J62" t="n">
-        <v>13.326</v>
+        <v>13.302</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.12</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2507</v>
+        <v>0.2796</v>
       </c>
       <c r="J63" t="n">
-        <v>7.521</v>
+        <v>8.388</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.11</v>
       </c>
       <c r="I64" t="n">
-        <v>0.234</v>
+        <v>0.2599</v>
       </c>
       <c r="J64" t="n">
-        <v>7.02</v>
+        <v>7.797</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.02</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0448</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>1.344</v>
+        <v>1.884</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.64</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.6009</v>
+        <v>-0.3954</v>
       </c>
       <c r="J66" t="n">
-        <v>-18.027</v>
+        <v>-11.862</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.18</v>
       </c>
       <c r="I67" t="n">
-        <v>0.597</v>
+        <v>0.4646</v>
       </c>
       <c r="J67" t="n">
-        <v>17.91</v>
+        <v>13.938</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.08</v>
       </c>
       <c r="I68" t="n">
-        <v>0.3118</v>
+        <v>0.2806</v>
       </c>
       <c r="J68" t="n">
-        <v>9.353999999999999</v>
+        <v>8.417999999999999</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0368</v>
+        <v>-0.006</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.104</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.96</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.221</v>
+        <v>-0.1726</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.63</v>
+        <v>-5.178</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2896</v>
+        <v>-0.2377</v>
       </c>
       <c r="J71" t="n">
-        <v>-8.688000000000001</v>
+        <v>-7.131</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.96</v>
       </c>
       <c r="I72" t="n">
-        <v>1.8411</v>
+        <v>1.3515</v>
       </c>
       <c r="J72" t="n">
-        <v>38.6631</v>
+        <v>28.3815</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.42</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.7281</v>
       </c>
       <c r="J73" t="n">
-        <v>18.6186</v>
+        <v>15.2901</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.35</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7323</v>
+        <v>0.6401</v>
       </c>
       <c r="J74" t="n">
-        <v>15.3783</v>
+        <v>13.4421</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.34</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7104</v>
+        <v>0.6271</v>
       </c>
       <c r="J75" t="n">
-        <v>14.9184</v>
+        <v>13.1691</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.28</v>
       </c>
       <c r="I76" t="n">
-        <v>0.5777</v>
+        <v>0.5474</v>
       </c>
       <c r="J76" t="n">
-        <v>12.1317</v>
+        <v>11.4954</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.83</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.198</v>
+        <v>-0.1713</v>
       </c>
       <c r="J77" t="n">
-        <v>-4.158</v>
+        <v>-3.5973</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.83</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.198</v>
+        <v>-0.1713</v>
       </c>
       <c r="J78" t="n">
-        <v>-4.158</v>
+        <v>-3.5973</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2305</v>
+        <v>-0.1926</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.8405</v>
+        <v>-4.0446</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.63</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.5385</v>
+        <v>-0.3635</v>
       </c>
       <c r="J80" t="n">
-        <v>-11.3085</v>
+        <v>-7.6335</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.47</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.7539</v>
+        <v>-0.513</v>
       </c>
       <c r="J81" t="n">
-        <v>-15.8319</v>
+        <v>-10.773</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.05</v>
       </c>
       <c r="I82" t="n">
-        <v>0.178</v>
+        <v>0.128</v>
       </c>
       <c r="J82" t="n">
-        <v>5.34</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.96</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0506</v>
+        <v>-0.0535</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.518</v>
+        <v>-1.605</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.93</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1119</v>
+        <v>-0.0907</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.357</v>
+        <v>-2.721</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3231</v>
+        <v>-0.2064</v>
       </c>
       <c r="J85" t="n">
-        <v>-9.693</v>
+        <v>-6.192</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4708</v>
+        <v>-0.3045</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.124</v>
+        <v>-9.135</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.76</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0029</v>
+        <v>0.68</v>
       </c>
       <c r="J87" t="n">
-        <v>30.087</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.08</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1221</v>
+        <v>0.1309</v>
       </c>
       <c r="J88" t="n">
-        <v>3.663</v>
+        <v>3.927</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.05</v>
       </c>
       <c r="I89" t="n">
-        <v>0.066</v>
+        <v>0.0848</v>
       </c>
       <c r="J89" t="n">
-        <v>1.98</v>
+        <v>2.544</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0553</v>
+        <v>-0.0122</v>
       </c>
       <c r="J90" t="n">
-        <v>-1.659</v>
+        <v>-0.366</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.78</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4369</v>
+        <v>-0.2733</v>
       </c>
       <c r="J91" t="n">
-        <v>-13.107</v>
+        <v>-8.199</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.48</v>
       </c>
       <c r="I92" t="n">
-        <v>1.1959</v>
+        <v>0.849</v>
       </c>
       <c r="J92" t="n">
-        <v>27.5057</v>
+        <v>19.527</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.29</v>
       </c>
       <c r="I93" t="n">
-        <v>0.7846</v>
+        <v>0.5958</v>
       </c>
       <c r="J93" t="n">
-        <v>18.0458</v>
+        <v>13.7034</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>0.2805</v>
+        <v>0.3328</v>
       </c>
       <c r="J94" t="n">
-        <v>6.4515</v>
+        <v>7.6544</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.02</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.0114</v>
+        <v>0.0544</v>
       </c>
       <c r="J95" t="n">
-        <v>-0.2622</v>
+        <v>1.2512</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.96</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2859</v>
+        <v>-0.2099</v>
       </c>
       <c r="J96" t="n">
-        <v>-6.5757</v>
+        <v>-4.8277</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.13</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3139</v>
+        <v>0.3342</v>
       </c>
       <c r="J97" t="n">
-        <v>7.2197</v>
+        <v>7.6866</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.11</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2818</v>
+        <v>0.2975</v>
       </c>
       <c r="J98" t="n">
-        <v>6.4814</v>
+        <v>6.8425</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.86</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2592</v>
+        <v>-0.1662</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.9616</v>
+        <v>-3.8226</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.72</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.4724</v>
+        <v>-0.3053</v>
       </c>
       <c r="J100" t="n">
-        <v>-10.8652</v>
+        <v>-7.0219</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.5132</v>
+        <v>-0.3339</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.8036</v>
+        <v>-7.6797</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.77</v>
       </c>
       <c r="I102" t="n">
-        <v>1.7074</v>
+        <v>1.1962</v>
       </c>
       <c r="J102" t="n">
-        <v>42.685</v>
+        <v>29.905</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.46</v>
       </c>
       <c r="I103" t="n">
-        <v>1.1282</v>
+        <v>0.8105</v>
       </c>
       <c r="J103" t="n">
-        <v>28.205</v>
+        <v>20.2625</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.2</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4989</v>
+        <v>0.4651</v>
       </c>
       <c r="J104" t="n">
-        <v>12.4725</v>
+        <v>11.6275</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.073</v>
+        <v>0.1459</v>
       </c>
       <c r="J105" t="n">
-        <v>1.825</v>
+        <v>3.6475</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.65</v>
       </c>
       <c r="I106" t="n">
-        <v>-1.066</v>
+        <v>-1.0496</v>
       </c>
       <c r="J106" t="n">
-        <v>-26.65</v>
+        <v>-26.24</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.19</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4134</v>
+        <v>0.4128</v>
       </c>
       <c r="J107" t="n">
-        <v>10.335</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.08</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2403</v>
+        <v>0.2424</v>
       </c>
       <c r="J108" t="n">
-        <v>6.0075</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.88</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.2021</v>
+        <v>-0.1436</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.0525</v>
+        <v>-3.59</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.7</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4937</v>
+        <v>-0.3213</v>
       </c>
       <c r="J110" t="n">
-        <v>-12.3425</v>
+        <v>-8.032500000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.54</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.6997</v>
+        <v>-0.4705</v>
       </c>
       <c r="J111" t="n">
-        <v>-17.4925</v>
+        <v>-11.7625</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.28</v>
       </c>
       <c r="I112" t="n">
-        <v>0.8293</v>
+        <v>0.608</v>
       </c>
       <c r="J112" t="n">
-        <v>24.879</v>
+        <v>18.24</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.08</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2955</v>
+        <v>0.2756</v>
       </c>
       <c r="J113" t="n">
-        <v>8.865</v>
+        <v>8.268000000000001</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.05</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1788</v>
+        <v>0.1861</v>
       </c>
       <c r="J114" t="n">
-        <v>5.364</v>
+        <v>5.583</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.03</v>
       </c>
       <c r="I115" t="n">
-        <v>0.0969</v>
+        <v>0.1205</v>
       </c>
       <c r="J115" t="n">
-        <v>2.907</v>
+        <v>3.615</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.82</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6372</v>
+        <v>-0.584</v>
       </c>
       <c r="J116" t="n">
-        <v>-19.116</v>
+        <v>-17.52</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.19</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3593</v>
+        <v>0.3799</v>
       </c>
       <c r="J117" t="n">
-        <v>10.779</v>
+        <v>11.397</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.17</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3295</v>
+        <v>0.3582</v>
       </c>
       <c r="J118" t="n">
-        <v>9.885</v>
+        <v>10.746</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0193</v>
+        <v>-0.002</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.579</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.9</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2363</v>
+        <v>-0.1373</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.089</v>
+        <v>-4.119</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.88</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2692</v>
+        <v>-0.1593</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.076000000000001</v>
+        <v>-4.779</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.14</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3767</v>
+        <v>0.4172</v>
       </c>
       <c r="J122" t="n">
-        <v>9.4175</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0596</v>
+        <v>-0.0722</v>
       </c>
       <c r="J123" t="n">
-        <v>-1.49</v>
+        <v>-1.805</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.66</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.5215</v>
+        <v>-0.346</v>
       </c>
       <c r="J124" t="n">
-        <v>-13.0375</v>
+        <v>-8.65</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.64</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.5493</v>
+        <v>-0.3649</v>
       </c>
       <c r="J125" t="n">
-        <v>-13.7325</v>
+        <v>-9.1225</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.55</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.6686</v>
+        <v>-0.449</v>
       </c>
       <c r="J126" t="n">
-        <v>-16.715</v>
+        <v>-11.225</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.58</v>
       </c>
       <c r="I127" t="n">
-        <v>1.3456</v>
+        <v>1.2255</v>
       </c>
       <c r="J127" t="n">
-        <v>33.64</v>
+        <v>30.6375</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.52</v>
       </c>
       <c r="I128" t="n">
-        <v>1.2281</v>
+        <v>1.1509</v>
       </c>
       <c r="J128" t="n">
-        <v>30.7025</v>
+        <v>28.7725</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.16</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3677</v>
+        <v>0.4476</v>
       </c>
       <c r="J129" t="n">
-        <v>9.192500000000001</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.05</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0569</v>
+        <v>0.1353</v>
       </c>
       <c r="J130" t="n">
-        <v>1.4225</v>
+        <v>3.3825</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.04</v>
       </c>
       <c r="I131" t="n">
-        <v>0.0241</v>
+        <v>0.1022</v>
       </c>
       <c r="J131" t="n">
-        <v>0.6025</v>
+        <v>2.555</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.11</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2956</v>
+        <v>0.312</v>
       </c>
       <c r="J132" t="n">
-        <v>8.2768</v>
+        <v>8.736000000000001</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.93</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0969</v>
+        <v>-0.0868</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.7132</v>
+        <v>-2.4304</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.87</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.2129</v>
+        <v>-0.1529</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.9612</v>
+        <v>-4.2812</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.77</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.3896</v>
+        <v>-0.2521</v>
       </c>
       <c r="J135" t="n">
-        <v>-10.9088</v>
+        <v>-7.0588</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.65</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5580000000000001</v>
+        <v>-0.367</v>
       </c>
       <c r="J136" t="n">
-        <v>-15.624</v>
+        <v>-10.276</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.39</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9774</v>
+        <v>0.9794</v>
       </c>
       <c r="J137" t="n">
-        <v>27.3672</v>
+        <v>27.4232</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.34</v>
       </c>
       <c r="I138" t="n">
-        <v>0.8662</v>
+        <v>0.8756</v>
       </c>
       <c r="J138" t="n">
-        <v>24.2536</v>
+        <v>24.5168</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.27</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6985</v>
+        <v>0.7169</v>
       </c>
       <c r="J139" t="n">
-        <v>19.558</v>
+        <v>20.0732</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.18</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4404</v>
+        <v>0.5064</v>
       </c>
       <c r="J140" t="n">
-        <v>12.3312</v>
+        <v>14.1792</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.98</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.2345</v>
+        <v>-0.1527</v>
       </c>
       <c r="J141" t="n">
-        <v>-6.566</v>
+        <v>-4.2756</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.15</v>
       </c>
       <c r="I142" t="n">
-        <v>0.5364</v>
+        <v>0.4876</v>
       </c>
       <c r="J142" t="n">
-        <v>22.5288</v>
+        <v>20.4792</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.01</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0679</v>
+        <v>0.053</v>
       </c>
       <c r="J143" t="n">
-        <v>2.8518</v>
+        <v>2.226</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.01</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0679</v>
+        <v>0.053</v>
       </c>
       <c r="J144" t="n">
-        <v>2.8518</v>
+        <v>2.226</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.96</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2007</v>
+        <v>-0.1648</v>
       </c>
       <c r="J145" t="n">
-        <v>-8.429399999999999</v>
+        <v>-6.9216</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.88</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4557</v>
+        <v>-0.4063</v>
       </c>
       <c r="J146" t="n">
-        <v>-19.1394</v>
+        <v>-17.0646</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.16</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3019</v>
+        <v>0.3479</v>
       </c>
       <c r="J147" t="n">
-        <v>12.6798</v>
+        <v>14.6118</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2022</v>
+        <v>0.2333</v>
       </c>
       <c r="J148" t="n">
-        <v>8.4924</v>
+        <v>9.7986</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.09</v>
       </c>
       <c r="I149" t="n">
-        <v>0.1839</v>
+        <v>0.2133</v>
       </c>
       <c r="J149" t="n">
-        <v>7.7238</v>
+        <v>8.958600000000001</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.02</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0274</v>
+        <v>0.0578</v>
       </c>
       <c r="J150" t="n">
-        <v>1.1508</v>
+        <v>2.4276</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1755</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J151" t="n">
-        <v>-7.371</v>
+        <v>-3.9774</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.58</v>
       </c>
       <c r="I152" t="n">
-        <v>1.3206</v>
+        <v>1.214</v>
       </c>
       <c r="J152" t="n">
-        <v>29.0532</v>
+        <v>26.708</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.49</v>
       </c>
       <c r="I153" t="n">
-        <v>1.1415</v>
+        <v>1.1033</v>
       </c>
       <c r="J153" t="n">
-        <v>25.113</v>
+        <v>24.2726</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.31</v>
       </c>
       <c r="I154" t="n">
-        <v>0.7181</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="J154" t="n">
-        <v>15.7982</v>
+        <v>17.4196</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.19</v>
       </c>
       <c r="I155" t="n">
-        <v>0.4206</v>
+        <v>0.5117</v>
       </c>
       <c r="J155" t="n">
-        <v>9.2532</v>
+        <v>11.2574</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.05</v>
       </c>
       <c r="I156" t="n">
-        <v>0.0396</v>
+        <v>0.1227</v>
       </c>
       <c r="J156" t="n">
-        <v>0.8712</v>
+        <v>2.6994</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.13</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3363</v>
+        <v>0.3639</v>
       </c>
       <c r="J157" t="n">
-        <v>7.3986</v>
+        <v>8.005800000000001</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.87</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1972</v>
+        <v>-0.1508</v>
       </c>
       <c r="J158" t="n">
-        <v>-4.3384</v>
+        <v>-3.3176</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.85</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.236</v>
+        <v>-0.1712</v>
       </c>
       <c r="J159" t="n">
-        <v>-5.192</v>
+        <v>-3.7664</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.76</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.3967</v>
+        <v>-0.259</v>
       </c>
       <c r="J160" t="n">
-        <v>-8.727399999999999</v>
+        <v>-5.698</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.61</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.6052</v>
+        <v>-0.4015</v>
       </c>
       <c r="J161" t="n">
-        <v>-13.3144</v>
+        <v>-8.833</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.65</v>
       </c>
       <c r="I162" t="n">
-        <v>1.4147</v>
+        <v>1.2813</v>
       </c>
       <c r="J162" t="n">
-        <v>32.5381</v>
+        <v>29.4699</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.48</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0753</v>
+        <v>1.0784</v>
       </c>
       <c r="J163" t="n">
-        <v>24.7319</v>
+        <v>24.8032</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.43</v>
       </c>
       <c r="I164" t="n">
-        <v>0.962</v>
+        <v>1.0132</v>
       </c>
       <c r="J164" t="n">
-        <v>22.126</v>
+        <v>23.3036</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.28</v>
       </c>
       <c r="I165" t="n">
-        <v>0.599</v>
+        <v>0.708</v>
       </c>
       <c r="J165" t="n">
-        <v>13.777</v>
+        <v>16.284</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.22</v>
       </c>
       <c r="I166" t="n">
-        <v>0.4599</v>
+        <v>0.5665</v>
       </c>
       <c r="J166" t="n">
-        <v>10.5777</v>
+        <v>13.0295</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.11</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3494</v>
+        <v>0.3817</v>
       </c>
       <c r="J167" t="n">
-        <v>8.036199999999999</v>
+        <v>8.7791</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.88</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1268</v>
+        <v>-0.1213</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.9164</v>
+        <v>-2.7899</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.66</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.5043</v>
+        <v>-0.3391</v>
       </c>
       <c r="J169" t="n">
-        <v>-11.5989</v>
+        <v>-7.7993</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.54</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.6701</v>
+        <v>-0.4514</v>
       </c>
       <c r="J170" t="n">
-        <v>-15.4123</v>
+        <v>-10.3822</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.5</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7215</v>
+        <v>-0.4887</v>
       </c>
       <c r="J171" t="n">
-        <v>-16.5945</v>
+        <v>-11.2401</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.32</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8662</v>
+        <v>0.8555</v>
       </c>
       <c r="J172" t="n">
-        <v>25.986</v>
+        <v>25.665</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.23</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6516999999999999</v>
+        <v>0.6424</v>
       </c>
       <c r="J173" t="n">
-        <v>19.551</v>
+        <v>19.272</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.18</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5188</v>
+        <v>0.5201</v>
       </c>
       <c r="J174" t="n">
-        <v>15.564</v>
+        <v>15.603</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.15</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4234</v>
+        <v>0.4458</v>
       </c>
       <c r="J175" t="n">
-        <v>12.702</v>
+        <v>13.374</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.87</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5417</v>
+        <v>-0.4757</v>
       </c>
       <c r="J176" t="n">
-        <v>-16.251</v>
+        <v>-14.271</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.33</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6026</v>
+        <v>0.7281</v>
       </c>
       <c r="J177" t="n">
-        <v>18.078</v>
+        <v>21.843</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0622</v>
+        <v>0.0274</v>
       </c>
       <c r="J178" t="n">
-        <v>1.866</v>
+        <v>0.822</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.82</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3159</v>
+        <v>-0.2042</v>
       </c>
       <c r="J179" t="n">
-        <v>-9.477</v>
+        <v>-6.126</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.66</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.5476</v>
+        <v>-0.3592</v>
       </c>
       <c r="J180" t="n">
-        <v>-16.428</v>
+        <v>-10.776</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.58</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.6504</v>
+        <v>-0.4338</v>
       </c>
       <c r="J181" t="n">
-        <v>-19.512</v>
+        <v>-13.014</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.19</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5616</v>
       </c>
       <c r="J182" t="n">
-        <v>20.587</v>
+        <v>19.656</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.18</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5362</v>
       </c>
       <c r="J183" t="n">
-        <v>19.67</v>
+        <v>18.767</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.16</v>
       </c>
       <c r="I184" t="n">
-        <v>0.5081</v>
+        <v>0.4847</v>
       </c>
       <c r="J184" t="n">
-        <v>17.7835</v>
+        <v>16.9645</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.99</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1333</v>
+        <v>-0.0746</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.6655</v>
+        <v>-2.611</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.92</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3793</v>
+        <v>-0.3148</v>
       </c>
       <c r="J186" t="n">
-        <v>-13.2755</v>
+        <v>-11.018</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.24</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4645</v>
+        <v>0.5384</v>
       </c>
       <c r="J187" t="n">
-        <v>16.2575</v>
+        <v>18.844</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1</v>
       </c>
       <c r="I188" t="n">
-        <v>0.04</v>
+        <v>0.0128</v>
       </c>
       <c r="J188" t="n">
-        <v>1.4</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.85</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.2874</v>
+        <v>-0.1798</v>
       </c>
       <c r="J189" t="n">
-        <v>-10.059</v>
+        <v>-6.293</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.8</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3653</v>
+        <v>-0.2306</v>
       </c>
       <c r="J190" t="n">
-        <v>-12.7855</v>
+        <v>-8.071</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.76</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.4235</v>
+        <v>-0.2701</v>
       </c>
       <c r="J191" t="n">
-        <v>-14.8225</v>
+        <v>-9.4535</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.92</v>
       </c>
       <c r="I192" t="n">
-        <v>1.8647</v>
+        <v>1.5782</v>
       </c>
       <c r="J192" t="n">
-        <v>35.4293</v>
+        <v>29.9858</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.53</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1441</v>
+        <v>1.1304</v>
       </c>
       <c r="J193" t="n">
-        <v>21.7379</v>
+        <v>21.4776</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.49</v>
       </c>
       <c r="I194" t="n">
-        <v>1.0533</v>
+        <v>1.0838</v>
       </c>
       <c r="J194" t="n">
-        <v>20.0127</v>
+        <v>20.5922</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.45</v>
       </c>
       <c r="I195" t="n">
-        <v>0.9487</v>
+        <v>1.0355</v>
       </c>
       <c r="J195" t="n">
-        <v>18.0253</v>
+        <v>19.6745</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.01</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.142</v>
+        <v>-0.0563</v>
       </c>
       <c r="J196" t="n">
-        <v>-2.698</v>
+        <v>-1.0697</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.7</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.3061</v>
+        <v>-0.26</v>
       </c>
       <c r="J197" t="n">
-        <v>-5.8159</v>
+        <v>-4.94</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.3214</v>
+        <v>-0.2708</v>
       </c>
       <c r="J198" t="n">
-        <v>-6.1066</v>
+        <v>-5.1452</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.57</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.5112</v>
+        <v>-0.3915</v>
       </c>
       <c r="J199" t="n">
-        <v>-9.7128</v>
+        <v>-7.4385</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.45</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.725</v>
+        <v>-0.5004</v>
       </c>
       <c r="J200" t="n">
-        <v>-13.775</v>
+        <v>-9.5076</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.3</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.9286</v>
+        <v>-0.6465</v>
       </c>
       <c r="J201" t="n">
-        <v>-17.6434</v>
+        <v>-12.2835</v>
       </c>
     </row>
     <row r="202">
@@ -10469,10 +10469,10 @@
         <v>1.02</v>
       </c>
       <c r="I203" t="n">
-        <v>0.1006</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="J203" t="n">
-        <v>2.6156</v>
+        <v>2.1086</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1</v>
       </c>
       <c r="I204" t="n">
-        <v>0.04</v>
+        <v>0.0128</v>
       </c>
       <c r="J204" t="n">
-        <v>1.04</v>
+        <v>0.3328</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.95</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0893</v>
+        <v>-0.0702</v>
       </c>
       <c r="J205" t="n">
-        <v>-2.3218</v>
+        <v>-1.8252</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.61</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6224</v>
+        <v>-0.4123</v>
       </c>
       <c r="J206" t="n">
-        <v>-16.1824</v>
+        <v>-10.7198</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.4</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0562</v>
+        <v>1.0273</v>
       </c>
       <c r="J207" t="n">
-        <v>27.4612</v>
+        <v>26.7098</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.32</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8815</v>
+        <v>0.8658</v>
       </c>
       <c r="J208" t="n">
-        <v>22.919</v>
+        <v>22.5108</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.22</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6439</v>
+        <v>0.626</v>
       </c>
       <c r="J209" t="n">
-        <v>16.7414</v>
+        <v>16.276</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.88</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5058</v>
+        <v>-0.4403</v>
       </c>
       <c r="J210" t="n">
-        <v>-13.1508</v>
+        <v>-11.4478</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.7331</v>
+        <v>-0.6814</v>
       </c>
       <c r="J211" t="n">
-        <v>-19.0606</v>
+        <v>-17.7164</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.24</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3959</v>
+        <v>0.3381</v>
       </c>
       <c r="J212" t="n">
-        <v>11.877</v>
+        <v>10.143</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.23</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3817</v>
+        <v>0.3259</v>
       </c>
       <c r="J213" t="n">
-        <v>11.451</v>
+        <v>9.776999999999999</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.14</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2395</v>
+        <v>0.2129</v>
       </c>
       <c r="J214" t="n">
-        <v>7.185</v>
+        <v>6.387</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.08</v>
       </c>
       <c r="I215" t="n">
-        <v>0.1236</v>
+        <v>0.1314</v>
       </c>
       <c r="J215" t="n">
-        <v>3.708</v>
+        <v>3.942</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.96</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.155</v>
+        <v>-0.0765</v>
       </c>
       <c r="J216" t="n">
-        <v>-4.65</v>
+        <v>-2.295</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.27</v>
       </c>
       <c r="I217" t="n">
-        <v>0.5073</v>
+        <v>0.456</v>
       </c>
       <c r="J217" t="n">
-        <v>15.219</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.1074</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="J218" t="n">
-        <v>-3.222</v>
+        <v>-2.451</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.88</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2342</v>
+        <v>-0.1476</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.026</v>
+        <v>-4.428</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.3483</v>
+        <v>-0.2198</v>
       </c>
       <c r="J220" t="n">
-        <v>-10.449</v>
+        <v>-6.594</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.72</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4778</v>
+        <v>-0.3081</v>
       </c>
       <c r="J221" t="n">
-        <v>-14.334</v>
+        <v>-9.243</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.15</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3272</v>
+        <v>0.3607</v>
       </c>
       <c r="J222" t="n">
-        <v>13.7424</v>
+        <v>15.1494</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.11</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2636</v>
+        <v>0.2809</v>
       </c>
       <c r="J223" t="n">
-        <v>11.0712</v>
+        <v>11.7978</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.05</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1565</v>
+        <v>0.151</v>
       </c>
       <c r="J224" t="n">
-        <v>6.573</v>
+        <v>6.342</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.84</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.3101</v>
+        <v>-0.1925</v>
       </c>
       <c r="J225" t="n">
-        <v>-13.0242</v>
+        <v>-8.085000000000001</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.6</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6382</v>
+        <v>-0.4238</v>
       </c>
       <c r="J226" t="n">
-        <v>-26.8044</v>
+        <v>-17.7996</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.63</v>
       </c>
       <c r="I227" t="n">
-        <v>1.5059</v>
+        <v>1.3258</v>
       </c>
       <c r="J227" t="n">
-        <v>63.2478</v>
+        <v>55.6836</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.18</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5295</v>
+        <v>0.5232</v>
       </c>
       <c r="J228" t="n">
-        <v>22.239</v>
+        <v>21.9744</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.08</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2112</v>
+        <v>0.2599</v>
       </c>
       <c r="J229" t="n">
-        <v>8.8704</v>
+        <v>10.9158</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.96</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2721</v>
+        <v>-0.2005</v>
       </c>
       <c r="J230" t="n">
-        <v>-11.4282</v>
+        <v>-8.420999999999999</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.83</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6398</v>
+        <v>-0.5806</v>
       </c>
       <c r="J231" t="n">
-        <v>-26.8716</v>
+        <v>-24.3852</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.21</v>
       </c>
       <c r="I232" t="n">
-        <v>0.4134</v>
+        <v>0.3616</v>
       </c>
       <c r="J232" t="n">
-        <v>11.5752</v>
+        <v>10.1248</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.14</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3095</v>
+        <v>0.2595</v>
       </c>
       <c r="J233" t="n">
-        <v>8.666</v>
+        <v>7.266</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.08</v>
       </c>
       <c r="I234" t="n">
-        <v>0.2101</v>
+        <v>0.1655</v>
       </c>
       <c r="J234" t="n">
-        <v>5.8828</v>
+        <v>4.634</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.1348</v>
+        <v>-0.0839</v>
       </c>
       <c r="J235" t="n">
-        <v>-3.7744</v>
+        <v>-2.3492</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.41</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.8609</v>
+        <v>-0.5952</v>
       </c>
       <c r="J236" t="n">
-        <v>-24.1052</v>
+        <v>-16.6656</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.57</v>
       </c>
       <c r="I237" t="n">
-        <v>0.8107</v>
+        <v>0.7258</v>
       </c>
       <c r="J237" t="n">
-        <v>22.6996</v>
+        <v>20.3224</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.16</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2873</v>
+        <v>0.2421</v>
       </c>
       <c r="J238" t="n">
-        <v>8.0444</v>
+        <v>6.7788</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.13</v>
       </c>
       <c r="I239" t="n">
-        <v>0.2375</v>
+        <v>0.2027</v>
       </c>
       <c r="J239" t="n">
-        <v>6.65</v>
+        <v>5.6756</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.92</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2209</v>
+        <v>-0.1224</v>
       </c>
       <c r="J240" t="n">
-        <v>-6.1852</v>
+        <v>-3.4272</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.72</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.5108</v>
+        <v>-0.3278</v>
       </c>
       <c r="J241" t="n">
-        <v>-14.3024</v>
+        <v>-9.1784</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.75</v>
       </c>
       <c r="I242" t="n">
-        <v>1.6959</v>
+        <v>1.4554</v>
       </c>
       <c r="J242" t="n">
-        <v>45.7893</v>
+        <v>39.2958</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.4</v>
       </c>
       <c r="I243" t="n">
-        <v>1.0176</v>
+        <v>1.0063</v>
       </c>
       <c r="J243" t="n">
-        <v>27.4752</v>
+        <v>27.1701</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.02</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.0212</v>
+        <v>0.0484</v>
       </c>
       <c r="J244" t="n">
-        <v>-0.5724</v>
+        <v>1.3068</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.95</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.3272</v>
+        <v>-0.2494</v>
       </c>
       <c r="J245" t="n">
-        <v>-8.8344</v>
+        <v>-6.7338</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.86</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5813</v>
+        <v>-0.515</v>
       </c>
       <c r="J246" t="n">
-        <v>-15.6951</v>
+        <v>-13.905</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.19</v>
       </c>
       <c r="I247" t="n">
-        <v>0.418</v>
+        <v>0.4735</v>
       </c>
       <c r="J247" t="n">
-        <v>11.286</v>
+        <v>12.7845</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.0774</v>
+        <v>-0.0747</v>
       </c>
       <c r="J248" t="n">
-        <v>-2.0898</v>
+        <v>-2.0169</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.75</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.4193</v>
+        <v>-0.2716</v>
       </c>
       <c r="J249" t="n">
-        <v>-11.3211</v>
+        <v>-7.3332</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.74</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4339</v>
+        <v>-0.2813</v>
       </c>
       <c r="J250" t="n">
-        <v>-11.7153</v>
+        <v>-7.5951</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.71</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4766</v>
+        <v>-0.3101</v>
       </c>
       <c r="J251" t="n">
-        <v>-12.8682</v>
+        <v>-8.3727</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.74</v>
       </c>
       <c r="I252" t="n">
-        <v>1.6531</v>
+        <v>1.4269</v>
       </c>
       <c r="J252" t="n">
-        <v>41.3275</v>
+        <v>35.6725</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.48</v>
       </c>
       <c r="I253" t="n">
-        <v>1.1582</v>
+        <v>1.1051</v>
       </c>
       <c r="J253" t="n">
-        <v>28.955</v>
+        <v>27.6275</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.21</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5105</v>
+        <v>0.5764</v>
       </c>
       <c r="J254" t="n">
-        <v>12.7625</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.3746</v>
+        <v>-0.2945</v>
       </c>
       <c r="J255" t="n">
-        <v>-9.365</v>
+        <v>-7.3625</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.87</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5693</v>
+        <v>-0.4999</v>
       </c>
       <c r="J256" t="n">
-        <v>-14.2325</v>
+        <v>-12.4975</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.37</v>
       </c>
       <c r="I257" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="J257" t="n">
-        <v>16.1675</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.0785</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.27</v>
+        <v>-1.9625</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.85</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.2728</v>
+        <v>-0.1757</v>
       </c>
       <c r="J259" t="n">
-        <v>-6.82</v>
+        <v>-4.3925</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.74</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.4422</v>
+        <v>-0.285</v>
       </c>
       <c r="J260" t="n">
-        <v>-11.055</v>
+        <v>-7.125</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.57</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6657</v>
+        <v>-0.4449</v>
       </c>
       <c r="J261" t="n">
-        <v>-16.6425</v>
+        <v>-11.1225</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.49</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2011</v>
+        <v>1.1282</v>
       </c>
       <c r="J262" t="n">
-        <v>28.8264</v>
+        <v>27.0768</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.48</v>
       </c>
       <c r="I263" t="n">
-        <v>1.1809</v>
+        <v>1.1153</v>
       </c>
       <c r="J263" t="n">
-        <v>28.3416</v>
+        <v>26.7672</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.16</v>
       </c>
       <c r="I264" t="n">
-        <v>0.4046</v>
+        <v>0.4622</v>
       </c>
       <c r="J264" t="n">
-        <v>9.7104</v>
+        <v>11.0928</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.1241</v>
+        <v>-0.0491</v>
       </c>
       <c r="J265" t="n">
-        <v>-2.9784</v>
+        <v>-1.1784</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.88</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.5308</v>
+        <v>-0.461</v>
       </c>
       <c r="J266" t="n">
-        <v>-12.7392</v>
+        <v>-11.064</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.28</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5105</v>
+        <v>0.6014</v>
       </c>
       <c r="J267" t="n">
-        <v>12.252</v>
+        <v>14.4336</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.14</v>
       </c>
       <c r="I268" t="n">
-        <v>0.311</v>
+        <v>0.3404</v>
       </c>
       <c r="J268" t="n">
-        <v>7.464</v>
+        <v>8.169600000000001</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.79</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.3862</v>
+        <v>-0.2433</v>
       </c>
       <c r="J269" t="n">
-        <v>-9.268800000000001</v>
+        <v>-5.8392</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.78</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.4007</v>
+        <v>-0.2532</v>
       </c>
       <c r="J270" t="n">
-        <v>-9.6168</v>
+        <v>-6.0768</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.77</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.415</v>
+        <v>-0.263</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.960000000000001</v>
+        <v>-6.312</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.42</v>
       </c>
       <c r="I272" t="n">
-        <v>1.1339</v>
+        <v>1.0764</v>
       </c>
       <c r="J272" t="n">
-        <v>32.8831</v>
+        <v>31.2156</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.15</v>
       </c>
       <c r="I273" t="n">
-        <v>0.5019</v>
+        <v>0.4681</v>
       </c>
       <c r="J273" t="n">
-        <v>14.5551</v>
+        <v>13.5749</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.03</v>
       </c>
       <c r="I274" t="n">
-        <v>0.0935</v>
+        <v>0.1197</v>
       </c>
       <c r="J274" t="n">
-        <v>2.7115</v>
+        <v>3.4713</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.01</v>
       </c>
       <c r="I275" t="n">
-        <v>0.0071</v>
+        <v>0.0427</v>
       </c>
       <c r="J275" t="n">
-        <v>0.2059</v>
+        <v>1.2383</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.67</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.9878</v>
+        <v>-0.9626</v>
       </c>
       <c r="J276" t="n">
-        <v>-28.6462</v>
+        <v>-27.9154</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.48</v>
       </c>
       <c r="I277" t="n">
-        <v>0.7354000000000001</v>
+        <v>0.9124</v>
       </c>
       <c r="J277" t="n">
-        <v>21.3266</v>
+        <v>26.4596</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.03</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0834</v>
+        <v>0.0893</v>
       </c>
       <c r="J278" t="n">
-        <v>2.4186</v>
+        <v>2.5897</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.92</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.198</v>
+        <v>-0.1134</v>
       </c>
       <c r="J279" t="n">
-        <v>-5.742</v>
+        <v>-3.2886</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.85</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.3132</v>
+        <v>-0.1898</v>
       </c>
       <c r="J280" t="n">
-        <v>-9.082800000000001</v>
+        <v>-5.5042</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.8</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3872</v>
+        <v>-0.2409</v>
       </c>
       <c r="J281" t="n">
-        <v>-11.2288</v>
+        <v>-6.9861</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.07</v>
       </c>
       <c r="I282" t="n">
-        <v>0.236</v>
+        <v>0.2337</v>
       </c>
       <c r="J282" t="n">
-        <v>7.08</v>
+        <v>7.011</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.97</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0061</v>
+        <v>-0.0315</v>
       </c>
       <c r="J283" t="n">
-        <v>-0.183</v>
+        <v>-0.945</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.85</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.236</v>
+        <v>-0.1712</v>
       </c>
       <c r="J284" t="n">
-        <v>-7.08</v>
+        <v>-5.136</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.4981</v>
+        <v>-0.3262</v>
       </c>
       <c r="J285" t="n">
-        <v>-14.943</v>
+        <v>-9.786</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.64</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.5659</v>
+        <v>-0.3734</v>
       </c>
       <c r="J286" t="n">
-        <v>-16.977</v>
+        <v>-11.202</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.66</v>
       </c>
       <c r="I287" t="n">
-        <v>1.5061</v>
+        <v>1.3289</v>
       </c>
       <c r="J287" t="n">
-        <v>45.183</v>
+        <v>39.867</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.44</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0747</v>
+        <v>1.0533</v>
       </c>
       <c r="J288" t="n">
-        <v>32.241</v>
+        <v>31.599</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.38</v>
       </c>
       <c r="I289" t="n">
-        <v>0.946</v>
+        <v>0.9559</v>
       </c>
       <c r="J289" t="n">
-        <v>28.38</v>
+        <v>28.677</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.08</v>
       </c>
       <c r="I290" t="n">
-        <v>0.1561</v>
+        <v>0.2328</v>
       </c>
       <c r="J290" t="n">
-        <v>4.683</v>
+        <v>6.984</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.9863</v>
+        <v>-0.9592000000000001</v>
       </c>
       <c r="J291" t="n">
-        <v>-29.589</v>
+        <v>-28.776</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>0.93</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J292" t="n">
-        <v>-1.644</v>
+        <v>-1.8312</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.92</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0885</v>
       </c>
       <c r="J293" t="n">
-        <v>-2.088</v>
+        <v>-2.124</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.84</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.228</v>
+        <v>-0.1769</v>
       </c>
       <c r="J294" t="n">
-        <v>-5.472</v>
+        <v>-4.2456</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.72</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.4417</v>
+        <v>-0.2921</v>
       </c>
       <c r="J295" t="n">
-        <v>-10.6008</v>
+        <v>-7.0104</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.61</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.5955</v>
+        <v>-0.3959</v>
       </c>
       <c r="J296" t="n">
-        <v>-14.292</v>
+        <v>-9.5016</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.59</v>
       </c>
       <c r="I297" t="n">
-        <v>1.3809</v>
+        <v>1.2461</v>
       </c>
       <c r="J297" t="n">
-        <v>33.1416</v>
+        <v>29.9064</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.51</v>
       </c>
       <c r="I298" t="n">
-        <v>1.2246</v>
+        <v>1.1457</v>
       </c>
       <c r="J298" t="n">
-        <v>29.3904</v>
+        <v>27.4968</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.23</v>
       </c>
       <c r="I299" t="n">
-        <v>0.5762</v>
+        <v>0.6253</v>
       </c>
       <c r="J299" t="n">
-        <v>13.8288</v>
+        <v>15.0072</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.21</v>
       </c>
       <c r="I300" t="n">
-        <v>0.5189</v>
+        <v>0.5786</v>
       </c>
       <c r="J300" t="n">
-        <v>12.4536</v>
+        <v>13.8864</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.64</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.0884</v>
+        <v>-1.0751</v>
       </c>
       <c r="J301" t="n">
-        <v>-26.1216</v>
+        <v>-25.8024</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4828/event_4828_evp_summary.xlsx
+++ b/database/event/4828/event_4828_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.679</v>
+        <v>6.7876</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5576</v>
+        <v>0.5666</v>
       </c>
       <c r="D2" t="n">
-        <v>2.3772</v>
+        <v>2.4657</v>
       </c>
       <c r="E2" t="n">
-        <v>6.679</v>
+        <v>6.7876</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0509</v>
+        <v>1.9823</v>
       </c>
       <c r="G2" t="n">
-        <v>4.6281</v>
+        <v>4.8053</v>
       </c>
       <c r="H2" t="n">
-        <v>2.0509</v>
+        <v>1.9823</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1352</v>
+        <v>2.0334</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6281</v>
+        <v>4.8053</v>
       </c>
       <c r="K2" t="n">
         <v>152</v>
@@ -529,7 +529,7 @@
         <v>214</v>
       </c>
       <c r="M2" t="n">
-        <v>6.7633</v>
+        <v>6.838699999999999</v>
       </c>
       <c r="N2" t="n">
         <v>366</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.4517</v>
+        <v>6.3878</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5386</v>
+        <v>0.5333</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2746</v>
+        <v>2.2837</v>
       </c>
       <c r="E3" t="n">
-        <v>6.4517</v>
+        <v>6.3878</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8341</v>
+        <v>2.5535</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6176</v>
+        <v>3.8343</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8634</v>
+        <v>2.8638</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9812</v>
+        <v>2.9376</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6176</v>
+        <v>3.8343</v>
       </c>
       <c r="K3" t="n">
         <v>152</v>
@@ -575,7 +575,7 @@
         <v>214</v>
       </c>
       <c r="M3" t="n">
-        <v>6.5988</v>
+        <v>6.7719</v>
       </c>
       <c r="N3" t="n">
         <v>366</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0316</v>
+        <v>6.2067</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5034999999999999</v>
+        <v>0.5181</v>
       </c>
       <c r="D4" t="n">
-        <v>2.085</v>
+        <v>2.2012</v>
       </c>
       <c r="E4" t="n">
-        <v>6.0316</v>
+        <v>6.2067</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3165</v>
+        <v>2.298</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7151</v>
+        <v>3.9087</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3165</v>
+        <v>2.3046</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4118</v>
+        <v>2.364</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7151</v>
+        <v>3.9087</v>
       </c>
       <c r="K4" t="n">
         <v>152</v>
@@ -621,7 +621,7 @@
         <v>214</v>
       </c>
       <c r="M4" t="n">
-        <v>6.1269</v>
+        <v>6.2727</v>
       </c>
       <c r="N4" t="n">
         <v>366</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8326</v>
+        <v>5.0535</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4034</v>
+        <v>0.4219</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5437</v>
+        <v>1.6763</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8326</v>
+        <v>5.0535</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2304</v>
+        <v>1.1522</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6022</v>
+        <v>3.9013</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2304</v>
+        <v>1.1522</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2304</v>
+        <v>1.1522</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6022</v>
+        <v>3.9013</v>
       </c>
       <c r="K5" t="n">
         <v>107</v>
@@ -667,7 +667,7 @@
         <v>185</v>
       </c>
       <c r="M5" t="n">
-        <v>4.832599999999999</v>
+        <v>5.0535</v>
       </c>
       <c r="N5" t="n">
         <v>292</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7348</v>
+        <v>4.7967</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3953</v>
+        <v>0.4004</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4995</v>
+        <v>1.5594</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7348</v>
+        <v>4.7967</v>
       </c>
       <c r="F6" t="n">
-        <v>3.7158</v>
+        <v>3.6599</v>
       </c>
       <c r="G6" t="n">
-        <v>1.019</v>
+        <v>1.1368</v>
       </c>
       <c r="H6" t="n">
-        <v>7.6059</v>
+        <v>7.1812</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9547</v>
+        <v>3.8778</v>
       </c>
       <c r="J6" t="n">
-        <v>1.019</v>
+        <v>1.1368</v>
       </c>
       <c r="K6" t="n">
         <v>144</v>
@@ -713,7 +713,7 @@
         <v>59</v>
       </c>
       <c r="M6" t="n">
-        <v>4.9737</v>
+        <v>5.0146</v>
       </c>
       <c r="N6" t="n">
         <v>203</v>
@@ -722,139 +722,139 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ropz</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6615</v>
+        <v>3.5792</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3057</v>
+        <v>0.2988</v>
       </c>
       <c r="D7" t="n">
-        <v>1.015</v>
+        <v>1.0051</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6615</v>
+        <v>3.5792</v>
       </c>
       <c r="F7" t="n">
-        <v>3.5631</v>
+        <v>2.8631</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0984</v>
+        <v>0.7161</v>
       </c>
       <c r="H7" t="n">
-        <v>7.0677</v>
+        <v>4.5523</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6749</v>
+        <v>2.4582</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0984</v>
+        <v>0.7161</v>
       </c>
       <c r="K7" t="n">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="L7" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7733</v>
+        <v>3.1743</v>
       </c>
       <c r="N7" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>Snax</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5711</v>
+        <v>3.5771</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2981</v>
+        <v>0.2986</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9742</v>
+        <v>1.0042</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5711</v>
+        <v>3.5771</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9173</v>
+        <v>1.3667</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6538</v>
+        <v>2.2104</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7925</v>
+        <v>1.3667</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4919</v>
+        <v>1.3667</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6538</v>
+        <v>2.2104</v>
       </c>
       <c r="K8" t="n">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="L8" t="n">
-        <v>59</v>
+        <v>185</v>
       </c>
       <c r="M8" t="n">
-        <v>3.1457</v>
+        <v>3.5771</v>
       </c>
       <c r="N8" t="n">
-        <v>203</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Snax</t>
+          <t>ropz</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.528</v>
+        <v>3.5567</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2945</v>
+        <v>0.2969</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9547</v>
+        <v>0.9949</v>
       </c>
       <c r="E9" t="n">
-        <v>3.528</v>
+        <v>3.5567</v>
       </c>
       <c r="F9" t="n">
-        <v>1.4842</v>
+        <v>3.4742</v>
       </c>
       <c r="G9" t="n">
-        <v>2.0438</v>
+        <v>0.0825</v>
       </c>
       <c r="H9" t="n">
-        <v>1.4842</v>
+        <v>6.5686</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4842</v>
+        <v>3.547</v>
       </c>
       <c r="J9" t="n">
-        <v>2.0438</v>
+        <v>0.0825</v>
       </c>
       <c r="K9" t="n">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L9" t="n">
-        <v>185</v>
+        <v>49</v>
       </c>
       <c r="M9" t="n">
-        <v>3.528</v>
+        <v>3.6295</v>
       </c>
       <c r="N9" t="n">
-        <v>292</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0277</v>
+        <v>3.1571</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2528</v>
+        <v>0.2636</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7288</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0277</v>
+        <v>3.1571</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8582</v>
+        <v>1.8022</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1695</v>
+        <v>1.3549</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8582</v>
+        <v>1.8022</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8582</v>
+        <v>1.8022</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1695</v>
+        <v>1.3549</v>
       </c>
       <c r="K10" t="n">
         <v>107</v>
@@ -897,7 +897,7 @@
         <v>185</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0277</v>
+        <v>3.1571</v>
       </c>
       <c r="N10" t="n">
         <v>292</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.6778</v>
+        <v>2.5839</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2235</v>
+        <v>0.2157</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5709</v>
+        <v>0.552</v>
       </c>
       <c r="E11" t="n">
-        <v>2.6778</v>
+        <v>2.5839</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3821</v>
+        <v>2.3025</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2957</v>
+        <v>0.2814</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9066</v>
+        <v>2.7026</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5113</v>
+        <v>1.4594</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2957</v>
+        <v>0.2814</v>
       </c>
       <c r="K11" t="n">
         <v>151</v>
@@ -943,7 +943,7 @@
         <v>49</v>
       </c>
       <c r="M11" t="n">
-        <v>1.807</v>
+        <v>1.7408</v>
       </c>
       <c r="N11" t="n">
         <v>200</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.441</v>
+        <v>2.3941</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2038</v>
+        <v>0.1999</v>
       </c>
       <c r="D12" t="n">
-        <v>0.464</v>
+        <v>0.4656</v>
       </c>
       <c r="E12" t="n">
-        <v>2.441</v>
+        <v>2.3941</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4794</v>
+        <v>1.9489</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0384</v>
+        <v>0.4452</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2495</v>
+        <v>1.9489</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6896</v>
+        <v>1.9489</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.0384</v>
+        <v>0.4452</v>
       </c>
       <c r="K12" t="n">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="L12" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6512</v>
+        <v>2.3941</v>
       </c>
       <c r="N12" t="n">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3824</v>
+        <v>2.3272</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1989</v>
+        <v>0.1943</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4375</v>
+        <v>0.4352</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3824</v>
+        <v>2.3272</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9716</v>
+        <v>2.3784</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4108</v>
+        <v>-0.0512</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9716</v>
+        <v>2.9532</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9716</v>
+        <v>1.5947</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4108</v>
+        <v>-0.0512</v>
       </c>
       <c r="K13" t="n">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="L13" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3824</v>
+        <v>1.5435</v>
       </c>
       <c r="N13" t="n">
-        <v>173</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2039</v>
+        <v>2.199</v>
       </c>
       <c r="C14" t="n">
-        <v>0.184</v>
+        <v>0.1836</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3569</v>
+        <v>0.3768</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2039</v>
+        <v>2.199</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3823</v>
+        <v>1.3029</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8216</v>
+        <v>0.8961</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3823</v>
+        <v>1.3029</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3823</v>
+        <v>1.3029</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8216</v>
+        <v>0.8961</v>
       </c>
       <c r="K14" t="n">
         <v>107</v>
@@ -1081,7 +1081,7 @@
         <v>74</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2039</v>
+        <v>2.199</v>
       </c>
       <c r="N14" t="n">
         <v>181</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.9637</v>
+        <v>1.8638</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1639</v>
+        <v>0.1556</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2485</v>
+        <v>0.2242</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9637</v>
+        <v>1.8638</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9637</v>
+        <v>1.8638</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9637</v>
+        <v>1.8638</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9637</v>
+        <v>1.8638</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.9637</v>
+        <v>1.8638</v>
       </c>
       <c r="N15" t="n">
         <v>133</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.8486</v>
+        <v>1.77</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1543</v>
+        <v>0.1478</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1965</v>
+        <v>0.1815</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8486</v>
+        <v>1.77</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2834</v>
+        <v>2.2208</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4348</v>
+        <v>-0.4508</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5591</v>
+        <v>2.433</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3306</v>
+        <v>1.3138</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4348</v>
+        <v>-0.4508</v>
       </c>
       <c r="K16" t="n">
         <v>144</v>
@@ -1173,7 +1173,7 @@
         <v>59</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8957999999999999</v>
+        <v>0.8630000000000001</v>
       </c>
       <c r="N16" t="n">
         <v>203</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.6351</v>
+        <v>1.743</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1365</v>
+        <v>0.1455</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1002</v>
+        <v>0.1692</v>
       </c>
       <c r="E17" t="n">
-        <v>1.6351</v>
+        <v>1.743</v>
       </c>
       <c r="F17" t="n">
-        <v>1.028</v>
+        <v>1.0479</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6071</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>1.028</v>
+        <v>1.0479</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0703</v>
+        <v>1.0749</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6071</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>152</v>
@@ -1219,7 +1219,7 @@
         <v>214</v>
       </c>
       <c r="M17" t="n">
-        <v>1.6774</v>
+        <v>1.77</v>
       </c>
       <c r="N17" t="n">
         <v>366</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6197</v>
+        <v>1.6595</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1352</v>
+        <v>0.1385</v>
       </c>
       <c r="D18" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.1312</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6197</v>
+        <v>1.6595</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9957</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.624</v>
+        <v>0.7517</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9957</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9957</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.624</v>
+        <v>0.7517</v>
       </c>
       <c r="K18" t="n">
         <v>107</v>
@@ -1265,7 +1265,7 @@
         <v>185</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6197</v>
+        <v>1.6595</v>
       </c>
       <c r="N18" t="n">
         <v>292</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.5382</v>
+        <v>1.4691</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1284</v>
+        <v>0.1226</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0564</v>
+        <v>0.0446</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5382</v>
+        <v>1.4691</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4551</v>
+        <v>1.4012</v>
       </c>
       <c r="G19" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0679</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4551</v>
+        <v>1.4012</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4551</v>
+        <v>1.4012</v>
       </c>
       <c r="J19" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0679</v>
       </c>
       <c r="K19" t="n">
         <v>118</v>
@@ -1311,7 +1311,7 @@
         <v>55</v>
       </c>
       <c r="M19" t="n">
-        <v>1.5382</v>
+        <v>1.4691</v>
       </c>
       <c r="N19" t="n">
         <v>173</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4297</v>
+        <v>1.4129</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1194</v>
+        <v>0.1179</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0074</v>
+        <v>0.019</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4297</v>
+        <v>1.4129</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3928</v>
+        <v>1.3729</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0369</v>
+        <v>0.04</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3928</v>
+        <v>1.3729</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3928</v>
+        <v>1.3729</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0369</v>
+        <v>0.04</v>
       </c>
       <c r="K20" t="n">
         <v>118</v>
@@ -1357,7 +1357,7 @@
         <v>55</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4297</v>
+        <v>1.4129</v>
       </c>
       <c r="N20" t="n">
         <v>173</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.2763</v>
+        <v>1.1894</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1065</v>
+        <v>0.0993</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0618</v>
+        <v>-0.0828</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2763</v>
+        <v>1.1894</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0653</v>
+        <v>0.9893</v>
       </c>
       <c r="G21" t="n">
-        <v>0.211</v>
+        <v>0.2001</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0653</v>
+        <v>0.9893</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0653</v>
+        <v>0.9893</v>
       </c>
       <c r="J21" t="n">
-        <v>0.211</v>
+        <v>0.2001</v>
       </c>
       <c r="K21" t="n">
         <v>107</v>
@@ -1403,7 +1403,7 @@
         <v>74</v>
       </c>
       <c r="M21" t="n">
-        <v>1.2763</v>
+        <v>1.1894</v>
       </c>
       <c r="N21" t="n">
         <v>181</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9123</v>
+        <v>0.9033</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0762</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2262</v>
+        <v>-0.213</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9123</v>
+        <v>0.9033</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2849</v>
+        <v>1.2985</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3726</v>
+        <v>-0.3952</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2849</v>
+        <v>1.2985</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6681</v>
+        <v>0.7012</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3726</v>
+        <v>-0.3952</v>
       </c>
       <c r="K22" t="n">
         <v>144</v>
@@ -1449,7 +1449,7 @@
         <v>59</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2955</v>
+        <v>0.306</v>
       </c>
       <c r="N22" t="n">
         <v>203</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6659</v>
+        <v>0.5723</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0556</v>
+        <v>0.0478</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3374</v>
+        <v>-0.3637</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6659</v>
+        <v>0.5723</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6659</v>
+        <v>0.5723</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6659</v>
+        <v>0.5723</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6659</v>
+        <v>0.5723</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6659</v>
+        <v>0.5723</v>
       </c>
       <c r="N23" t="n">
         <v>106</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6102</v>
+        <v>0.5031</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0509</v>
+        <v>0.042</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3625</v>
+        <v>-0.3952</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6102</v>
+        <v>0.5031</v>
       </c>
       <c r="F24" t="n">
-        <v>1.218</v>
+        <v>1.1311</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6078</v>
+        <v>-0.628</v>
       </c>
       <c r="H24" t="n">
-        <v>1.218</v>
+        <v>1.1311</v>
       </c>
       <c r="I24" t="n">
-        <v>1.218</v>
+        <v>1.1311</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6078</v>
+        <v>-0.628</v>
       </c>
       <c r="K24" t="n">
         <v>118</v>
@@ -1541,7 +1541,7 @@
         <v>55</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6102</v>
+        <v>0.5031</v>
       </c>
       <c r="N24" t="n">
         <v>173</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.4981</v>
       </c>
       <c r="C25" t="n">
-        <v>0.049</v>
+        <v>0.0416</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3729</v>
+        <v>-0.3975</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.4981</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2786</v>
+        <v>1.2117</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6914</v>
+        <v>-0.7136</v>
       </c>
       <c r="H25" t="n">
-        <v>1.2786</v>
+        <v>1.2117</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2786</v>
+        <v>1.2117</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6914</v>
+        <v>-0.7136</v>
       </c>
       <c r="K25" t="n">
         <v>107</v>
@@ -1587,7 +1587,7 @@
         <v>74</v>
       </c>
       <c r="M25" t="n">
-        <v>0.5871999999999999</v>
+        <v>0.4981</v>
       </c>
       <c r="N25" t="n">
         <v>181</v>
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4045</v>
+        <v>0.3494</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0338</v>
+        <v>0.0292</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4554</v>
+        <v>-0.4651</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4045</v>
+        <v>0.3494</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4045</v>
+        <v>0.3494</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4045</v>
+        <v>0.3494</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4045</v>
+        <v>0.3494</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.4045</v>
+        <v>0.3494</v>
       </c>
       <c r="N26" t="n">
         <v>106</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.3025</v>
+        <v>0.344</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0253</v>
+        <v>0.0287</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-0.4676</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3025</v>
+        <v>0.344</v>
       </c>
       <c r="F27" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0936</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2363</v>
+        <v>0.2504</v>
       </c>
       <c r="H27" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0936</v>
       </c>
       <c r="I27" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.0936</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2363</v>
+        <v>0.2504</v>
       </c>
       <c r="K27" t="n">
         <v>118</v>
@@ -1679,7 +1679,7 @@
         <v>55</v>
       </c>
       <c r="M27" t="n">
-        <v>0.3025</v>
+        <v>0.344</v>
       </c>
       <c r="N27" t="n">
         <v>173</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.054</v>
+        <v>-0.1393</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0045</v>
+        <v>-0.0116</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6624</v>
+        <v>-0.6876</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.054</v>
+        <v>-0.1393</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.054</v>
+        <v>-0.1393</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.054</v>
+        <v>-0.1393</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.054</v>
+        <v>-0.1393</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.054</v>
+        <v>-0.1393</v>
       </c>
       <c r="N28" t="n">
         <v>106</v>
@@ -1734,93 +1734,93 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>kaper</t>
+          <t>fredi</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.2258</v>
+        <v>-0.3019</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0188</v>
+        <v>-0.0252</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.74</v>
+        <v>-0.7616000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2258</v>
+        <v>-0.3019</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5527</v>
+        <v>-0.3019</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.7785</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5527</v>
+        <v>-0.3019</v>
       </c>
       <c r="I29" t="n">
-        <v>0.5527</v>
+        <v>-0.3019</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.7785</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L29" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2258</v>
+        <v>-0.3019</v>
       </c>
       <c r="N29" t="n">
-        <v>181</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>fredi</t>
+          <t>kaper</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2676</v>
+        <v>-0.3511</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0223</v>
+        <v>-0.0293</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7588</v>
+        <v>-0.784</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2676</v>
+        <v>-0.3511</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.2676</v>
+        <v>0.4734</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.8245</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.2676</v>
+        <v>0.4734</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2676</v>
+        <v>0.4734</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.8245</v>
       </c>
       <c r="K30" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2676</v>
+        <v>-0.3511</v>
       </c>
       <c r="N30" t="n">
-        <v>106</v>
+        <v>181</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.372</v>
+        <v>-0.4438</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0311</v>
+        <v>-0.037</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.806</v>
+        <v>-0.8262</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.372</v>
+        <v>-0.4438</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.372</v>
+        <v>-0.4438</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.372</v>
+        <v>-0.4438</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.372</v>
+        <v>-0.4438</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.372</v>
+        <v>-0.4438</v>
       </c>
       <c r="N31" t="n">
         <v>133</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5917</v>
+        <v>-0.5303</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0494</v>
+        <v>-0.0443</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.9051</v>
+        <v>-0.8656</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5917</v>
+        <v>-0.5303</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.9849</v>
+        <v>-0.9639</v>
       </c>
       <c r="G32" t="n">
-        <v>0.3932</v>
+        <v>0.4336</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.9849</v>
+        <v>-0.9639</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5121</v>
+        <v>-0.5205</v>
       </c>
       <c r="J32" t="n">
-        <v>0.3932</v>
+        <v>0.4336</v>
       </c>
       <c r="K32" t="n">
         <v>144</v>
@@ -1909,7 +1909,7 @@
         <v>59</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1189</v>
+        <v>-0.08689999999999998</v>
       </c>
       <c r="N32" t="n">
         <v>203</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7589</v>
+        <v>-0.8003</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0634</v>
+        <v>-0.0668</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9806</v>
+        <v>-0.9885</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7589</v>
+        <v>-0.8003</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7589</v>
+        <v>-0.8003</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7589</v>
+        <v>-0.8003</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7589</v>
+        <v>-0.8003</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7589</v>
+        <v>-0.8003</v>
       </c>
       <c r="N33" t="n">
         <v>133</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.0282</v>
+        <v>-1.052</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0858</v>
+        <v>-0.0878</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.1022</v>
+        <v>-1.1031</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.0282</v>
+        <v>-1.052</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.4903</v>
+        <v>-0.498</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.5379</v>
+        <v>-0.554</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4903</v>
+        <v>-0.498</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4903</v>
+        <v>-0.498</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.5379</v>
+        <v>-0.554</v>
       </c>
       <c r="K34" t="n">
         <v>107</v>
@@ -2001,7 +2001,7 @@
         <v>74</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.0282</v>
+        <v>-1.052</v>
       </c>
       <c r="N34" t="n">
         <v>181</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.041</v>
+        <v>-1.1131</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.0929</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.108</v>
+        <v>-1.1309</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.041</v>
+        <v>-1.1131</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.041</v>
+        <v>-1.1131</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.041</v>
+        <v>-1.1131</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.041</v>
+        <v>-1.1131</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.041</v>
+        <v>-1.1131</v>
       </c>
       <c r="N35" t="n">
         <v>133</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0914</v>
+        <v>-1.1335</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0911</v>
+        <v>-0.0946</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1307</v>
+        <v>-1.1402</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0914</v>
+        <v>-1.1335</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.0914</v>
+        <v>-1.1335</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.0914</v>
+        <v>-1.1335</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.0914</v>
+        <v>-1.1335</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0914</v>
+        <v>-1.1335</v>
       </c>
       <c r="N36" t="n">
         <v>133</v>
@@ -2102,47 +2102,47 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BLUEE</t>
+          <t>phr</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3694</v>
+        <v>-1.2515</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1143</v>
+        <v>-0.1045</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.2562</v>
+        <v>-1.1939</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3694</v>
+        <v>-1.2515</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.3694</v>
+        <v>-0.6403</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>-0.6112</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.3694</v>
+        <v>-0.6403</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.3694</v>
+        <v>-0.6403</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>-0.6112</v>
       </c>
       <c r="K37" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3694</v>
+        <v>-1.2515</v>
       </c>
       <c r="N37" t="n">
-        <v>106</v>
+        <v>292</v>
       </c>
     </row>
     <row r="38">
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3754</v>
+        <v>-1.3251</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1148</v>
+        <v>-0.1106</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2589</v>
+        <v>-1.2274</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3754</v>
+        <v>-1.3251</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.6172</v>
+        <v>-0.5404</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.7582</v>
+        <v>-0.7847</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.6172</v>
+        <v>-0.5404</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3209</v>
+        <v>-0.2918</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7582</v>
+        <v>-0.7847</v>
       </c>
       <c r="K38" t="n">
         <v>151</v>
@@ -2185,7 +2185,7 @@
         <v>49</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0791</v>
+        <v>-1.0765</v>
       </c>
       <c r="N38" t="n">
         <v>200</v>
@@ -2194,47 +2194,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>phr</t>
+          <t>BLUEE</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4063</v>
+        <v>-1.4192</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1174</v>
+        <v>-0.1185</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2729</v>
+        <v>-1.2703</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4063</v>
+        <v>-1.4192</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.6313</v>
+        <v>-1.4192</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.775</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.6313</v>
+        <v>-1.4192</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6313</v>
+        <v>-1.4192</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.775</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L39" t="n">
-        <v>185</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4063</v>
+        <v>-1.4192</v>
       </c>
       <c r="N39" t="n">
-        <v>292</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.4619</v>
+        <v>-2.1255</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2055</v>
+        <v>-0.1774</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.7494</v>
+        <v>-1.5918</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.4619</v>
+        <v>-2.1255</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.2906</v>
+        <v>-2.0004</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.1713</v>
+        <v>-0.1251</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.2906</v>
+        <v>-2.0004</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.191</v>
+        <v>-1.0802</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1713</v>
+        <v>-0.1251</v>
       </c>
       <c r="K40" t="n">
         <v>151</v>
@@ -2277,7 +2277,7 @@
         <v>49</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3623</v>
+        <v>-1.2053</v>
       </c>
       <c r="N40" t="n">
         <v>200</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.3129</v>
+        <v>-4.1019</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.36</v>
+        <v>-0.3424</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.5851</v>
+        <v>-2.4915</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.3129</v>
+        <v>-4.1019</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.444</v>
+        <v>-2.3034</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.8689</v>
+        <v>-1.7985</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.444</v>
+        <v>-2.3034</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.5445</v>
+        <v>-2.3628</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.8689</v>
+        <v>-1.7985</v>
       </c>
       <c r="K41" t="n">
         <v>152</v>
@@ -2323,7 +2323,7 @@
         <v>214</v>
       </c>
       <c r="M41" t="n">
-        <v>-4.4134</v>
+        <v>-4.1613</v>
       </c>
       <c r="N41" t="n">
         <v>366</v>
@@ -2429,10 +2429,10 @@
         <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1666</v>
+        <v>0.1809</v>
       </c>
       <c r="J2" t="n">
-        <v>4.6648</v>
+        <v>5.0652</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.07</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1233</v>
+        <v>0.1368</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4524</v>
+        <v>3.8304</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1084</v>
+        <v>0.1214</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0352</v>
+        <v>3.3992</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.1054</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6096</v>
+        <v>2.9512</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0212</v>
+        <v>0.0281</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5936</v>
+        <v>0.7868000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4707</v>
+        <v>0.4691</v>
       </c>
       <c r="J7" t="n">
-        <v>13.1796</v>
+        <v>13.1348</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.29</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4445</v>
+        <v>0.4447</v>
       </c>
       <c r="J8" t="n">
-        <v>12.446</v>
+        <v>12.4516</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3236</v>
+        <v>0.3307</v>
       </c>
       <c r="J9" t="n">
-        <v>9.0608</v>
+        <v>9.259600000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2351</v>
+        <v>-0.2472</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.5828</v>
+        <v>-6.9216</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.66</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3795</v>
+        <v>-0.3885</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.626</v>
+        <v>-10.878</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.24</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5065</v>
+        <v>0.4972</v>
       </c>
       <c r="J12" t="n">
-        <v>13.169</v>
+        <v>12.9272</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.18</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3975</v>
+        <v>0.3962</v>
       </c>
       <c r="J13" t="n">
-        <v>10.335</v>
+        <v>10.3012</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2018</v>
+        <v>0.2102</v>
       </c>
       <c r="J14" t="n">
-        <v>5.2468</v>
+        <v>5.4652</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.93</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1015</v>
+        <v>-0.1127</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.639</v>
+        <v>-2.9302</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.64</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3939</v>
+        <v>-0.4031</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.2414</v>
+        <v>-10.4806</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.51</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1976</v>
+        <v>1.2101</v>
       </c>
       <c r="J17" t="n">
-        <v>31.1376</v>
+        <v>31.4626</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.21</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.5939</v>
       </c>
       <c r="J18" t="n">
-        <v>16.211</v>
+        <v>15.4414</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.93</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2755</v>
+        <v>-0.2703</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.163</v>
+        <v>-7.0278</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.87</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.45</v>
+        <v>-0.4307</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.7</v>
+        <v>-11.1982</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.76</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7401</v>
+        <v>-0.6895</v>
       </c>
       <c r="J21" t="n">
-        <v>-19.2426</v>
+        <v>-17.927</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.14</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3533</v>
+        <v>0.3482</v>
       </c>
       <c r="J22" t="n">
-        <v>9.539099999999999</v>
+        <v>9.401400000000001</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.03</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1116</v>
+        <v>0.1143</v>
       </c>
       <c r="J23" t="n">
-        <v>3.0132</v>
+        <v>3.0861</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.95</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0688</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8576</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.87</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1573</v>
+        <v>-0.1728</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.2471</v>
+        <v>-4.6656</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.59</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4291</v>
+        <v>-0.4387</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.5857</v>
+        <v>-11.8449</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.46</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0976</v>
+        <v>1.0738</v>
       </c>
       <c r="J27" t="n">
-        <v>29.6352</v>
+        <v>28.9926</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.44</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0714</v>
+        <v>1.0357</v>
       </c>
       <c r="J28" t="n">
-        <v>28.9278</v>
+        <v>27.9639</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.22</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6137</v>
+        <v>0.592</v>
       </c>
       <c r="J29" t="n">
-        <v>16.5699</v>
+        <v>15.984</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3058</v>
+        <v>-0.2914</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.256600000000001</v>
+        <v>-7.8678</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6931</v>
+        <v>-0.6428</v>
       </c>
       <c r="J31" t="n">
-        <v>-18.7137</v>
+        <v>-17.3556</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.3</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4911</v>
+        <v>0.5471</v>
       </c>
       <c r="J32" t="n">
-        <v>14.733</v>
+        <v>16.413</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.27</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4607</v>
+        <v>0.5121</v>
       </c>
       <c r="J33" t="n">
-        <v>13.821</v>
+        <v>15.363</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.21</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3983</v>
+        <v>0.4375</v>
       </c>
       <c r="J34" t="n">
-        <v>11.949</v>
+        <v>13.125</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.79</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2542</v>
+        <v>-0.2664</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.626</v>
+        <v>-7.992</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.66</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3787</v>
+        <v>-0.3879</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.361</v>
+        <v>-11.637</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.17</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4405</v>
+        <v>0.4825</v>
       </c>
       <c r="J37" t="n">
-        <v>13.215</v>
+        <v>14.475</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.13</v>
       </c>
       <c r="I38" t="n">
-        <v>0.3785</v>
+        <v>0.4024</v>
       </c>
       <c r="J38" t="n">
-        <v>11.355</v>
+        <v>12.072</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.09</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2995</v>
+        <v>0.3013</v>
       </c>
       <c r="J39" t="n">
-        <v>8.984999999999999</v>
+        <v>9.039</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.04</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1499</v>
+        <v>0.159</v>
       </c>
       <c r="J40" t="n">
-        <v>4.497</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2493</v>
+        <v>-0.2445</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.479</v>
+        <v>-7.335</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.34</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5279</v>
+        <v>0.5897</v>
       </c>
       <c r="J42" t="n">
-        <v>15.3091</v>
+        <v>17.1013</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.08</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1931</v>
+        <v>0.204</v>
       </c>
       <c r="J43" t="n">
-        <v>5.5999</v>
+        <v>5.916</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0051</v>
+        <v>-0.0039</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.1479</v>
+        <v>-0.1131</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0561</v>
+        <v>-0.0629</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.6269</v>
+        <v>-1.8241</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.92</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1184</v>
+        <v>-0.1288</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.4336</v>
+        <v>-3.7352</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.51</v>
       </c>
       <c r="I47" t="n">
-        <v>0.902</v>
+        <v>0.9897</v>
       </c>
       <c r="J47" t="n">
-        <v>26.158</v>
+        <v>28.7013</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.22</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5061</v>
+        <v>0.5583</v>
       </c>
       <c r="J48" t="n">
-        <v>14.6769</v>
+        <v>16.1907</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3185</v>
+        <v>0.322</v>
       </c>
       <c r="J49" t="n">
-        <v>9.236499999999999</v>
+        <v>9.337999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.04</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1386</v>
+        <v>0.1512</v>
       </c>
       <c r="J50" t="n">
-        <v>4.0194</v>
+        <v>4.3848</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.74</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8079</v>
+        <v>-0.746</v>
       </c>
       <c r="J51" t="n">
-        <v>-23.4291</v>
+        <v>-21.634</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.04</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2329</v>
+        <v>0.2103</v>
       </c>
       <c r="J52" t="n">
-        <v>4.4251</v>
+        <v>3.9957</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.82</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1812</v>
+        <v>-0.2033</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.4428</v>
+        <v>-3.8627</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.7</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2983</v>
+        <v>-0.3182</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.6677</v>
+        <v>-6.0458</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.63</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3628</v>
+        <v>-0.3804</v>
       </c>
       <c r="J55" t="n">
-        <v>-6.8932</v>
+        <v>-7.2276</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.36</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6147</v>
+        <v>-0.6166</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.6793</v>
+        <v>-11.7154</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.91</v>
       </c>
       <c r="I57" t="n">
-        <v>1.3017</v>
+        <v>1.427</v>
       </c>
       <c r="J57" t="n">
-        <v>24.7323</v>
+        <v>27.113</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.54</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8728</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>16.5832</v>
+        <v>18.4547</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.53</v>
       </c>
       <c r="I59" t="n">
-        <v>0.8609</v>
+        <v>0.9584</v>
       </c>
       <c r="J59" t="n">
-        <v>16.3571</v>
+        <v>18.2096</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.31</v>
       </c>
       <c r="I60" t="n">
-        <v>0.591</v>
+        <v>0.6626</v>
       </c>
       <c r="J60" t="n">
-        <v>11.229</v>
+        <v>12.5894</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.92</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3979</v>
+        <v>-0.3632</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.5601</v>
+        <v>-6.9008</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.25</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4434</v>
+        <v>0.4915</v>
       </c>
       <c r="J62" t="n">
-        <v>13.302</v>
+        <v>14.745</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.12</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2796</v>
+        <v>0.2858</v>
       </c>
       <c r="J63" t="n">
-        <v>8.388</v>
+        <v>8.574</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.11</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2599</v>
+        <v>0.267</v>
       </c>
       <c r="J64" t="n">
-        <v>7.797</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.02</v>
       </c>
       <c r="I65" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0711</v>
       </c>
       <c r="J65" t="n">
-        <v>1.884</v>
+        <v>2.133</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.64</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3954</v>
+        <v>-0.4043</v>
       </c>
       <c r="J66" t="n">
-        <v>-11.862</v>
+        <v>-12.129</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.18</v>
       </c>
       <c r="I67" t="n">
-        <v>0.4646</v>
+        <v>0.5074</v>
       </c>
       <c r="J67" t="n">
-        <v>13.938</v>
+        <v>15.222</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.08</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2806</v>
+        <v>0.2811</v>
       </c>
       <c r="J68" t="n">
-        <v>8.417999999999999</v>
+        <v>8.433</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.006</v>
+        <v>-0.0041</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.18</v>
+        <v>-0.123</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.96</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1726</v>
+        <v>-0.1744</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.178</v>
+        <v>-5.232</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2377</v>
+        <v>-0.2364</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.131</v>
+        <v>-7.092</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.96</v>
       </c>
       <c r="I72" t="n">
-        <v>1.3515</v>
+        <v>1.4804</v>
       </c>
       <c r="J72" t="n">
-        <v>28.3815</v>
+        <v>31.0884</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.42</v>
       </c>
       <c r="I73" t="n">
-        <v>0.7281</v>
+        <v>0.8141</v>
       </c>
       <c r="J73" t="n">
-        <v>15.2901</v>
+        <v>17.0961</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.35</v>
       </c>
       <c r="I74" t="n">
-        <v>0.6401</v>
+        <v>0.7175</v>
       </c>
       <c r="J74" t="n">
-        <v>13.4421</v>
+        <v>15.0675</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.34</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6271</v>
+        <v>0.7032</v>
       </c>
       <c r="J75" t="n">
-        <v>13.1691</v>
+        <v>14.7672</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.28</v>
       </c>
       <c r="I76" t="n">
-        <v>0.5474</v>
+        <v>0.6151</v>
       </c>
       <c r="J76" t="n">
-        <v>11.4954</v>
+        <v>12.9171</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.83</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.1713</v>
+        <v>-0.1935</v>
       </c>
       <c r="J77" t="n">
-        <v>-3.5973</v>
+        <v>-4.0635</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.83</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1713</v>
+        <v>-0.1935</v>
       </c>
       <c r="J78" t="n">
-        <v>-3.5973</v>
+        <v>-4.0635</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.1926</v>
+        <v>-0.2144</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.0446</v>
+        <v>-4.5024</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.63</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3635</v>
+        <v>-0.3809</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.6335</v>
+        <v>-7.9989</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.47</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.513</v>
+        <v>-0.522</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.773</v>
+        <v>-10.962</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.05</v>
       </c>
       <c r="I82" t="n">
-        <v>0.128</v>
+        <v>0.1317</v>
       </c>
       <c r="J82" t="n">
-        <v>3.84</v>
+        <v>3.951</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.96</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0535</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.605</v>
+        <v>-1.953</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.93</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0907</v>
+        <v>-0.1044</v>
       </c>
       <c r="J84" t="n">
-        <v>-2.721</v>
+        <v>-3.132</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2064</v>
+        <v>-0.2227</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.192</v>
+        <v>-6.681</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3045</v>
+        <v>-0.3192</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.135</v>
+        <v>-9.576000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.76</v>
       </c>
       <c r="I87" t="n">
-        <v>0.68</v>
+        <v>0.7772</v>
       </c>
       <c r="J87" t="n">
-        <v>20.4</v>
+        <v>23.316</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.08</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1309</v>
+        <v>0.1467</v>
       </c>
       <c r="J88" t="n">
-        <v>3.927</v>
+        <v>4.401</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.05</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0848</v>
+        <v>0.0992</v>
       </c>
       <c r="J89" t="n">
-        <v>2.544</v>
+        <v>2.976</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0122</v>
+        <v>-0.0094</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.366</v>
+        <v>-0.282</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.78</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2733</v>
+        <v>-0.2834</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.199</v>
+        <v>-8.502000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.48</v>
       </c>
       <c r="I92" t="n">
-        <v>0.849</v>
+        <v>0.9354</v>
       </c>
       <c r="J92" t="n">
-        <v>19.527</v>
+        <v>21.5142</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.29</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5958</v>
+        <v>0.6601</v>
       </c>
       <c r="J93" t="n">
-        <v>13.7034</v>
+        <v>15.1823</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3328</v>
+        <v>0.3404</v>
       </c>
       <c r="J94" t="n">
-        <v>7.6544</v>
+        <v>7.8292</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.02</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0544</v>
+        <v>0.0725</v>
       </c>
       <c r="J95" t="n">
-        <v>1.2512</v>
+        <v>1.6675</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.96</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2099</v>
+        <v>-0.2004</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.8277</v>
+        <v>-4.6092</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.13</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3342</v>
+        <v>0.3333</v>
       </c>
       <c r="J97" t="n">
-        <v>7.6866</v>
+        <v>7.6659</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.11</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2975</v>
+        <v>0.2944</v>
       </c>
       <c r="J98" t="n">
-        <v>6.8425</v>
+        <v>6.7712</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.86</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1662</v>
+        <v>-0.1822</v>
       </c>
       <c r="J99" t="n">
-        <v>-3.8226</v>
+        <v>-4.1906</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.72</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3053</v>
+        <v>-0.3198</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.0219</v>
+        <v>-7.3554</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3339</v>
+        <v>-0.3476</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.6797</v>
+        <v>-7.9948</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.77</v>
       </c>
       <c r="I102" t="n">
-        <v>1.1962</v>
+        <v>1.3068</v>
       </c>
       <c r="J102" t="n">
-        <v>29.905</v>
+        <v>32.67</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.46</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8105</v>
+        <v>0.8965</v>
       </c>
       <c r="J103" t="n">
-        <v>20.2625</v>
+        <v>22.4125</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.2</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4651</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="J104" t="n">
-        <v>11.6275</v>
+        <v>12.89</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.1459</v>
+        <v>0.165</v>
       </c>
       <c r="J105" t="n">
-        <v>3.6475</v>
+        <v>4.125</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.65</v>
       </c>
       <c r="I106" t="n">
-        <v>-1.0496</v>
+        <v>-0.9527</v>
       </c>
       <c r="J106" t="n">
-        <v>-26.24</v>
+        <v>-23.8175</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.19</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4128</v>
+        <v>0.4467</v>
       </c>
       <c r="J107" t="n">
-        <v>10.32</v>
+        <v>11.1675</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.08</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2424</v>
+        <v>0.2397</v>
       </c>
       <c r="J108" t="n">
-        <v>6.06</v>
+        <v>5.9925</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.88</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1436</v>
+        <v>-0.1597</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.59</v>
+        <v>-3.9925</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.7</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.3213</v>
+        <v>-0.336</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.032500000000001</v>
+        <v>-8.4</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.54</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4705</v>
+        <v>-0.4787</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.7625</v>
+        <v>-11.9675</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.28</v>
       </c>
       <c r="I112" t="n">
-        <v>0.608</v>
+        <v>0.6676</v>
       </c>
       <c r="J112" t="n">
-        <v>18.24</v>
+        <v>20.028</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.08</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2756</v>
+        <v>0.2777</v>
       </c>
       <c r="J113" t="n">
-        <v>8.268000000000001</v>
+        <v>8.331</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.05</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1861</v>
+        <v>0.1928</v>
       </c>
       <c r="J114" t="n">
-        <v>5.583</v>
+        <v>5.784</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.03</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1205</v>
+        <v>0.129</v>
       </c>
       <c r="J115" t="n">
-        <v>3.615</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.82</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.584</v>
+        <v>-0.5515</v>
       </c>
       <c r="J116" t="n">
-        <v>-17.52</v>
+        <v>-16.545</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.19</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3799</v>
+        <v>0.4101</v>
       </c>
       <c r="J117" t="n">
-        <v>11.397</v>
+        <v>12.303</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.17</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3582</v>
+        <v>0.376</v>
       </c>
       <c r="J118" t="n">
-        <v>10.746</v>
+        <v>11.28</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.002</v>
+        <v>-0.0015</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.06</v>
+        <v>-0.045</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.9</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1373</v>
+        <v>-0.1493</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.119</v>
+        <v>-4.479</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.88</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1593</v>
+        <v>-0.1718</v>
       </c>
       <c r="J121" t="n">
-        <v>-4.779</v>
+        <v>-5.154</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.14</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4172</v>
+        <v>0.3953</v>
       </c>
       <c r="J122" t="n">
-        <v>10.43</v>
+        <v>9.8825</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0722</v>
+        <v>-0.0901</v>
       </c>
       <c r="J123" t="n">
-        <v>-1.805</v>
+        <v>-2.2525</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.66</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.346</v>
+        <v>-0.3622</v>
       </c>
       <c r="J124" t="n">
-        <v>-8.65</v>
+        <v>-9.055</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.64</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3649</v>
+        <v>-0.3803</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.1225</v>
+        <v>-9.5075</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.55</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.449</v>
+        <v>-0.4603</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.225</v>
+        <v>-11.5075</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.58</v>
       </c>
       <c r="I127" t="n">
-        <v>1.2255</v>
+        <v>1.1973</v>
       </c>
       <c r="J127" t="n">
-        <v>30.6375</v>
+        <v>29.9325</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.52</v>
       </c>
       <c r="I128" t="n">
-        <v>1.1509</v>
+        <v>1.1174</v>
       </c>
       <c r="J128" t="n">
-        <v>28.7725</v>
+        <v>27.935</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.16</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4476</v>
+        <v>0.4465</v>
       </c>
       <c r="J129" t="n">
-        <v>11.19</v>
+        <v>11.1625</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.05</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1353</v>
+        <v>0.1576</v>
       </c>
       <c r="J130" t="n">
-        <v>3.3825</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.04</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1022</v>
+        <v>0.1259</v>
       </c>
       <c r="J131" t="n">
-        <v>2.555</v>
+        <v>3.1475</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.11</v>
       </c>
       <c r="I132" t="n">
-        <v>0.312</v>
+        <v>0.3051</v>
       </c>
       <c r="J132" t="n">
-        <v>8.736000000000001</v>
+        <v>8.5428</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.93</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.0868</v>
+        <v>-0.1015</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.4304</v>
+        <v>-2.842</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.87</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1529</v>
+        <v>-0.1695</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.2812</v>
+        <v>-4.746</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.77</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2521</v>
+        <v>-0.2688</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.0588</v>
+        <v>-7.5264</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.65</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.367</v>
+        <v>-0.3803</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.276</v>
+        <v>-10.6484</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.39</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9794</v>
+        <v>0.9232</v>
       </c>
       <c r="J137" t="n">
-        <v>27.4232</v>
+        <v>25.8496</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.34</v>
       </c>
       <c r="I138" t="n">
-        <v>0.8756</v>
+        <v>0.8266</v>
       </c>
       <c r="J138" t="n">
-        <v>24.5168</v>
+        <v>23.1448</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.27</v>
       </c>
       <c r="I139" t="n">
-        <v>0.7169</v>
+        <v>0.6868</v>
       </c>
       <c r="J139" t="n">
-        <v>20.0732</v>
+        <v>19.2304</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.18</v>
       </c>
       <c r="I140" t="n">
-        <v>0.5064</v>
+        <v>0.4978</v>
       </c>
       <c r="J140" t="n">
-        <v>14.1792</v>
+        <v>13.9384</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.98</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1527</v>
+        <v>-0.1404</v>
       </c>
       <c r="J141" t="n">
-        <v>-4.2756</v>
+        <v>-3.9312</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.15</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4876</v>
+        <v>0.4683</v>
       </c>
       <c r="J142" t="n">
-        <v>20.4792</v>
+        <v>19.6686</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.01</v>
       </c>
       <c r="I143" t="n">
-        <v>0.053</v>
+        <v>0.0585</v>
       </c>
       <c r="J143" t="n">
-        <v>2.226</v>
+        <v>2.457</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.01</v>
       </c>
       <c r="I144" t="n">
-        <v>0.053</v>
+        <v>0.0585</v>
       </c>
       <c r="J144" t="n">
-        <v>2.226</v>
+        <v>2.457</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.96</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1648</v>
+        <v>-0.1691</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.9216</v>
+        <v>-7.1022</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.88</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.4063</v>
+        <v>-0.3944</v>
       </c>
       <c r="J146" t="n">
-        <v>-17.0646</v>
+        <v>-16.5648</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.16</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3479</v>
+        <v>0.3524</v>
       </c>
       <c r="J147" t="n">
-        <v>14.6118</v>
+        <v>14.8008</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.2333</v>
+        <v>0.243</v>
       </c>
       <c r="J148" t="n">
-        <v>9.7986</v>
+        <v>10.206</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.09</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2133</v>
+        <v>0.2237</v>
       </c>
       <c r="J149" t="n">
-        <v>8.958600000000001</v>
+        <v>9.3954</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.02</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0578</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="J150" t="n">
-        <v>2.4276</v>
+        <v>2.8392</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.1041</v>
       </c>
       <c r="J151" t="n">
-        <v>-3.9774</v>
+        <v>-4.3722</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.58</v>
       </c>
       <c r="I152" t="n">
-        <v>1.214</v>
+        <v>1.1872</v>
       </c>
       <c r="J152" t="n">
-        <v>26.708</v>
+        <v>26.1184</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.49</v>
       </c>
       <c r="I153" t="n">
-        <v>1.1033</v>
+        <v>1.068</v>
       </c>
       <c r="J153" t="n">
-        <v>24.2726</v>
+        <v>23.496</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.31</v>
       </c>
       <c r="I154" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.7562</v>
       </c>
       <c r="J154" t="n">
-        <v>17.4196</v>
+        <v>16.6364</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.19</v>
       </c>
       <c r="I155" t="n">
-        <v>0.5117</v>
+        <v>0.5067</v>
       </c>
       <c r="J155" t="n">
-        <v>11.2574</v>
+        <v>11.1474</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.05</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1227</v>
+        <v>0.1488</v>
       </c>
       <c r="J156" t="n">
-        <v>2.6994</v>
+        <v>3.2736</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.13</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3639</v>
+        <v>0.3519</v>
       </c>
       <c r="J157" t="n">
-        <v>8.005800000000001</v>
+        <v>7.7418</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.87</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1508</v>
+        <v>-0.1679</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.3176</v>
+        <v>-3.6938</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.85</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1712</v>
+        <v>-0.1886</v>
       </c>
       <c r="J159" t="n">
-        <v>-3.7664</v>
+        <v>-4.1492</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.76</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.259</v>
+        <v>-0.2762</v>
       </c>
       <c r="J160" t="n">
-        <v>-5.698</v>
+        <v>-6.0764</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.61</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4015</v>
+        <v>-0.4138</v>
       </c>
       <c r="J161" t="n">
-        <v>-8.833</v>
+        <v>-9.1036</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.65</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2813</v>
+        <v>1.2623</v>
       </c>
       <c r="J162" t="n">
-        <v>29.4699</v>
+        <v>29.0329</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.48</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0784</v>
+        <v>1.0426</v>
       </c>
       <c r="J163" t="n">
-        <v>24.8032</v>
+        <v>23.9798</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.43</v>
       </c>
       <c r="I164" t="n">
-        <v>1.0132</v>
+        <v>0.9664</v>
       </c>
       <c r="J164" t="n">
-        <v>23.3036</v>
+        <v>22.2272</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.28</v>
       </c>
       <c r="I165" t="n">
-        <v>0.708</v>
+        <v>0.6854</v>
       </c>
       <c r="J165" t="n">
-        <v>16.284</v>
+        <v>15.7642</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.22</v>
       </c>
       <c r="I166" t="n">
-        <v>0.5665</v>
+        <v>0.5596</v>
       </c>
       <c r="J166" t="n">
-        <v>13.0295</v>
+        <v>12.8708</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.11</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3817</v>
+        <v>0.3566</v>
       </c>
       <c r="J167" t="n">
-        <v>8.7791</v>
+        <v>8.2018</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.88</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1213</v>
+        <v>-0.1425</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.7899</v>
+        <v>-3.2775</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.66</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3391</v>
+        <v>-0.3569</v>
       </c>
       <c r="J169" t="n">
-        <v>-7.7993</v>
+        <v>-8.2087</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.54</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4514</v>
+        <v>-0.4637</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.3822</v>
+        <v>-10.6651</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.5</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4887</v>
+        <v>-0.4987</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.2401</v>
+        <v>-11.4701</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.32</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8555</v>
+        <v>0.8044</v>
       </c>
       <c r="J172" t="n">
-        <v>25.665</v>
+        <v>24.132</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.23</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6424</v>
+        <v>0.6167</v>
       </c>
       <c r="J173" t="n">
-        <v>19.272</v>
+        <v>18.501</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.18</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5201</v>
+        <v>0.5071</v>
       </c>
       <c r="J174" t="n">
-        <v>15.603</v>
+        <v>15.213</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.15</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4458</v>
+        <v>0.4395</v>
       </c>
       <c r="J175" t="n">
-        <v>13.374</v>
+        <v>13.185</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.87</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4757</v>
+        <v>-0.4488</v>
       </c>
       <c r="J176" t="n">
-        <v>-14.271</v>
+        <v>-13.464</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.33</v>
       </c>
       <c r="I177" t="n">
-        <v>0.7281</v>
+        <v>0.6881</v>
       </c>
       <c r="J177" t="n">
-        <v>21.843</v>
+        <v>20.643</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0274</v>
+        <v>0.0197</v>
       </c>
       <c r="J178" t="n">
-        <v>0.822</v>
+        <v>0.591</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.82</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2042</v>
+        <v>-0.221</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.126</v>
+        <v>-6.63</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.66</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3592</v>
+        <v>-0.3725</v>
       </c>
       <c r="J180" t="n">
-        <v>-10.776</v>
+        <v>-11.175</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.58</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4338</v>
+        <v>-0.4438</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.014</v>
+        <v>-13.314</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.19</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5616</v>
+        <v>0.541</v>
       </c>
       <c r="J182" t="n">
-        <v>19.656</v>
+        <v>18.935</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.18</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5362</v>
+        <v>0.5181</v>
       </c>
       <c r="J183" t="n">
-        <v>18.767</v>
+        <v>18.1335</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.16</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4847</v>
+        <v>0.4718</v>
       </c>
       <c r="J184" t="n">
-        <v>16.9645</v>
+        <v>16.513</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.99</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0746</v>
+        <v>-0.0732</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.611</v>
+        <v>-2.562</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.92</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3148</v>
+        <v>-0.3048</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.018</v>
+        <v>-10.668</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.24</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5384</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="J187" t="n">
-        <v>18.844</v>
+        <v>18.2245</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0128</v>
+        <v>0.0091</v>
       </c>
       <c r="J188" t="n">
-        <v>0.448</v>
+        <v>0.3185</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.85</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1798</v>
+        <v>-0.1951</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.293</v>
+        <v>-6.8285</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.8</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2306</v>
+        <v>-0.2459</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.071</v>
+        <v>-8.6065</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.76</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2701</v>
+        <v>-0.2848</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.4535</v>
+        <v>-9.968</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.92</v>
       </c>
       <c r="I192" t="n">
-        <v>1.5782</v>
+        <v>1.5787</v>
       </c>
       <c r="J192" t="n">
-        <v>29.9858</v>
+        <v>29.9953</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.53</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1304</v>
+        <v>1.1021</v>
       </c>
       <c r="J193" t="n">
-        <v>21.4776</v>
+        <v>20.9399</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.49</v>
       </c>
       <c r="I194" t="n">
-        <v>1.0838</v>
+        <v>1.0504</v>
       </c>
       <c r="J194" t="n">
-        <v>20.5922</v>
+        <v>19.9576</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.45</v>
       </c>
       <c r="I195" t="n">
-        <v>1.0355</v>
+        <v>0.9933</v>
       </c>
       <c r="J195" t="n">
-        <v>19.6745</v>
+        <v>18.8727</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.01</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.0563</v>
+        <v>-0.0177</v>
       </c>
       <c r="J196" t="n">
-        <v>-1.0697</v>
+        <v>-0.3363</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.7</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.26</v>
+        <v>-0.2884</v>
       </c>
       <c r="J197" t="n">
-        <v>-4.94</v>
+        <v>-5.4796</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2708</v>
+        <v>-0.2986</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.1452</v>
+        <v>-5.6734</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.57</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3915</v>
+        <v>-0.4126</v>
       </c>
       <c r="J199" t="n">
-        <v>-7.4385</v>
+        <v>-7.8394</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.45</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5004</v>
+        <v>-0.5149</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.5076</v>
+        <v>-9.783099999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.3</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6465</v>
+        <v>-0.6489</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.2835</v>
+        <v>-12.3291</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.07</v>
       </c>
       <c r="I202" t="n">
-        <v>0.2022</v>
+        <v>0.2051</v>
       </c>
       <c r="J202" t="n">
-        <v>5.2572</v>
+        <v>5.3326</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.02</v>
       </c>
       <c r="I203" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0842</v>
       </c>
       <c r="J203" t="n">
-        <v>2.1086</v>
+        <v>2.1892</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0128</v>
+        <v>0.0091</v>
       </c>
       <c r="J204" t="n">
-        <v>0.3328</v>
+        <v>0.2366</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.95</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0702</v>
+        <v>-0.0818</v>
       </c>
       <c r="J205" t="n">
-        <v>-1.8252</v>
+        <v>-2.1268</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.61</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4123</v>
+        <v>-0.4224</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.7198</v>
+        <v>-10.9824</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.4</v>
       </c>
       <c r="I207" t="n">
-        <v>1.0273</v>
+        <v>0.969</v>
       </c>
       <c r="J207" t="n">
-        <v>26.7098</v>
+        <v>25.194</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.32</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8658</v>
+        <v>0.8116</v>
       </c>
       <c r="J208" t="n">
-        <v>22.5108</v>
+        <v>21.1016</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.22</v>
       </c>
       <c r="I209" t="n">
-        <v>0.626</v>
+        <v>0.6005</v>
       </c>
       <c r="J209" t="n">
-        <v>16.276</v>
+        <v>15.613</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.88</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4403</v>
+        <v>-0.4182</v>
       </c>
       <c r="J210" t="n">
-        <v>-11.4478</v>
+        <v>-10.8732</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6814</v>
+        <v>-0.6345</v>
       </c>
       <c r="J211" t="n">
-        <v>-17.7164</v>
+        <v>-16.497</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.24</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3381</v>
+        <v>0.3523</v>
       </c>
       <c r="J212" t="n">
-        <v>10.143</v>
+        <v>10.569</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.23</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3259</v>
+        <v>0.3405</v>
       </c>
       <c r="J213" t="n">
-        <v>9.776999999999999</v>
+        <v>10.215</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.14</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2129</v>
+        <v>0.2294</v>
       </c>
       <c r="J214" t="n">
-        <v>6.387</v>
+        <v>6.882</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.08</v>
       </c>
       <c r="I215" t="n">
-        <v>0.1314</v>
+        <v>0.147</v>
       </c>
       <c r="J215" t="n">
-        <v>3.942</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.96</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.0765</v>
+        <v>-0.0828</v>
       </c>
       <c r="J216" t="n">
-        <v>-2.295</v>
+        <v>-2.484</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.27</v>
       </c>
       <c r="I217" t="n">
-        <v>0.456</v>
+        <v>0.4485</v>
       </c>
       <c r="J217" t="n">
-        <v>13.68</v>
+        <v>13.455</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.08169999999999999</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="J218" t="n">
-        <v>-2.451</v>
+        <v>-2.826</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.88</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1476</v>
+        <v>-0.1627</v>
       </c>
       <c r="J219" t="n">
-        <v>-4.428</v>
+        <v>-4.881</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2198</v>
+        <v>-0.2353</v>
       </c>
       <c r="J220" t="n">
-        <v>-6.594</v>
+        <v>-7.059</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.72</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3081</v>
+        <v>-0.322</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.243</v>
+        <v>-9.66</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.15</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3607</v>
+        <v>0.3577</v>
       </c>
       <c r="J222" t="n">
-        <v>15.1494</v>
+        <v>15.0234</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.11</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2809</v>
+        <v>0.2823</v>
       </c>
       <c r="J223" t="n">
-        <v>11.7978</v>
+        <v>11.8566</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.05</v>
       </c>
       <c r="I224" t="n">
-        <v>0.151</v>
+        <v>0.1563</v>
       </c>
       <c r="J224" t="n">
-        <v>6.342</v>
+        <v>6.5646</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.84</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.1925</v>
+        <v>-0.2073</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.085000000000001</v>
+        <v>-8.7066</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.6</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4238</v>
+        <v>-0.433</v>
       </c>
       <c r="J226" t="n">
-        <v>-17.7996</v>
+        <v>-18.186</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.63</v>
       </c>
       <c r="I227" t="n">
-        <v>1.3258</v>
+        <v>1.2973</v>
       </c>
       <c r="J227" t="n">
-        <v>55.6836</v>
+        <v>54.4866</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.18</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5232</v>
+        <v>0.5092</v>
       </c>
       <c r="J228" t="n">
-        <v>21.9744</v>
+        <v>21.3864</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.08</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2599</v>
+        <v>0.2671</v>
       </c>
       <c r="J229" t="n">
-        <v>10.9158</v>
+        <v>11.2182</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.96</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.2005</v>
+        <v>-0.1938</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.420999999999999</v>
+        <v>-8.1396</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.83</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5806</v>
+        <v>-0.544</v>
       </c>
       <c r="J231" t="n">
-        <v>-24.3852</v>
+        <v>-22.848</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.21</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3616</v>
+        <v>0.3619</v>
       </c>
       <c r="J232" t="n">
-        <v>10.1248</v>
+        <v>10.1332</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.14</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2595</v>
+        <v>0.2646</v>
       </c>
       <c r="J233" t="n">
-        <v>7.266</v>
+        <v>7.4088</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.08</v>
       </c>
       <c r="I234" t="n">
-        <v>0.1655</v>
+        <v>0.1728</v>
       </c>
       <c r="J234" t="n">
-        <v>4.634</v>
+        <v>4.8384</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0839</v>
+        <v>-0.0958</v>
       </c>
       <c r="J235" t="n">
-        <v>-2.3492</v>
+        <v>-2.6824</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.41</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5952</v>
+        <v>-0.5949</v>
       </c>
       <c r="J236" t="n">
-        <v>-16.6656</v>
+        <v>-16.6572</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.57</v>
       </c>
       <c r="I237" t="n">
-        <v>0.7258</v>
+        <v>0.7159</v>
       </c>
       <c r="J237" t="n">
-        <v>20.3224</v>
+        <v>20.0452</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.16</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2421</v>
+        <v>0.2576</v>
       </c>
       <c r="J238" t="n">
-        <v>6.7788</v>
+        <v>7.2128</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.13</v>
       </c>
       <c r="I239" t="n">
-        <v>0.2027</v>
+        <v>0.2185</v>
       </c>
       <c r="J239" t="n">
-        <v>5.6756</v>
+        <v>6.118</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.92</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1224</v>
+        <v>-0.132</v>
       </c>
       <c r="J240" t="n">
-        <v>-3.4272</v>
+        <v>-3.696</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.72</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3278</v>
+        <v>-0.3375</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.1784</v>
+        <v>-9.449999999999999</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.75</v>
       </c>
       <c r="I242" t="n">
-        <v>1.4554</v>
+        <v>1.4372</v>
       </c>
       <c r="J242" t="n">
-        <v>39.2958</v>
+        <v>38.8044</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.4</v>
       </c>
       <c r="I243" t="n">
-        <v>1.0063</v>
+        <v>0.9498</v>
       </c>
       <c r="J243" t="n">
-        <v>27.1701</v>
+        <v>25.6446</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.02</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0484</v>
+        <v>0.0683</v>
       </c>
       <c r="J244" t="n">
-        <v>1.3068</v>
+        <v>1.8441</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.95</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2494</v>
+        <v>-0.2366</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.7338</v>
+        <v>-6.3882</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.86</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.515</v>
+        <v>-0.482</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.905</v>
+        <v>-13.014</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.19</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4735</v>
+        <v>0.4558</v>
       </c>
       <c r="J247" t="n">
-        <v>12.7845</v>
+        <v>12.3066</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.0747</v>
+        <v>-0.0888</v>
       </c>
       <c r="J248" t="n">
-        <v>-2.0169</v>
+        <v>-2.3976</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.75</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2716</v>
+        <v>-0.2879</v>
       </c>
       <c r="J249" t="n">
-        <v>-7.3332</v>
+        <v>-7.7733</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.74</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2813</v>
+        <v>-0.2974</v>
       </c>
       <c r="J250" t="n">
-        <v>-7.5951</v>
+        <v>-8.0298</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.71</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3101</v>
+        <v>-0.3254</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.3727</v>
+        <v>-8.7858</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.74</v>
       </c>
       <c r="I252" t="n">
-        <v>1.4269</v>
+        <v>1.4099</v>
       </c>
       <c r="J252" t="n">
-        <v>35.6725</v>
+        <v>35.2475</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.48</v>
       </c>
       <c r="I253" t="n">
-        <v>1.1051</v>
+        <v>1.0669</v>
       </c>
       <c r="J253" t="n">
-        <v>27.6275</v>
+        <v>26.6725</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.21</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5764</v>
+        <v>0.5616</v>
       </c>
       <c r="J254" t="n">
-        <v>14.41</v>
+        <v>14.04</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2945</v>
+        <v>-0.2761</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.3625</v>
+        <v>-6.9025</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.87</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4999</v>
+        <v>-0.4658</v>
       </c>
       <c r="J256" t="n">
-        <v>-12.4975</v>
+        <v>-11.645</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.37</v>
       </c>
       <c r="I257" t="n">
-        <v>0.79</v>
+        <v>0.7449</v>
       </c>
       <c r="J257" t="n">
-        <v>19.75</v>
+        <v>18.6225</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0785</v>
+        <v>-0.0917</v>
       </c>
       <c r="J258" t="n">
-        <v>-1.9625</v>
+        <v>-2.2925</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.85</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1757</v>
+        <v>-0.192</v>
       </c>
       <c r="J259" t="n">
-        <v>-4.3925</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.74</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.285</v>
+        <v>-0.3002</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.125</v>
+        <v>-7.505</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.57</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4449</v>
+        <v>-0.4541</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.1225</v>
+        <v>-11.3525</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.49</v>
       </c>
       <c r="I262" t="n">
-        <v>1.1282</v>
+        <v>1.09</v>
       </c>
       <c r="J262" t="n">
-        <v>27.0768</v>
+        <v>26.16</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.48</v>
       </c>
       <c r="I263" t="n">
-        <v>1.1153</v>
+        <v>1.0761</v>
       </c>
       <c r="J263" t="n">
-        <v>26.7672</v>
+        <v>25.8264</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.16</v>
       </c>
       <c r="I264" t="n">
-        <v>0.4622</v>
+        <v>0.4565</v>
       </c>
       <c r="J264" t="n">
-        <v>11.0928</v>
+        <v>10.956</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0491</v>
+        <v>-0.0339</v>
       </c>
       <c r="J265" t="n">
-        <v>-1.1784</v>
+        <v>-0.8136</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.88</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.461</v>
+        <v>-0.4327</v>
       </c>
       <c r="J266" t="n">
-        <v>-11.064</v>
+        <v>-10.3848</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.28</v>
       </c>
       <c r="I267" t="n">
-        <v>0.6014</v>
+        <v>0.5797</v>
       </c>
       <c r="J267" t="n">
-        <v>14.4336</v>
+        <v>13.9128</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.14</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3404</v>
+        <v>0.3388</v>
       </c>
       <c r="J268" t="n">
-        <v>8.169600000000001</v>
+        <v>8.1312</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.79</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2433</v>
+        <v>-0.2578</v>
       </c>
       <c r="J269" t="n">
-        <v>-5.8392</v>
+        <v>-6.1872</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.78</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2532</v>
+        <v>-0.2676</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.0768</v>
+        <v>-6.4224</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.77</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.263</v>
+        <v>-0.2773</v>
       </c>
       <c r="J271" t="n">
-        <v>-6.312</v>
+        <v>-6.6552</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.42</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0764</v>
+        <v>1.0235</v>
       </c>
       <c r="J272" t="n">
-        <v>31.2156</v>
+        <v>29.6815</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.15</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4681</v>
+        <v>0.4547</v>
       </c>
       <c r="J273" t="n">
-        <v>13.5749</v>
+        <v>13.1863</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.03</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1197</v>
+        <v>0.1285</v>
       </c>
       <c r="J274" t="n">
-        <v>3.4713</v>
+        <v>3.7265</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.01</v>
       </c>
       <c r="I275" t="n">
-        <v>0.0427</v>
+        <v>0.0515</v>
       </c>
       <c r="J275" t="n">
-        <v>1.2383</v>
+        <v>1.4935</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.67</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.9626</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="J276" t="n">
-        <v>-27.9154</v>
+        <v>-25.6244</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.48</v>
       </c>
       <c r="I277" t="n">
-        <v>0.9124</v>
+        <v>0.8638</v>
       </c>
       <c r="J277" t="n">
-        <v>26.4596</v>
+        <v>25.0502</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.03</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0893</v>
+        <v>0.0982</v>
       </c>
       <c r="J278" t="n">
-        <v>2.5897</v>
+        <v>2.8478</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.92</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.1134</v>
+        <v>-0.125</v>
       </c>
       <c r="J279" t="n">
-        <v>-3.2886</v>
+        <v>-3.625</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.85</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.1898</v>
+        <v>-0.2029</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.5042</v>
+        <v>-5.8841</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.8</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2409</v>
+        <v>-0.2539</v>
       </c>
       <c r="J281" t="n">
-        <v>-6.9861</v>
+        <v>-7.3631</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.07</v>
       </c>
       <c r="I282" t="n">
-        <v>0.2337</v>
+        <v>0.2282</v>
       </c>
       <c r="J282" t="n">
-        <v>7.011</v>
+        <v>6.846</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.97</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.0315</v>
+        <v>-0.044</v>
       </c>
       <c r="J283" t="n">
-        <v>-0.945</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.85</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1712</v>
+        <v>-0.1886</v>
       </c>
       <c r="J284" t="n">
-        <v>-5.136</v>
+        <v>-5.658</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3262</v>
+        <v>-0.3416</v>
       </c>
       <c r="J285" t="n">
-        <v>-9.786</v>
+        <v>-10.248</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.64</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.3734</v>
+        <v>-0.387</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.202</v>
+        <v>-11.61</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.66</v>
       </c>
       <c r="I287" t="n">
-        <v>1.3289</v>
+        <v>1.3064</v>
       </c>
       <c r="J287" t="n">
-        <v>39.867</v>
+        <v>39.192</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.44</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0533</v>
+        <v>1.0067</v>
       </c>
       <c r="J288" t="n">
-        <v>31.599</v>
+        <v>30.201</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.38</v>
       </c>
       <c r="I289" t="n">
-        <v>0.9559</v>
+        <v>0.9006</v>
       </c>
       <c r="J289" t="n">
-        <v>28.677</v>
+        <v>27.018</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.08</v>
       </c>
       <c r="I290" t="n">
-        <v>0.2328</v>
+        <v>0.2483</v>
       </c>
       <c r="J290" t="n">
-        <v>6.984</v>
+        <v>7.449</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.9592000000000001</v>
+        <v>-0.8734</v>
       </c>
       <c r="J291" t="n">
-        <v>-28.776</v>
+        <v>-26.202</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>0.93</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J292" t="n">
-        <v>-1.8312</v>
+        <v>-2.2392</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.92</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.0885</v>
+        <v>-0.1059</v>
       </c>
       <c r="J293" t="n">
-        <v>-2.124</v>
+        <v>-2.5416</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.84</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1769</v>
+        <v>-0.1954</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.2456</v>
+        <v>-4.6896</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.72</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.2921</v>
+        <v>-0.3095</v>
       </c>
       <c r="J295" t="n">
-        <v>-7.0104</v>
+        <v>-7.428</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.61</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3959</v>
+        <v>-0.4095</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.5016</v>
+        <v>-9.827999999999999</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.59</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2461</v>
+        <v>1.2178</v>
       </c>
       <c r="J297" t="n">
-        <v>29.9064</v>
+        <v>29.2272</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.51</v>
       </c>
       <c r="I298" t="n">
-        <v>1.1457</v>
+        <v>1.1104</v>
       </c>
       <c r="J298" t="n">
-        <v>27.4968</v>
+        <v>26.6496</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.23</v>
       </c>
       <c r="I299" t="n">
-        <v>0.6253</v>
+        <v>0.6051</v>
       </c>
       <c r="J299" t="n">
-        <v>15.0072</v>
+        <v>14.5224</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.21</v>
       </c>
       <c r="I300" t="n">
-        <v>0.5786</v>
+        <v>0.5631</v>
       </c>
       <c r="J300" t="n">
-        <v>13.8864</v>
+        <v>13.5144</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.64</v>
       </c>
       <c r="I301" t="n">
-        <v>-1.0751</v>
+        <v>-0.9745</v>
       </c>
       <c r="J301" t="n">
-        <v>-25.8024</v>
+        <v>-23.388</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4828/event_4828_evp_summary.xlsx
+++ b/database/event/4828/event_4828_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.7876</v>
+        <v>6.6515</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5666</v>
+        <v>0.5553</v>
       </c>
       <c r="D2" t="n">
-        <v>2.4657</v>
+        <v>2.4243</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7876</v>
+        <v>6.6515</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9823</v>
+        <v>1.9748</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8053</v>
+        <v>4.6767</v>
       </c>
       <c r="H2" t="n">
-        <v>1.9823</v>
+        <v>1.9748</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0334</v>
+        <v>2.0276</v>
       </c>
       <c r="J2" t="n">
-        <v>4.8053</v>
+        <v>4.6767</v>
       </c>
       <c r="K2" t="n">
         <v>152</v>
@@ -529,7 +529,7 @@
         <v>214</v>
       </c>
       <c r="M2" t="n">
-        <v>6.838699999999999</v>
+        <v>6.7043</v>
       </c>
       <c r="N2" t="n">
         <v>366</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.3878</v>
+        <v>6.3117</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5333</v>
+        <v>0.5269</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2837</v>
+        <v>2.2695</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3878</v>
+        <v>6.3117</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5535</v>
+        <v>2.5061</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8343</v>
+        <v>3.8056</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8638</v>
+        <v>2.7931</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9376</v>
+        <v>2.8678</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8343</v>
+        <v>3.8056</v>
       </c>
       <c r="K3" t="n">
         <v>152</v>
@@ -575,7 +575,7 @@
         <v>214</v>
       </c>
       <c r="M3" t="n">
-        <v>6.7719</v>
+        <v>6.6734</v>
       </c>
       <c r="N3" t="n">
         <v>366</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.2067</v>
+        <v>6.0426</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5181</v>
+        <v>0.5044</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2012</v>
+        <v>2.1469</v>
       </c>
       <c r="E4" t="n">
-        <v>6.2067</v>
+        <v>6.0426</v>
       </c>
       <c r="F4" t="n">
-        <v>2.298</v>
+        <v>2.1321</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9087</v>
+        <v>3.9105</v>
       </c>
       <c r="H4" t="n">
-        <v>2.3046</v>
+        <v>2.1321</v>
       </c>
       <c r="I4" t="n">
-        <v>2.364</v>
+        <v>2.1891</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9087</v>
+        <v>3.9105</v>
       </c>
       <c r="K4" t="n">
         <v>152</v>
@@ -621,7 +621,7 @@
         <v>214</v>
       </c>
       <c r="M4" t="n">
-        <v>6.2727</v>
+        <v>6.0996</v>
       </c>
       <c r="N4" t="n">
         <v>366</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0535</v>
+        <v>4.9081</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4219</v>
+        <v>0.4097</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6763</v>
+        <v>1.6301</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0535</v>
+        <v>4.9081</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1522</v>
+        <v>1.1196</v>
       </c>
       <c r="G5" t="n">
-        <v>3.9013</v>
+        <v>3.7885</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1522</v>
+        <v>1.1196</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1522</v>
+        <v>1.1196</v>
       </c>
       <c r="J5" t="n">
-        <v>3.9013</v>
+        <v>3.7885</v>
       </c>
       <c r="K5" t="n">
         <v>107</v>
@@ -667,7 +667,7 @@
         <v>185</v>
       </c>
       <c r="M5" t="n">
-        <v>5.0535</v>
+        <v>4.9081</v>
       </c>
       <c r="N5" t="n">
         <v>292</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7967</v>
+        <v>4.669</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4004</v>
+        <v>0.3898</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5594</v>
+        <v>1.5212</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7967</v>
+        <v>4.669</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6599</v>
+        <v>3.5875</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1368</v>
+        <v>1.0815</v>
       </c>
       <c r="H6" t="n">
-        <v>7.1812</v>
+        <v>7.0262</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8778</v>
+        <v>3.945</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1368</v>
+        <v>1.0815</v>
       </c>
       <c r="K6" t="n">
         <v>144</v>
@@ -713,7 +713,7 @@
         <v>59</v>
       </c>
       <c r="M6" t="n">
-        <v>5.0146</v>
+        <v>5.0265</v>
       </c>
       <c r="N6" t="n">
         <v>203</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5792</v>
+        <v>3.4805</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2988</v>
+        <v>0.2906</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0051</v>
+        <v>0.9797</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5792</v>
+        <v>3.4805</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8631</v>
+        <v>2.8382</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7161</v>
+        <v>0.6423</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5523</v>
+        <v>4.2131</v>
       </c>
       <c r="I7" t="n">
-        <v>2.4582</v>
+        <v>2.3655</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7161</v>
+        <v>0.6423</v>
       </c>
       <c r="K7" t="n">
         <v>144</v>
@@ -759,7 +759,7 @@
         <v>59</v>
       </c>
       <c r="M7" t="n">
-        <v>3.1743</v>
+        <v>3.0078</v>
       </c>
       <c r="N7" t="n">
         <v>203</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5771</v>
+        <v>3.4548</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2986</v>
+        <v>0.2884</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0042</v>
+        <v>0.968</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5771</v>
+        <v>3.4548</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3667</v>
+        <v>1.3768</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2104</v>
+        <v>2.078</v>
       </c>
       <c r="H8" t="n">
-        <v>1.3667</v>
+        <v>1.3768</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3667</v>
+        <v>1.3768</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2104</v>
+        <v>2.078</v>
       </c>
       <c r="K8" t="n">
         <v>107</v>
@@ -805,7 +805,7 @@
         <v>185</v>
       </c>
       <c r="M8" t="n">
-        <v>3.5771</v>
+        <v>3.4548</v>
       </c>
       <c r="N8" t="n">
         <v>292</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.5567</v>
+        <v>3.4524</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2969</v>
+        <v>0.2882</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9949</v>
+        <v>0.9669</v>
       </c>
       <c r="E9" t="n">
-        <v>3.5567</v>
+        <v>3.4524</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4742</v>
+        <v>3.4035</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0825</v>
+        <v>0.0489</v>
       </c>
       <c r="H9" t="n">
-        <v>6.5686</v>
+        <v>6.3357</v>
       </c>
       <c r="I9" t="n">
-        <v>3.547</v>
+        <v>3.5573</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0825</v>
+        <v>0.0489</v>
       </c>
       <c r="K9" t="n">
         <v>151</v>
@@ -851,7 +851,7 @@
         <v>49</v>
       </c>
       <c r="M9" t="n">
-        <v>3.6295</v>
+        <v>3.6062</v>
       </c>
       <c r="N9" t="n">
         <v>200</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.1571</v>
+        <v>3.0065</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2636</v>
+        <v>0.251</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.7638</v>
       </c>
       <c r="E10" t="n">
-        <v>3.1571</v>
+        <v>3.0065</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8022</v>
+        <v>1.7582</v>
       </c>
       <c r="G10" t="n">
-        <v>1.3549</v>
+        <v>1.2483</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8022</v>
+        <v>1.7582</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8022</v>
+        <v>1.7582</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3549</v>
+        <v>1.2483</v>
       </c>
       <c r="K10" t="n">
         <v>107</v>
@@ -897,7 +897,7 @@
         <v>185</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1571</v>
+        <v>3.0065</v>
       </c>
       <c r="N10" t="n">
         <v>292</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5839</v>
+        <v>2.5895</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2157</v>
+        <v>0.2162</v>
       </c>
       <c r="D11" t="n">
-        <v>0.552</v>
+        <v>0.5739</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5839</v>
+        <v>2.5895</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3025</v>
+        <v>2.3544</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2814</v>
+        <v>0.2351</v>
       </c>
       <c r="H11" t="n">
-        <v>2.7026</v>
+        <v>2.3967</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4594</v>
+        <v>1.3457</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2814</v>
+        <v>0.2351</v>
       </c>
       <c r="K11" t="n">
         <v>151</v>
@@ -943,7 +943,7 @@
         <v>49</v>
       </c>
       <c r="M11" t="n">
-        <v>1.7408</v>
+        <v>1.5808</v>
       </c>
       <c r="N11" t="n">
         <v>200</v>
@@ -952,93 +952,93 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Plopski</t>
+          <t>woxic</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.3941</v>
+        <v>2.4072</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1999</v>
+        <v>0.201</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4656</v>
+        <v>0.4908</v>
       </c>
       <c r="E12" t="n">
-        <v>2.3941</v>
+        <v>2.4072</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9489</v>
+        <v>2.4917</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4452</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9489</v>
+        <v>2.9124</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9489</v>
+        <v>1.6352</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4452</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>118</v>
+        <v>151</v>
       </c>
       <c r="L12" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3941</v>
+        <v>1.5507</v>
       </c>
       <c r="N12" t="n">
-        <v>173</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>woxic</t>
+          <t>Plopski</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.3272</v>
+        <v>2.3062</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1943</v>
+        <v>0.1925</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4352</v>
+        <v>0.4448</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3272</v>
+        <v>2.3062</v>
       </c>
       <c r="F13" t="n">
-        <v>2.3784</v>
+        <v>1.9127</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0512</v>
+        <v>0.3935</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9532</v>
+        <v>1.9127</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5947</v>
+        <v>1.9127</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.0512</v>
+        <v>0.3935</v>
       </c>
       <c r="K13" t="n">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="L13" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5435</v>
+        <v>2.3062</v>
       </c>
       <c r="N13" t="n">
-        <v>200</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.199</v>
+        <v>2.023</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1836</v>
+        <v>0.1689</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3768</v>
+        <v>0.3158</v>
       </c>
       <c r="E14" t="n">
-        <v>2.199</v>
+        <v>2.023</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3029</v>
+        <v>1.2163</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8961</v>
+        <v>0.8067</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3029</v>
+        <v>1.2163</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3029</v>
+        <v>1.2163</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8961</v>
+        <v>0.8067</v>
       </c>
       <c r="K14" t="n">
         <v>107</v>
@@ -1081,7 +1081,7 @@
         <v>74</v>
       </c>
       <c r="M14" t="n">
-        <v>2.199</v>
+        <v>2.023</v>
       </c>
       <c r="N14" t="n">
         <v>181</v>
@@ -1090,185 +1090,185 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>torzsi</t>
+          <t>kNgV-</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.8638</v>
+        <v>1.856</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1556</v>
+        <v>0.1549</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2242</v>
+        <v>0.2397</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8638</v>
+        <v>1.856</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8638</v>
+        <v>2.2822</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-0.4262</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8638</v>
+        <v>2.2822</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8638</v>
+        <v>1.2814</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.4262</v>
       </c>
       <c r="K15" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8638</v>
+        <v>0.8552000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>133</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>kNgV-</t>
+          <t>torzsi</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.77</v>
+        <v>1.658</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1478</v>
+        <v>0.1384</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1815</v>
+        <v>0.1495</v>
       </c>
       <c r="E16" t="n">
-        <v>1.77</v>
+        <v>1.658</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2208</v>
+        <v>1.658</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4508</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.433</v>
+        <v>1.658</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3138</v>
+        <v>1.658</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4508</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="L16" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8630000000000001</v>
+        <v>1.658</v>
       </c>
       <c r="N16" t="n">
-        <v>203</v>
+        <v>133</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>roeJ</t>
+          <t>Vegi</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.743</v>
+        <v>1.6246</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1455</v>
+        <v>0.1356</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1692</v>
+        <v>0.1343</v>
       </c>
       <c r="E17" t="n">
-        <v>1.743</v>
+        <v>1.6246</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0479</v>
+        <v>0.905</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.7196</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0479</v>
+        <v>0.905</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0749</v>
+        <v>0.905</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6951000000000001</v>
+        <v>0.7196</v>
       </c>
       <c r="K17" t="n">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="L17" t="n">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="M17" t="n">
-        <v>1.77</v>
+        <v>1.6246</v>
       </c>
       <c r="N17" t="n">
-        <v>366</v>
+        <v>292</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Vegi</t>
+          <t>roeJ</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6595</v>
+        <v>1.597</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1385</v>
+        <v>0.1333</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1312</v>
+        <v>0.1217</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6595</v>
+        <v>1.597</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7517</v>
+        <v>0.6653</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9078000000000001</v>
+        <v>0.9566</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7517</v>
+        <v>0.6653</v>
       </c>
       <c r="K18" t="n">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="L18" t="n">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6595</v>
+        <v>1.6219</v>
       </c>
       <c r="N18" t="n">
-        <v>292</v>
+        <v>366</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4691</v>
+        <v>1.4177</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1226</v>
+        <v>0.1184</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0446</v>
+        <v>0.04</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4691</v>
+        <v>1.4177</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4012</v>
+        <v>1.3742</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0679</v>
+        <v>0.0435</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4012</v>
+        <v>1.3742</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4012</v>
+        <v>1.3742</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0679</v>
+        <v>0.0435</v>
       </c>
       <c r="K19" t="n">
         <v>118</v>
@@ -1311,7 +1311,7 @@
         <v>55</v>
       </c>
       <c r="M19" t="n">
-        <v>1.4691</v>
+        <v>1.4177</v>
       </c>
       <c r="N19" t="n">
         <v>173</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.4129</v>
+        <v>1.3369</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1179</v>
+        <v>0.1116</v>
       </c>
       <c r="D20" t="n">
-        <v>0.019</v>
+        <v>0.0032</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4129</v>
+        <v>1.3369</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3729</v>
+        <v>1.3359</v>
       </c>
       <c r="G20" t="n">
-        <v>0.04</v>
+        <v>0.0011</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3729</v>
+        <v>1.3359</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3729</v>
+        <v>1.3359</v>
       </c>
       <c r="J20" t="n">
-        <v>0.04</v>
+        <v>0.0011</v>
       </c>
       <c r="K20" t="n">
         <v>118</v>
@@ -1357,7 +1357,7 @@
         <v>55</v>
       </c>
       <c r="M20" t="n">
-        <v>1.4129</v>
+        <v>1.337</v>
       </c>
       <c r="N20" t="n">
         <v>173</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1894</v>
+        <v>1.1163</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0993</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0828</v>
+        <v>-0.0973</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1894</v>
+        <v>1.1163</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9893</v>
+        <v>0.9764</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2001</v>
+        <v>0.1399</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9893</v>
+        <v>0.9764</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9893</v>
+        <v>0.9764</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2001</v>
+        <v>0.1399</v>
       </c>
       <c r="K21" t="n">
         <v>107</v>
@@ -1403,7 +1403,7 @@
         <v>74</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1894</v>
+        <v>1.1163</v>
       </c>
       <c r="N21" t="n">
         <v>181</v>
@@ -1416,31 +1416,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9033</v>
+        <v>0.9962</v>
       </c>
       <c r="C22" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0832</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.213</v>
+        <v>-0.152</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9033</v>
+        <v>0.9962</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2985</v>
+        <v>1.3531</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3952</v>
+        <v>-0.3569</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2985</v>
+        <v>1.3531</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7012</v>
+        <v>0.7597</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3952</v>
+        <v>-0.3569</v>
       </c>
       <c r="K22" t="n">
         <v>144</v>
@@ -1449,7 +1449,7 @@
         <v>59</v>
       </c>
       <c r="M22" t="n">
-        <v>0.306</v>
+        <v>0.4028</v>
       </c>
       <c r="N22" t="n">
         <v>203</v>
@@ -1458,139 +1458,139 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>conoR</t>
+          <t>GeT_RiGhT</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5723</v>
+        <v>0.528</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0478</v>
+        <v>0.0441</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3637</v>
+        <v>-0.3653</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5723</v>
+        <v>0.528</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5723</v>
+        <v>1.1335</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-0.6055</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5723</v>
+        <v>1.1335</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5723</v>
+        <v>1.1335</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-0.6055</v>
       </c>
       <c r="K23" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5723</v>
+        <v>0.5279999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>106</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GeT_RiGhT</t>
+          <t>morelz</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5031</v>
+        <v>0.4995</v>
       </c>
       <c r="C24" t="n">
-        <v>0.042</v>
+        <v>0.0417</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3952</v>
+        <v>-0.3782</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5031</v>
+        <v>0.4995</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1311</v>
+        <v>1.1925</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.628</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>1.1311</v>
+        <v>1.1925</v>
       </c>
       <c r="I24" t="n">
-        <v>1.1311</v>
+        <v>1.1925</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.628</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="L24" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5031</v>
+        <v>0.4994999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>morelz</t>
+          <t>conoR</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4981</v>
+        <v>0.4726</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0416</v>
+        <v>0.0395</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3975</v>
+        <v>-0.3905</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4981</v>
+        <v>0.4726</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2117</v>
+        <v>0.4726</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7136</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.2117</v>
+        <v>0.4726</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2117</v>
+        <v>0.4726</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7136</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L25" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4981</v>
+        <v>0.4726</v>
       </c>
       <c r="N25" t="n">
-        <v>181</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3494</v>
+        <v>0.2928</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0292</v>
+        <v>0.0244</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4651</v>
+        <v>-0.4724</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3494</v>
+        <v>0.2928</v>
       </c>
       <c r="F26" t="n">
-        <v>0.3494</v>
+        <v>0.2928</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3494</v>
+        <v>0.2928</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3494</v>
+        <v>0.2928</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3494</v>
+        <v>0.2928</v>
       </c>
       <c r="N26" t="n">
         <v>106</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.344</v>
+        <v>0.2723</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0287</v>
+        <v>0.0227</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4676</v>
+        <v>-0.4817</v>
       </c>
       <c r="E27" t="n">
-        <v>0.344</v>
+        <v>0.2723</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0936</v>
+        <v>0.0618</v>
       </c>
       <c r="G27" t="n">
-        <v>0.2504</v>
+        <v>0.2105</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0936</v>
+        <v>0.0618</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0936</v>
+        <v>0.0618</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2504</v>
+        <v>0.2105</v>
       </c>
       <c r="K27" t="n">
         <v>118</v>
@@ -1679,7 +1679,7 @@
         <v>55</v>
       </c>
       <c r="M27" t="n">
-        <v>0.344</v>
+        <v>0.2723</v>
       </c>
       <c r="N27" t="n">
         <v>173</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1393</v>
+        <v>-0.1365</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0116</v>
+        <v>-0.0114</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6876</v>
+        <v>-0.668</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1393</v>
+        <v>-0.1365</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1393</v>
+        <v>-0.1365</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1393</v>
+        <v>-0.1365</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1393</v>
+        <v>-0.1365</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1393</v>
+        <v>-0.1365</v>
       </c>
       <c r="N28" t="n">
         <v>106</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3019</v>
+        <v>-0.2977</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0252</v>
+        <v>-0.0249</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.7616000000000001</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3019</v>
+        <v>-0.2977</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3019</v>
+        <v>-0.2977</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3019</v>
+        <v>-0.2977</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3019</v>
+        <v>-0.2977</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3019</v>
+        <v>-0.2977</v>
       </c>
       <c r="N29" t="n">
         <v>106</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.3511</v>
+        <v>-0.3377</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0293</v>
+        <v>-0.0282</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.784</v>
+        <v>-0.7596000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3511</v>
+        <v>-0.3377</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4734</v>
+        <v>0.4382</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.8245</v>
+        <v>-0.7759</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4734</v>
+        <v>0.4382</v>
       </c>
       <c r="I30" t="n">
-        <v>0.4734</v>
+        <v>0.4382</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.8245</v>
+        <v>-0.7759</v>
       </c>
       <c r="K30" t="n">
         <v>107</v>
@@ -1817,7 +1817,7 @@
         <v>74</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.3511</v>
+        <v>-0.3377000000000001</v>
       </c>
       <c r="N30" t="n">
         <v>181</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>kory</t>
+          <t>TACO</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.4438</v>
+        <v>-0.4234</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.037</v>
+        <v>-0.0353</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.8262</v>
+        <v>-0.7987</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4438</v>
+        <v>-0.4234</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.4438</v>
+        <v>-0.8038</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>0.3804</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4438</v>
+        <v>-0.8038</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4438</v>
+        <v>-0.4513</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>0.3804</v>
       </c>
       <c r="K31" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.4438</v>
+        <v>-0.07089999999999996</v>
       </c>
       <c r="N31" t="n">
-        <v>133</v>
+        <v>203</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TACO</t>
+          <t>kory</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.5303</v>
+        <v>-0.4424</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0443</v>
+        <v>-0.0369</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8656</v>
+        <v>-0.8073</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5303</v>
+        <v>-0.4424</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.9639</v>
+        <v>-0.4424</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4336</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.9639</v>
+        <v>-0.4424</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5205</v>
+        <v>-0.4424</v>
       </c>
       <c r="J32" t="n">
-        <v>0.4336</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="L32" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.08689999999999998</v>
+        <v>-0.4424</v>
       </c>
       <c r="N32" t="n">
-        <v>203</v>
+        <v>133</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8003</v>
+        <v>-0.7903</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0668</v>
+        <v>-0.066</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.9885</v>
+        <v>-0.9658</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8003</v>
+        <v>-0.7903</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.8003</v>
+        <v>-0.7903</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8003</v>
+        <v>-0.7903</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.8003</v>
+        <v>-0.7903</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8003</v>
+        <v>-0.7903</v>
       </c>
       <c r="N33" t="n">
         <v>133</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.052</v>
+        <v>-1.0208</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0878</v>
+        <v>-0.0852</v>
       </c>
       <c r="D34" t="n">
-        <v>-1.1031</v>
+        <v>-1.0708</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.052</v>
+        <v>-1.0208</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.498</v>
+        <v>-0.4624</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.554</v>
+        <v>-0.5584</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.498</v>
+        <v>-0.4624</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.498</v>
+        <v>-0.4624</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.554</v>
+        <v>-0.5584</v>
       </c>
       <c r="K34" t="n">
         <v>107</v>
@@ -2001,7 +2001,7 @@
         <v>74</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.052</v>
+        <v>-1.0208</v>
       </c>
       <c r="N34" t="n">
         <v>181</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.1131</v>
+        <v>-1.0293</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0929</v>
+        <v>-0.0859</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.1309</v>
+        <v>-1.0747</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.1131</v>
+        <v>-1.0293</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.1131</v>
+        <v>-1.0293</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.1131</v>
+        <v>-1.0293</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.1131</v>
+        <v>-1.0293</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.1131</v>
+        <v>-1.0293</v>
       </c>
       <c r="N35" t="n">
         <v>133</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1335</v>
+        <v>-1.1281</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0946</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.1402</v>
+        <v>-1.1197</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1335</v>
+        <v>-1.1281</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1335</v>
+        <v>-1.1281</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1335</v>
+        <v>-1.1281</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1335</v>
+        <v>-1.1281</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1335</v>
+        <v>-1.1281</v>
       </c>
       <c r="N36" t="n">
         <v>133</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2515</v>
+        <v>-1.2195</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1045</v>
+        <v>-0.1018</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.1939</v>
+        <v>-1.1613</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2515</v>
+        <v>-1.2195</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.6403</v>
+        <v>-0.5989</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6112</v>
+        <v>-0.6206</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6403</v>
+        <v>-0.5989</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6403</v>
+        <v>-0.5989</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6112</v>
+        <v>-0.6206</v>
       </c>
       <c r="K37" t="n">
         <v>107</v>
@@ -2139,7 +2139,7 @@
         <v>185</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2515</v>
+        <v>-1.2195</v>
       </c>
       <c r="N37" t="n">
         <v>292</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3251</v>
+        <v>-1.233</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1106</v>
+        <v>-0.1029</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.2274</v>
+        <v>-1.1675</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3251</v>
+        <v>-1.233</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.5404</v>
+        <v>-0.47</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.7847</v>
+        <v>-0.763</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.5404</v>
+        <v>-0.47</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.2918</v>
+        <v>-0.2639</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.7847</v>
+        <v>-0.763</v>
       </c>
       <c r="K38" t="n">
         <v>151</v>
@@ -2185,7 +2185,7 @@
         <v>49</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0765</v>
+        <v>-1.0269</v>
       </c>
       <c r="N38" t="n">
         <v>200</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.4192</v>
+        <v>-1.3672</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1185</v>
+        <v>-0.1141</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.2703</v>
+        <v>-1.2286</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.4192</v>
+        <v>-1.3672</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4192</v>
+        <v>-1.3672</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4192</v>
+        <v>-1.3672</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.4192</v>
+        <v>-1.3672</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.4192</v>
+        <v>-1.3672</v>
       </c>
       <c r="N39" t="n">
         <v>106</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-2.1255</v>
+        <v>-1.9019</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1774</v>
+        <v>-0.1588</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.5918</v>
+        <v>-1.4722</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.1255</v>
+        <v>-1.9019</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0004</v>
+        <v>-1.7203</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.1251</v>
+        <v>-0.1816</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0004</v>
+        <v>-1.7203</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.0802</v>
+        <v>-0.9659</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.1251</v>
+        <v>-0.1816</v>
       </c>
       <c r="K40" t="n">
         <v>151</v>
@@ -2277,7 +2277,7 @@
         <v>49</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2053</v>
+        <v>-1.1475</v>
       </c>
       <c r="N40" t="n">
         <v>200</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-4.1019</v>
+        <v>-4.013</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3424</v>
+        <v>-0.335</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.4915</v>
+        <v>-2.4339</v>
       </c>
       <c r="E41" t="n">
-        <v>-4.1019</v>
+        <v>-4.013</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.3034</v>
+        <v>-2.3313</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.7985</v>
+        <v>-1.6817</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.3034</v>
+        <v>-2.3313</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.3628</v>
+        <v>-2.3936</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.7985</v>
+        <v>-1.6817</v>
       </c>
       <c r="K41" t="n">
         <v>152</v>
@@ -2323,7 +2323,7 @@
         <v>214</v>
       </c>
       <c r="M41" t="n">
-        <v>-4.1613</v>
+        <v>-4.0753</v>
       </c>
       <c r="N41" t="n">
         <v>366</v>
@@ -2429,10 +2429,10 @@
         <v>1.1</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1809</v>
+        <v>0.1401</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0652</v>
+        <v>3.9228</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.07</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1368</v>
+        <v>0.1033</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8304</v>
+        <v>2.8924</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.06</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1214</v>
+        <v>0.0907</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3992</v>
+        <v>2.5396</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1054</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9512</v>
+        <v>2.1784</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0281</v>
+        <v>0.0186</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7868000000000001</v>
+        <v>0.5208</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4691</v>
+        <v>0.474</v>
       </c>
       <c r="J7" t="n">
-        <v>13.1348</v>
+        <v>13.272</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.29</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4447</v>
+        <v>0.4466</v>
       </c>
       <c r="J8" t="n">
-        <v>12.4516</v>
+        <v>12.5048</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.2</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3307</v>
+        <v>0.3212</v>
       </c>
       <c r="J9" t="n">
-        <v>9.259600000000001</v>
+        <v>8.993600000000001</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2472</v>
+        <v>-0.2274</v>
       </c>
       <c r="J10" t="n">
-        <v>-6.9216</v>
+        <v>-6.3672</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.66</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3885</v>
+        <v>-0.3778</v>
       </c>
       <c r="J11" t="n">
-        <v>-10.878</v>
+        <v>-10.5784</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.24</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4972</v>
+        <v>0.4381</v>
       </c>
       <c r="J12" t="n">
-        <v>12.9272</v>
+        <v>11.3906</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.18</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3962</v>
+        <v>0.3401</v>
       </c>
       <c r="J13" t="n">
-        <v>10.3012</v>
+        <v>8.842599999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.08</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2102</v>
+        <v>0.1683</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4652</v>
+        <v>4.3758</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.93</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1127</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-2.9302</v>
+        <v>-2.4622</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.64</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4031</v>
+        <v>-0.3934</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.4806</v>
+        <v>-10.2284</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.51</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2101</v>
+        <v>1.2317</v>
       </c>
       <c r="J17" t="n">
-        <v>31.4626</v>
+        <v>32.0242</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.21</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5939</v>
+        <v>0.5551</v>
       </c>
       <c r="J18" t="n">
-        <v>15.4414</v>
+        <v>14.4326</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.93</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2703</v>
+        <v>-0.2303</v>
       </c>
       <c r="J19" t="n">
-        <v>-7.0278</v>
+        <v>-5.9878</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.87</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4307</v>
+        <v>-0.3877</v>
       </c>
       <c r="J20" t="n">
-        <v>-11.1982</v>
+        <v>-10.0802</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.76</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6895</v>
+        <v>-0.6566</v>
       </c>
       <c r="J21" t="n">
-        <v>-17.927</v>
+        <v>-17.0716</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.14</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3482</v>
+        <v>0.2952</v>
       </c>
       <c r="J22" t="n">
-        <v>9.401400000000001</v>
+        <v>7.9704</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.03</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1143</v>
+        <v>0.0848</v>
       </c>
       <c r="J23" t="n">
-        <v>3.0861</v>
+        <v>2.2896</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.95</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.0673</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.1789</v>
+        <v>-1.8171</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.87</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1728</v>
+        <v>-0.1535</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.6656</v>
+        <v>-4.1445</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.59</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4387</v>
+        <v>-0.4316</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.8449</v>
+        <v>-11.6532</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.46</v>
       </c>
       <c r="I27" t="n">
-        <v>1.0738</v>
+        <v>1.0736</v>
       </c>
       <c r="J27" t="n">
-        <v>28.9926</v>
+        <v>28.9872</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.44</v>
       </c>
       <c r="I28" t="n">
-        <v>1.0357</v>
+        <v>1.0312</v>
       </c>
       <c r="J28" t="n">
-        <v>27.9639</v>
+        <v>27.8424</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.22</v>
       </c>
       <c r="I29" t="n">
-        <v>0.592</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>15.984</v>
+        <v>15.039</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.93</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2914</v>
+        <v>-0.2515</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.8678</v>
+        <v>-6.7905</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.79</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6428</v>
+        <v>-0.6092</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.3556</v>
+        <v>-16.4484</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.3</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5471</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>16.413</v>
+        <v>15.591</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.27</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5121</v>
+        <v>0.478</v>
       </c>
       <c r="J33" t="n">
-        <v>15.363</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.21</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4375</v>
+        <v>0.3828</v>
       </c>
       <c r="J34" t="n">
-        <v>13.125</v>
+        <v>11.484</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.79</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2664</v>
+        <v>-0.2472</v>
       </c>
       <c r="J35" t="n">
-        <v>-7.992</v>
+        <v>-7.416</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.66</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3879</v>
+        <v>-0.377</v>
       </c>
       <c r="J36" t="n">
-        <v>-11.637</v>
+        <v>-11.31</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.17</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4825</v>
+        <v>0.4573</v>
       </c>
       <c r="J37" t="n">
-        <v>14.475</v>
+        <v>13.719</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.13</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4024</v>
+        <v>0.362</v>
       </c>
       <c r="J38" t="n">
-        <v>12.072</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.09</v>
       </c>
       <c r="I39" t="n">
-        <v>0.3013</v>
+        <v>0.2638</v>
       </c>
       <c r="J39" t="n">
-        <v>9.039</v>
+        <v>7.914</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.04</v>
       </c>
       <c r="I40" t="n">
-        <v>0.159</v>
+        <v>0.1318</v>
       </c>
       <c r="J40" t="n">
-        <v>4.77</v>
+        <v>3.954</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.2445</v>
+        <v>-0.2058</v>
       </c>
       <c r="J41" t="n">
-        <v>-7.335</v>
+        <v>-6.174</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.34</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5897</v>
+        <v>0.5618</v>
       </c>
       <c r="J42" t="n">
-        <v>17.1013</v>
+        <v>16.2922</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>1.08</v>
       </c>
       <c r="I43" t="n">
-        <v>0.204</v>
+        <v>0.1643</v>
       </c>
       <c r="J43" t="n">
-        <v>5.916</v>
+        <v>4.7647</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.0039</v>
+        <v>-0.0024</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.1131</v>
+        <v>-0.0696</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.97</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.0629</v>
+        <v>-0.0492</v>
       </c>
       <c r="J45" t="n">
-        <v>-1.8241</v>
+        <v>-1.4268</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.92</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.1288</v>
+        <v>-0.1097</v>
       </c>
       <c r="J46" t="n">
-        <v>-3.7352</v>
+        <v>-3.1813</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.51</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9897</v>
+        <v>0.9778</v>
       </c>
       <c r="J47" t="n">
-        <v>28.7013</v>
+        <v>28.3562</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.22</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5583</v>
+        <v>0.5482</v>
       </c>
       <c r="J48" t="n">
-        <v>16.1907</v>
+        <v>15.8978</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.322</v>
+        <v>0.2861</v>
       </c>
       <c r="J49" t="n">
-        <v>9.337999999999999</v>
+        <v>8.296900000000001</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.04</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1512</v>
+        <v>0.1261</v>
       </c>
       <c r="J50" t="n">
-        <v>4.3848</v>
+        <v>3.6569</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.74</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.746</v>
+        <v>-0.7188</v>
       </c>
       <c r="J51" t="n">
-        <v>-21.634</v>
+        <v>-20.8452</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.04</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2103</v>
+        <v>0.1836</v>
       </c>
       <c r="J52" t="n">
-        <v>3.9957</v>
+        <v>3.4884</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.82</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.2033</v>
+        <v>-0.188</v>
       </c>
       <c r="J53" t="n">
-        <v>-3.8627</v>
+        <v>-3.572</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.7</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3182</v>
+        <v>-0.3041</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.0458</v>
+        <v>-5.7779</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.63</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3804</v>
+        <v>-0.3682</v>
       </c>
       <c r="J55" t="n">
-        <v>-7.2276</v>
+        <v>-6.9958</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.36</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.6166</v>
+        <v>-0.6324</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.7154</v>
+        <v>-12.0156</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.91</v>
       </c>
       <c r="I57" t="n">
-        <v>1.427</v>
+        <v>1.4385</v>
       </c>
       <c r="J57" t="n">
-        <v>27.113</v>
+        <v>27.3315</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.54</v>
       </c>
       <c r="I58" t="n">
-        <v>0.9713000000000001</v>
+        <v>0.9618</v>
       </c>
       <c r="J58" t="n">
-        <v>18.4547</v>
+        <v>18.2742</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.53</v>
       </c>
       <c r="I59" t="n">
-        <v>0.9584</v>
+        <v>0.9489</v>
       </c>
       <c r="J59" t="n">
-        <v>18.2096</v>
+        <v>18.0291</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.31</v>
       </c>
       <c r="I60" t="n">
-        <v>0.6626</v>
+        <v>0.6573</v>
       </c>
       <c r="J60" t="n">
-        <v>12.5894</v>
+        <v>12.4887</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.92</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3632</v>
+        <v>-0.3298</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.9008</v>
+        <v>-6.2662</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.25</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4915</v>
+        <v>0.4508</v>
       </c>
       <c r="J62" t="n">
-        <v>14.745</v>
+        <v>13.524</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.12</v>
       </c>
       <c r="I63" t="n">
-        <v>0.2858</v>
+        <v>0.2369</v>
       </c>
       <c r="J63" t="n">
-        <v>8.574</v>
+        <v>7.107</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.11</v>
       </c>
       <c r="I64" t="n">
-        <v>0.267</v>
+        <v>0.2196</v>
       </c>
       <c r="J64" t="n">
-        <v>8.01</v>
+        <v>6.588</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.02</v>
       </c>
       <c r="I65" t="n">
-        <v>0.0711</v>
+        <v>0.0515</v>
       </c>
       <c r="J65" t="n">
-        <v>2.133</v>
+        <v>1.545</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.64</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4043</v>
+        <v>-0.3948</v>
       </c>
       <c r="J66" t="n">
-        <v>-12.129</v>
+        <v>-11.844</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.18</v>
       </c>
       <c r="I67" t="n">
-        <v>0.5074</v>
+        <v>0.4894</v>
       </c>
       <c r="J67" t="n">
-        <v>15.222</v>
+        <v>14.682</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.08</v>
       </c>
       <c r="I68" t="n">
-        <v>0.2811</v>
+        <v>0.2426</v>
       </c>
       <c r="J68" t="n">
-        <v>8.433</v>
+        <v>7.278</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0041</v>
+        <v>-0.0022</v>
       </c>
       <c r="J69" t="n">
-        <v>-0.123</v>
+        <v>-0.066</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.96</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1744</v>
+        <v>-0.1415</v>
       </c>
       <c r="J70" t="n">
-        <v>-5.232</v>
+        <v>-4.245</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2364</v>
+        <v>-0.1986</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.092</v>
+        <v>-5.958</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.96</v>
       </c>
       <c r="I72" t="n">
-        <v>1.4804</v>
+        <v>1.4962</v>
       </c>
       <c r="J72" t="n">
-        <v>31.0884</v>
+        <v>31.4202</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.42</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8141</v>
+        <v>0.8063</v>
       </c>
       <c r="J73" t="n">
-        <v>17.0961</v>
+        <v>16.9323</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.35</v>
       </c>
       <c r="I74" t="n">
-        <v>0.7175</v>
+        <v>0.7114</v>
       </c>
       <c r="J74" t="n">
-        <v>15.0675</v>
+        <v>14.9394</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.34</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7032</v>
+        <v>0.6974</v>
       </c>
       <c r="J75" t="n">
-        <v>14.7672</v>
+        <v>14.6454</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.28</v>
       </c>
       <c r="I76" t="n">
-        <v>0.6151</v>
+        <v>0.6116</v>
       </c>
       <c r="J76" t="n">
-        <v>12.9171</v>
+        <v>12.8436</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.83</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.1935</v>
+        <v>-0.178</v>
       </c>
       <c r="J77" t="n">
-        <v>-4.0635</v>
+        <v>-3.738</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.83</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1935</v>
+        <v>-0.178</v>
       </c>
       <c r="J78" t="n">
-        <v>-4.0635</v>
+        <v>-3.738</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.2144</v>
+        <v>-0.1992</v>
       </c>
       <c r="J79" t="n">
-        <v>-4.5024</v>
+        <v>-4.1832</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.63</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.3809</v>
+        <v>-0.3687</v>
       </c>
       <c r="J80" t="n">
-        <v>-7.9989</v>
+        <v>-7.7427</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.47</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.522</v>
+        <v>-0.5231</v>
       </c>
       <c r="J81" t="n">
-        <v>-10.962</v>
+        <v>-10.9851</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.05</v>
       </c>
       <c r="I82" t="n">
-        <v>0.1317</v>
+        <v>0.1151</v>
       </c>
       <c r="J82" t="n">
-        <v>3.951</v>
+        <v>3.453</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.96</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0536</v>
       </c>
       <c r="J83" t="n">
-        <v>-1.953</v>
+        <v>-1.608</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.93</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1044</v>
+        <v>-0.0893</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.132</v>
+        <v>-2.679</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.82</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2227</v>
+        <v>-0.2029</v>
       </c>
       <c r="J85" t="n">
-        <v>-6.681</v>
+        <v>-6.087</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.72</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3192</v>
+        <v>-0.3021</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.576000000000001</v>
+        <v>-9.063000000000001</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.76</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7772</v>
+        <v>0.7301</v>
       </c>
       <c r="J87" t="n">
-        <v>23.316</v>
+        <v>21.903</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.08</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1467</v>
+        <v>0.1131</v>
       </c>
       <c r="J88" t="n">
-        <v>4.401</v>
+        <v>3.393</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.05</v>
       </c>
       <c r="I89" t="n">
-        <v>0.0992</v>
+        <v>0.074</v>
       </c>
       <c r="J89" t="n">
-        <v>2.976</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.0094</v>
+        <v>-0.007</v>
       </c>
       <c r="J90" t="n">
-        <v>-0.282</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.78</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.2834</v>
+        <v>-0.2656</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.502000000000001</v>
+        <v>-7.968</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.48</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9354</v>
+        <v>0.9211</v>
       </c>
       <c r="J92" t="n">
-        <v>21.5142</v>
+        <v>21.1853</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.29</v>
       </c>
       <c r="I93" t="n">
-        <v>0.6601</v>
+        <v>0.6468</v>
       </c>
       <c r="J93" t="n">
-        <v>15.1823</v>
+        <v>14.8764</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.11</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3404</v>
+        <v>0.306</v>
       </c>
       <c r="J94" t="n">
-        <v>7.8292</v>
+        <v>7.038</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.02</v>
       </c>
       <c r="I95" t="n">
-        <v>0.0725</v>
+        <v>0.0562</v>
       </c>
       <c r="J95" t="n">
-        <v>1.6675</v>
+        <v>1.2926</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.96</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2004</v>
+        <v>-0.1658</v>
       </c>
       <c r="J96" t="n">
-        <v>-4.6092</v>
+        <v>-3.8134</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.13</v>
       </c>
       <c r="I97" t="n">
-        <v>0.3333</v>
+        <v>0.2814</v>
       </c>
       <c r="J97" t="n">
-        <v>7.6659</v>
+        <v>6.4722</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.11</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2944</v>
+        <v>0.2449</v>
       </c>
       <c r="J98" t="n">
-        <v>6.7712</v>
+        <v>5.6327</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.86</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1822</v>
+        <v>-0.1629</v>
       </c>
       <c r="J99" t="n">
-        <v>-4.1906</v>
+        <v>-3.7467</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.72</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3198</v>
+        <v>-0.3028</v>
       </c>
       <c r="J100" t="n">
-        <v>-7.3554</v>
+        <v>-6.9644</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3476</v>
+        <v>-0.3323</v>
       </c>
       <c r="J101" t="n">
-        <v>-7.9948</v>
+        <v>-7.6429</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.77</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3068</v>
+        <v>1.3123</v>
       </c>
       <c r="J102" t="n">
-        <v>32.67</v>
+        <v>32.8075</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.46</v>
       </c>
       <c r="I103" t="n">
-        <v>0.8965</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="J103" t="n">
-        <v>22.4125</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.2</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5155999999999999</v>
+        <v>0.5067</v>
       </c>
       <c r="J104" t="n">
-        <v>12.89</v>
+        <v>12.6675</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.05</v>
       </c>
       <c r="I105" t="n">
-        <v>0.165</v>
+        <v>0.1391</v>
       </c>
       <c r="J105" t="n">
-        <v>4.125</v>
+        <v>3.4775</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.65</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.9527</v>
+        <v>-0.9496</v>
       </c>
       <c r="J106" t="n">
-        <v>-23.8175</v>
+        <v>-23.74</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.19</v>
       </c>
       <c r="I107" t="n">
-        <v>0.4467</v>
+        <v>0.397</v>
       </c>
       <c r="J107" t="n">
-        <v>11.1675</v>
+        <v>9.925000000000001</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.08</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2397</v>
+        <v>0.1951</v>
       </c>
       <c r="J108" t="n">
-        <v>5.9925</v>
+        <v>4.8775</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.88</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1597</v>
+        <v>-0.1418</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.9925</v>
+        <v>-3.545</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.7</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.336</v>
+        <v>-0.3198</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.4</v>
+        <v>-7.995</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.54</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4787</v>
+        <v>-0.476</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.9675</v>
+        <v>-11.9</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.28</v>
       </c>
       <c r="I112" t="n">
-        <v>0.6676</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="J112" t="n">
-        <v>20.028</v>
+        <v>19.581</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.08</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2777</v>
+        <v>0.2403</v>
       </c>
       <c r="J113" t="n">
-        <v>8.331</v>
+        <v>7.209</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.05</v>
       </c>
       <c r="I114" t="n">
-        <v>0.1928</v>
+        <v>0.1614</v>
       </c>
       <c r="J114" t="n">
-        <v>5.784</v>
+        <v>4.842</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.03</v>
       </c>
       <c r="I115" t="n">
-        <v>0.129</v>
+        <v>0.1043</v>
       </c>
       <c r="J115" t="n">
-        <v>3.87</v>
+        <v>3.129</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.82</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5515</v>
+        <v>-0.5111</v>
       </c>
       <c r="J116" t="n">
-        <v>-16.545</v>
+        <v>-15.333</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.19</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4101</v>
+        <v>0.3538</v>
       </c>
       <c r="J117" t="n">
-        <v>12.303</v>
+        <v>10.614</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.17</v>
       </c>
       <c r="I118" t="n">
-        <v>0.376</v>
+        <v>0.3209</v>
       </c>
       <c r="J118" t="n">
-        <v>11.28</v>
+        <v>9.627000000000001</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0015</v>
+        <v>-0.0008</v>
       </c>
       <c r="J119" t="n">
-        <v>-0.045</v>
+        <v>-0.024</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.9</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.1493</v>
+        <v>-0.1295</v>
       </c>
       <c r="J120" t="n">
-        <v>-4.479</v>
+        <v>-3.885</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.88</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1718</v>
+        <v>-0.1513</v>
       </c>
       <c r="J121" t="n">
-        <v>-5.154</v>
+        <v>-4.539</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.14</v>
       </c>
       <c r="I122" t="n">
-        <v>0.3953</v>
+        <v>0.3492</v>
       </c>
       <c r="J122" t="n">
-        <v>9.8825</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>0.93</v>
       </c>
       <c r="I123" t="n">
-        <v>-0.0901</v>
+        <v>-0.0765</v>
       </c>
       <c r="J123" t="n">
-        <v>-2.2525</v>
+        <v>-1.9125</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.66</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.3622</v>
+        <v>-0.3481</v>
       </c>
       <c r="J124" t="n">
-        <v>-9.055</v>
+        <v>-8.702500000000001</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.64</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.3803</v>
+        <v>-0.3673</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.5075</v>
+        <v>-9.182499999999999</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.55</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4603</v>
+        <v>-0.4545</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.5075</v>
+        <v>-11.3625</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.58</v>
       </c>
       <c r="I127" t="n">
-        <v>1.1973</v>
+        <v>1.2121</v>
       </c>
       <c r="J127" t="n">
-        <v>29.9325</v>
+        <v>30.3025</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.52</v>
       </c>
       <c r="I128" t="n">
-        <v>1.1174</v>
+        <v>1.1298</v>
       </c>
       <c r="J128" t="n">
-        <v>27.935</v>
+        <v>28.245</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.16</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4465</v>
+        <v>0.4142</v>
       </c>
       <c r="J129" t="n">
-        <v>11.1625</v>
+        <v>10.355</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.05</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1576</v>
+        <v>0.1317</v>
       </c>
       <c r="J130" t="n">
-        <v>3.94</v>
+        <v>3.2925</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1.04</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1259</v>
+        <v>0.1023</v>
       </c>
       <c r="J131" t="n">
-        <v>3.1475</v>
+        <v>2.5575</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.11</v>
       </c>
       <c r="I132" t="n">
-        <v>0.3051</v>
+        <v>0.2561</v>
       </c>
       <c r="J132" t="n">
-        <v>8.5428</v>
+        <v>7.1708</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>0.93</v>
       </c>
       <c r="I133" t="n">
-        <v>-0.1015</v>
+        <v>-0.0871</v>
       </c>
       <c r="J133" t="n">
-        <v>-2.842</v>
+        <v>-2.4388</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.87</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1695</v>
+        <v>-0.1515</v>
       </c>
       <c r="J134" t="n">
-        <v>-4.746</v>
+        <v>-4.242</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.77</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2688</v>
+        <v>-0.25</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.5264</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.65</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.3803</v>
+        <v>-0.3673</v>
       </c>
       <c r="J136" t="n">
-        <v>-10.6484</v>
+        <v>-10.2844</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.39</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9232</v>
+        <v>0.9094</v>
       </c>
       <c r="J137" t="n">
-        <v>25.8496</v>
+        <v>25.4632</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.34</v>
       </c>
       <c r="I138" t="n">
-        <v>0.8266</v>
+        <v>0.8051</v>
       </c>
       <c r="J138" t="n">
-        <v>23.1448</v>
+        <v>22.5428</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.27</v>
       </c>
       <c r="I139" t="n">
-        <v>0.6868</v>
+        <v>0.6581</v>
       </c>
       <c r="J139" t="n">
-        <v>19.2304</v>
+        <v>18.4268</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.18</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4978</v>
+        <v>0.4648</v>
       </c>
       <c r="J140" t="n">
-        <v>13.9384</v>
+        <v>13.0144</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.98</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.1404</v>
+        <v>-0.1136</v>
       </c>
       <c r="J141" t="n">
-        <v>-3.9312</v>
+        <v>-3.1808</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.15</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4683</v>
+        <v>0.4257</v>
       </c>
       <c r="J142" t="n">
-        <v>19.6686</v>
+        <v>17.8794</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.01</v>
       </c>
       <c r="I143" t="n">
-        <v>0.0585</v>
+        <v>0.0426</v>
       </c>
       <c r="J143" t="n">
-        <v>2.457</v>
+        <v>1.7892</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.01</v>
       </c>
       <c r="I144" t="n">
-        <v>0.0585</v>
+        <v>0.0426</v>
       </c>
       <c r="J144" t="n">
-        <v>2.457</v>
+        <v>1.7892</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.96</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1691</v>
+        <v>-0.1375</v>
       </c>
       <c r="J145" t="n">
-        <v>-7.1022</v>
+        <v>-5.775</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.88</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3944</v>
+        <v>-0.3516</v>
       </c>
       <c r="J146" t="n">
-        <v>-16.5648</v>
+        <v>-14.7672</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.16</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3524</v>
+        <v>0.2992</v>
       </c>
       <c r="J147" t="n">
-        <v>14.8008</v>
+        <v>12.5664</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.1</v>
       </c>
       <c r="I148" t="n">
-        <v>0.243</v>
+        <v>0.199</v>
       </c>
       <c r="J148" t="n">
-        <v>10.206</v>
+        <v>8.358000000000001</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.09</v>
       </c>
       <c r="I149" t="n">
-        <v>0.2237</v>
+        <v>0.1818</v>
       </c>
       <c r="J149" t="n">
-        <v>9.3954</v>
+        <v>7.6356</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1.02</v>
       </c>
       <c r="I150" t="n">
-        <v>0.06759999999999999</v>
+        <v>0.0496</v>
       </c>
       <c r="J150" t="n">
-        <v>2.8392</v>
+        <v>2.0832</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.1041</v>
+        <v>-0.0864</v>
       </c>
       <c r="J151" t="n">
-        <v>-4.3722</v>
+        <v>-3.6288</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.58</v>
       </c>
       <c r="I152" t="n">
-        <v>1.1872</v>
+        <v>1.2019</v>
       </c>
       <c r="J152" t="n">
-        <v>26.1184</v>
+        <v>26.4418</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.49</v>
       </c>
       <c r="I153" t="n">
-        <v>1.068</v>
+        <v>1.0778</v>
       </c>
       <c r="J153" t="n">
-        <v>23.496</v>
+        <v>23.7116</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.31</v>
       </c>
       <c r="I154" t="n">
-        <v>0.7562</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="J154" t="n">
-        <v>16.6364</v>
+        <v>16.1788</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.19</v>
       </c>
       <c r="I155" t="n">
-        <v>0.5067</v>
+        <v>0.4767</v>
       </c>
       <c r="J155" t="n">
-        <v>11.1474</v>
+        <v>10.4874</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>1.05</v>
       </c>
       <c r="I156" t="n">
-        <v>0.1488</v>
+        <v>0.1225</v>
       </c>
       <c r="J156" t="n">
-        <v>3.2736</v>
+        <v>2.695</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.13</v>
       </c>
       <c r="I157" t="n">
-        <v>0.3519</v>
+        <v>0.3018</v>
       </c>
       <c r="J157" t="n">
-        <v>7.7418</v>
+        <v>6.6396</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>0.87</v>
       </c>
       <c r="I158" t="n">
-        <v>-0.1679</v>
+        <v>-0.1507</v>
       </c>
       <c r="J158" t="n">
-        <v>-3.6938</v>
+        <v>-3.3154</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>0.85</v>
       </c>
       <c r="I159" t="n">
-        <v>-0.1886</v>
+        <v>-0.1706</v>
       </c>
       <c r="J159" t="n">
-        <v>-4.1492</v>
+        <v>-3.7532</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.76</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2762</v>
+        <v>-0.2578</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.0764</v>
+        <v>-5.6716</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.61</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.4138</v>
+        <v>-0.4037</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.1036</v>
+        <v>-8.881399999999999</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.65</v>
       </c>
       <c r="I162" t="n">
-        <v>1.2623</v>
+        <v>1.2808</v>
       </c>
       <c r="J162" t="n">
-        <v>29.0329</v>
+        <v>29.4584</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.48</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0426</v>
+        <v>1.0523</v>
       </c>
       <c r="J163" t="n">
-        <v>23.9798</v>
+        <v>24.2029</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.43</v>
       </c>
       <c r="I164" t="n">
-        <v>0.9664</v>
+        <v>0.9659</v>
       </c>
       <c r="J164" t="n">
-        <v>22.2272</v>
+        <v>22.2157</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.28</v>
       </c>
       <c r="I165" t="n">
-        <v>0.6854</v>
+        <v>0.6645</v>
       </c>
       <c r="J165" t="n">
-        <v>15.7642</v>
+        <v>15.2835</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.22</v>
       </c>
       <c r="I166" t="n">
-        <v>0.5596</v>
+        <v>0.5327</v>
       </c>
       <c r="J166" t="n">
-        <v>12.8708</v>
+        <v>12.2521</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.11</v>
       </c>
       <c r="I167" t="n">
-        <v>0.3566</v>
+        <v>0.317</v>
       </c>
       <c r="J167" t="n">
-        <v>8.2018</v>
+        <v>7.291</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.88</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1425</v>
+        <v>-0.127</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.2775</v>
+        <v>-2.921</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.66</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.3569</v>
+        <v>-0.3431</v>
       </c>
       <c r="J169" t="n">
-        <v>-8.2087</v>
+        <v>-7.8913</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.54</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4637</v>
+        <v>-0.458</v>
       </c>
       <c r="J170" t="n">
-        <v>-10.6651</v>
+        <v>-10.534</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.5</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4987</v>
+        <v>-0.4971</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.4701</v>
+        <v>-11.4333</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.32</v>
       </c>
       <c r="I172" t="n">
-        <v>0.8044</v>
+        <v>0.7788</v>
       </c>
       <c r="J172" t="n">
-        <v>24.132</v>
+        <v>23.364</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.23</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6167</v>
+        <v>0.5815</v>
       </c>
       <c r="J173" t="n">
-        <v>18.501</v>
+        <v>17.445</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.18</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5071</v>
+        <v>0.4699</v>
       </c>
       <c r="J174" t="n">
-        <v>15.213</v>
+        <v>14.097</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.15</v>
       </c>
       <c r="I175" t="n">
-        <v>0.4395</v>
+        <v>0.4024</v>
       </c>
       <c r="J175" t="n">
-        <v>13.185</v>
+        <v>12.072</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.87</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4488</v>
+        <v>-0.4071</v>
       </c>
       <c r="J176" t="n">
-        <v>-13.464</v>
+        <v>-12.213</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.33</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6881</v>
+        <v>0.639</v>
       </c>
       <c r="J177" t="n">
-        <v>20.643</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1</v>
       </c>
       <c r="I178" t="n">
-        <v>0.0197</v>
+        <v>0.0146</v>
       </c>
       <c r="J178" t="n">
-        <v>0.591</v>
+        <v>0.438</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.82</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.221</v>
+        <v>-0.2016</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.63</v>
+        <v>-6.048</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.66</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3725</v>
+        <v>-0.3589</v>
       </c>
       <c r="J180" t="n">
-        <v>-11.175</v>
+        <v>-10.767</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.58</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4438</v>
+        <v>-0.437</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.314</v>
+        <v>-13.11</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.19</v>
       </c>
       <c r="I182" t="n">
-        <v>0.541</v>
+        <v>0.5014</v>
       </c>
       <c r="J182" t="n">
-        <v>18.935</v>
+        <v>17.549</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.18</v>
       </c>
       <c r="I183" t="n">
-        <v>0.5181</v>
+        <v>0.4782</v>
       </c>
       <c r="J183" t="n">
-        <v>18.1335</v>
+        <v>16.737</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.16</v>
       </c>
       <c r="I184" t="n">
-        <v>0.4718</v>
+        <v>0.4314</v>
       </c>
       <c r="J184" t="n">
-        <v>16.513</v>
+        <v>15.099</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.99</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.0732</v>
+        <v>-0.0533</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.562</v>
+        <v>-1.8655</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.92</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3048</v>
+        <v>-0.2635</v>
       </c>
       <c r="J186" t="n">
-        <v>-10.668</v>
+        <v>-9.2225</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.24</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5207000000000001</v>
+        <v>0.4634</v>
       </c>
       <c r="J187" t="n">
-        <v>18.2245</v>
+        <v>16.219</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1</v>
       </c>
       <c r="I188" t="n">
-        <v>0.0091</v>
+        <v>0.0057</v>
       </c>
       <c r="J188" t="n">
-        <v>0.3185</v>
+        <v>0.1995</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.85</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.1951</v>
+        <v>-0.1751</v>
       </c>
       <c r="J189" t="n">
-        <v>-6.8285</v>
+        <v>-6.1285</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.8</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2459</v>
+        <v>-0.2259</v>
       </c>
       <c r="J190" t="n">
-        <v>-8.6065</v>
+        <v>-7.9065</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.76</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2848</v>
+        <v>-0.266</v>
       </c>
       <c r="J191" t="n">
-        <v>-9.968</v>
+        <v>-9.31</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.92</v>
       </c>
       <c r="I192" t="n">
-        <v>1.5787</v>
+        <v>1.616</v>
       </c>
       <c r="J192" t="n">
-        <v>29.9953</v>
+        <v>30.704</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.53</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1021</v>
+        <v>1.1191</v>
       </c>
       <c r="J193" t="n">
-        <v>20.9399</v>
+        <v>21.2629</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.49</v>
       </c>
       <c r="I194" t="n">
-        <v>1.0504</v>
+        <v>1.0638</v>
       </c>
       <c r="J194" t="n">
-        <v>19.9576</v>
+        <v>20.2122</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.45</v>
       </c>
       <c r="I195" t="n">
-        <v>0.9933</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="J195" t="n">
-        <v>18.8727</v>
+        <v>18.9905</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.01</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.0177</v>
+        <v>-0.0324</v>
       </c>
       <c r="J196" t="n">
-        <v>-0.3363</v>
+        <v>-0.6156</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>0.7</v>
       </c>
       <c r="I197" t="n">
-        <v>-0.2884</v>
+        <v>-0.276</v>
       </c>
       <c r="J197" t="n">
-        <v>-5.4796</v>
+        <v>-5.244</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2986</v>
+        <v>-0.287</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.6734</v>
+        <v>-5.453</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.57</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.4126</v>
+        <v>-0.4078</v>
       </c>
       <c r="J199" t="n">
-        <v>-7.8394</v>
+        <v>-7.7482</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.45</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.5149</v>
+        <v>-0.5151</v>
       </c>
       <c r="J200" t="n">
-        <v>-9.783099999999999</v>
+        <v>-9.786899999999999</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.3</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.6489</v>
+        <v>-0.6679</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.3291</v>
+        <v>-12.6901</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.07</v>
       </c>
       <c r="I202" t="n">
-        <v>0.2051</v>
+        <v>0.163</v>
       </c>
       <c r="J202" t="n">
-        <v>5.3326</v>
+        <v>4.238</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.02</v>
       </c>
       <c r="I203" t="n">
-        <v>0.0842</v>
+        <v>0.0601</v>
       </c>
       <c r="J203" t="n">
-        <v>2.1892</v>
+        <v>1.5626</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0091</v>
+        <v>0.0057</v>
       </c>
       <c r="J204" t="n">
-        <v>0.2366</v>
+        <v>0.1482</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.95</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0818</v>
+        <v>-0.0679</v>
       </c>
       <c r="J205" t="n">
-        <v>-2.1268</v>
+        <v>-1.7654</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.61</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4224</v>
+        <v>-0.4137</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.9824</v>
+        <v>-10.7562</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.4</v>
       </c>
       <c r="I207" t="n">
-        <v>0.969</v>
+        <v>0.9603</v>
       </c>
       <c r="J207" t="n">
-        <v>25.194</v>
+        <v>24.9678</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.32</v>
       </c>
       <c r="I208" t="n">
-        <v>0.8116</v>
+        <v>0.7861</v>
       </c>
       <c r="J208" t="n">
-        <v>21.1016</v>
+        <v>20.4386</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.22</v>
       </c>
       <c r="I209" t="n">
-        <v>0.6005</v>
+        <v>0.5637</v>
       </c>
       <c r="J209" t="n">
-        <v>15.613</v>
+        <v>14.6562</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.88</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.4182</v>
+        <v>-0.3757</v>
       </c>
       <c r="J210" t="n">
-        <v>-10.8732</v>
+        <v>-9.7682</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.79</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6345</v>
+        <v>-0.5994</v>
       </c>
       <c r="J211" t="n">
-        <v>-16.497</v>
+        <v>-15.5844</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.24</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3523</v>
+        <v>0.293</v>
       </c>
       <c r="J212" t="n">
-        <v>10.569</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.23</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3405</v>
+        <v>0.2822</v>
       </c>
       <c r="J213" t="n">
-        <v>10.215</v>
+        <v>8.465999999999999</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.14</v>
       </c>
       <c r="I214" t="n">
-        <v>0.2294</v>
+        <v>0.1835</v>
       </c>
       <c r="J214" t="n">
-        <v>6.882</v>
+        <v>5.505</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.08</v>
       </c>
       <c r="I215" t="n">
-        <v>0.147</v>
+        <v>0.1133</v>
       </c>
       <c r="J215" t="n">
-        <v>4.41</v>
+        <v>3.399</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.96</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.0828</v>
+        <v>-0.067</v>
       </c>
       <c r="J216" t="n">
-        <v>-2.484</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.27</v>
       </c>
       <c r="I217" t="n">
-        <v>0.4485</v>
+        <v>0.4538</v>
       </c>
       <c r="J217" t="n">
-        <v>13.455</v>
+        <v>13.614</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.09420000000000001</v>
+        <v>-0.0793</v>
       </c>
       <c r="J218" t="n">
-        <v>-2.826</v>
+        <v>-2.379</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.88</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.1627</v>
+        <v>-0.1436</v>
       </c>
       <c r="J219" t="n">
-        <v>-4.881</v>
+        <v>-4.308</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2353</v>
+        <v>-0.2153</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.059</v>
+        <v>-6.459</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.72</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.322</v>
+        <v>-0.3051</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.66</v>
+        <v>-9.153</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.15</v>
       </c>
       <c r="I222" t="n">
-        <v>0.3577</v>
+        <v>0.3036</v>
       </c>
       <c r="J222" t="n">
-        <v>15.0234</v>
+        <v>12.7512</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.11</v>
       </c>
       <c r="I223" t="n">
-        <v>0.2823</v>
+        <v>0.2329</v>
       </c>
       <c r="J223" t="n">
-        <v>11.8566</v>
+        <v>9.7818</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.05</v>
       </c>
       <c r="I224" t="n">
-        <v>0.1563</v>
+        <v>0.1203</v>
       </c>
       <c r="J224" t="n">
-        <v>6.5646</v>
+        <v>5.0526</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.84</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2073</v>
+        <v>-0.187</v>
       </c>
       <c r="J225" t="n">
-        <v>-8.7066</v>
+        <v>-7.854</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.6</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.433</v>
+        <v>-0.4257</v>
       </c>
       <c r="J226" t="n">
-        <v>-18.186</v>
+        <v>-17.8794</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.63</v>
       </c>
       <c r="I227" t="n">
-        <v>1.2973</v>
+        <v>1.3195</v>
       </c>
       <c r="J227" t="n">
-        <v>54.4866</v>
+        <v>55.419</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.18</v>
       </c>
       <c r="I228" t="n">
-        <v>0.5092</v>
+        <v>0.4713</v>
       </c>
       <c r="J228" t="n">
-        <v>21.3864</v>
+        <v>19.7946</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.08</v>
       </c>
       <c r="I229" t="n">
-        <v>0.2671</v>
+        <v>0.2342</v>
       </c>
       <c r="J229" t="n">
-        <v>11.2182</v>
+        <v>9.836399999999999</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.96</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1938</v>
+        <v>-0.1591</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.1396</v>
+        <v>-6.6822</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.83</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.544</v>
+        <v>-0.5046</v>
       </c>
       <c r="J231" t="n">
-        <v>-22.848</v>
+        <v>-21.1932</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.21</v>
       </c>
       <c r="I232" t="n">
-        <v>0.3619</v>
+        <v>0.3555</v>
       </c>
       <c r="J232" t="n">
-        <v>10.1332</v>
+        <v>9.954000000000001</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.14</v>
       </c>
       <c r="I233" t="n">
-        <v>0.2646</v>
+        <v>0.2503</v>
       </c>
       <c r="J233" t="n">
-        <v>7.4088</v>
+        <v>7.0084</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1.08</v>
       </c>
       <c r="I234" t="n">
-        <v>0.1728</v>
+        <v>0.1555</v>
       </c>
       <c r="J234" t="n">
-        <v>4.8384</v>
+        <v>4.354</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.0958</v>
+        <v>-0.08</v>
       </c>
       <c r="J235" t="n">
-        <v>-2.6824</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.41</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.5949</v>
+        <v>-0.6106</v>
       </c>
       <c r="J236" t="n">
-        <v>-16.6572</v>
+        <v>-17.0968</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.57</v>
       </c>
       <c r="I237" t="n">
-        <v>0.7159</v>
+        <v>0.6459</v>
       </c>
       <c r="J237" t="n">
-        <v>20.0452</v>
+        <v>18.0852</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.16</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2576</v>
+        <v>0.2074</v>
       </c>
       <c r="J238" t="n">
-        <v>7.2128</v>
+        <v>5.8072</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>1.13</v>
       </c>
       <c r="I239" t="n">
-        <v>0.2185</v>
+        <v>0.1733</v>
       </c>
       <c r="J239" t="n">
-        <v>6.118</v>
+        <v>4.8524</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.92</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.132</v>
+        <v>-0.1128</v>
       </c>
       <c r="J240" t="n">
-        <v>-3.696</v>
+        <v>-3.1584</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.72</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.3375</v>
+        <v>-0.3229</v>
       </c>
       <c r="J241" t="n">
-        <v>-9.449999999999999</v>
+        <v>-9.0412</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.75</v>
       </c>
       <c r="I242" t="n">
-        <v>1.4372</v>
+        <v>1.4678</v>
       </c>
       <c r="J242" t="n">
-        <v>38.8044</v>
+        <v>39.6306</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.4</v>
       </c>
       <c r="I243" t="n">
-        <v>0.9498</v>
+        <v>0.9385</v>
       </c>
       <c r="J243" t="n">
-        <v>25.6446</v>
+        <v>25.3395</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.02</v>
       </c>
       <c r="I244" t="n">
-        <v>0.0683</v>
+        <v>0.0522</v>
       </c>
       <c r="J244" t="n">
-        <v>1.8441</v>
+        <v>1.4094</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>0.95</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.2366</v>
+        <v>-0.1999</v>
       </c>
       <c r="J245" t="n">
-        <v>-6.3882</v>
+        <v>-5.3973</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.86</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.482</v>
+        <v>-0.4419</v>
       </c>
       <c r="J246" t="n">
-        <v>-13.014</v>
+        <v>-11.9313</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>1.19</v>
       </c>
       <c r="I247" t="n">
-        <v>0.4558</v>
+        <v>0.402</v>
       </c>
       <c r="J247" t="n">
-        <v>12.3066</v>
+        <v>10.854</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.0888</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="J248" t="n">
-        <v>-2.3976</v>
+        <v>-2.0358</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.75</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.2879</v>
+        <v>-0.2696</v>
       </c>
       <c r="J249" t="n">
-        <v>-7.7733</v>
+        <v>-7.2792</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.74</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.2974</v>
+        <v>-0.2794</v>
       </c>
       <c r="J250" t="n">
-        <v>-8.0298</v>
+        <v>-7.5438</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.71</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3254</v>
+        <v>-0.3087</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.7858</v>
+        <v>-8.334899999999999</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.74</v>
       </c>
       <c r="I252" t="n">
-        <v>1.4099</v>
+        <v>1.4368</v>
       </c>
       <c r="J252" t="n">
-        <v>35.2475</v>
+        <v>35.92</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.48</v>
       </c>
       <c r="I253" t="n">
-        <v>1.0669</v>
+        <v>1.0752</v>
       </c>
       <c r="J253" t="n">
-        <v>26.6725</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>1.21</v>
       </c>
       <c r="I254" t="n">
-        <v>0.5616</v>
+        <v>0.5302</v>
       </c>
       <c r="J254" t="n">
-        <v>14.04</v>
+        <v>13.255</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2761</v>
+        <v>-0.2387</v>
       </c>
       <c r="J255" t="n">
-        <v>-6.9025</v>
+        <v>-5.9675</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.87</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.4658</v>
+        <v>-0.4267</v>
       </c>
       <c r="J256" t="n">
-        <v>-11.645</v>
+        <v>-10.6675</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.37</v>
       </c>
       <c r="I257" t="n">
-        <v>0.7449</v>
+        <v>0.6977</v>
       </c>
       <c r="J257" t="n">
-        <v>18.6225</v>
+        <v>17.4425</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I258" t="n">
-        <v>-0.0917</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="J258" t="n">
-        <v>-2.2925</v>
+        <v>-1.9425</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.85</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.192</v>
+        <v>-0.1726</v>
       </c>
       <c r="J259" t="n">
-        <v>-4.8</v>
+        <v>-4.315</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.74</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.3002</v>
+        <v>-0.2822</v>
       </c>
       <c r="J260" t="n">
-        <v>-7.505</v>
+        <v>-7.055</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.57</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4541</v>
+        <v>-0.4486</v>
       </c>
       <c r="J261" t="n">
-        <v>-11.3525</v>
+        <v>-11.215</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.49</v>
       </c>
       <c r="I262" t="n">
-        <v>1.09</v>
+        <v>1.1004</v>
       </c>
       <c r="J262" t="n">
-        <v>26.16</v>
+        <v>26.4096</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.48</v>
       </c>
       <c r="I263" t="n">
-        <v>1.0761</v>
+        <v>1.0851</v>
       </c>
       <c r="J263" t="n">
-        <v>25.8264</v>
+        <v>26.0424</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.16</v>
       </c>
       <c r="I264" t="n">
-        <v>0.4565</v>
+        <v>0.422</v>
       </c>
       <c r="J264" t="n">
-        <v>10.956</v>
+        <v>10.128</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1</v>
       </c>
       <c r="I265" t="n">
-        <v>-0.0339</v>
+        <v>-0.0283</v>
       </c>
       <c r="J265" t="n">
-        <v>-0.8136</v>
+        <v>-0.6792</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.88</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.4327</v>
+        <v>-0.3919</v>
       </c>
       <c r="J266" t="n">
-        <v>-10.3848</v>
+        <v>-9.4056</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>1.28</v>
       </c>
       <c r="I267" t="n">
-        <v>0.5797</v>
+        <v>0.5221</v>
       </c>
       <c r="J267" t="n">
-        <v>13.9128</v>
+        <v>12.5304</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>1.14</v>
       </c>
       <c r="I268" t="n">
-        <v>0.3388</v>
+        <v>0.2856</v>
       </c>
       <c r="J268" t="n">
-        <v>8.1312</v>
+        <v>6.8544</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.79</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2578</v>
+        <v>-0.2381</v>
       </c>
       <c r="J269" t="n">
-        <v>-6.1872</v>
+        <v>-5.7144</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.78</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.2676</v>
+        <v>-0.2482</v>
       </c>
       <c r="J270" t="n">
-        <v>-6.4224</v>
+        <v>-5.9568</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.77</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.2773</v>
+        <v>-0.2582</v>
       </c>
       <c r="J271" t="n">
-        <v>-6.6552</v>
+        <v>-6.1968</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>1.42</v>
       </c>
       <c r="I272" t="n">
-        <v>1.0235</v>
+        <v>1.0262</v>
       </c>
       <c r="J272" t="n">
-        <v>29.6815</v>
+        <v>29.7598</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>1.15</v>
       </c>
       <c r="I273" t="n">
-        <v>0.4547</v>
+        <v>0.4131</v>
       </c>
       <c r="J273" t="n">
-        <v>13.1863</v>
+        <v>11.9799</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>1.03</v>
       </c>
       <c r="I274" t="n">
-        <v>0.1285</v>
+        <v>0.104</v>
       </c>
       <c r="J274" t="n">
-        <v>3.7265</v>
+        <v>3.016</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>1.01</v>
       </c>
       <c r="I275" t="n">
-        <v>0.0515</v>
+        <v>0.0387</v>
       </c>
       <c r="J275" t="n">
-        <v>1.4935</v>
+        <v>1.1223</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.67</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-0.8677</v>
       </c>
       <c r="J276" t="n">
-        <v>-25.6244</v>
+        <v>-25.1633</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.48</v>
       </c>
       <c r="I277" t="n">
-        <v>0.8638</v>
+        <v>0.8157</v>
       </c>
       <c r="J277" t="n">
-        <v>25.0502</v>
+        <v>23.6553</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.03</v>
       </c>
       <c r="I278" t="n">
-        <v>0.0982</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="J278" t="n">
-        <v>2.8478</v>
+        <v>2.1141</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>0.92</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.125</v>
+        <v>-0.1062</v>
       </c>
       <c r="J279" t="n">
-        <v>-3.625</v>
+        <v>-3.0798</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>0.85</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2029</v>
+        <v>-0.1822</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.8841</v>
+        <v>-5.2838</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>0.8</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.2539</v>
+        <v>-0.2341</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.3631</v>
+        <v>-6.7889</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>1.07</v>
       </c>
       <c r="I282" t="n">
-        <v>0.2282</v>
+        <v>0.1861</v>
       </c>
       <c r="J282" t="n">
-        <v>6.846</v>
+        <v>5.583</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.97</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.044</v>
+        <v>-0.0347</v>
       </c>
       <c r="J283" t="n">
-        <v>-1.32</v>
+        <v>-1.041</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.85</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.1886</v>
+        <v>-0.1706</v>
       </c>
       <c r="J284" t="n">
-        <v>-5.658</v>
+        <v>-5.118</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.3416</v>
+        <v>-0.3258</v>
       </c>
       <c r="J285" t="n">
-        <v>-10.248</v>
+        <v>-9.773999999999999</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.64</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.387</v>
+        <v>-0.3745</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.61</v>
+        <v>-11.235</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.66</v>
       </c>
       <c r="I287" t="n">
-        <v>1.3064</v>
+        <v>1.3264</v>
       </c>
       <c r="J287" t="n">
-        <v>39.192</v>
+        <v>39.792</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.44</v>
       </c>
       <c r="I288" t="n">
-        <v>1.0067</v>
+        <v>1.0058</v>
       </c>
       <c r="J288" t="n">
-        <v>30.201</v>
+        <v>30.174</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.38</v>
       </c>
       <c r="I289" t="n">
-        <v>0.9006</v>
+        <v>0.8852</v>
       </c>
       <c r="J289" t="n">
-        <v>27.018</v>
+        <v>26.556</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.08</v>
       </c>
       <c r="I290" t="n">
-        <v>0.2483</v>
+        <v>0.218</v>
       </c>
       <c r="J290" t="n">
-        <v>7.449</v>
+        <v>6.54</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.8734</v>
+        <v>-0.862</v>
       </c>
       <c r="J291" t="n">
-        <v>-26.202</v>
+        <v>-25.86</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>0.93</v>
       </c>
       <c r="I292" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.0798</v>
       </c>
       <c r="J292" t="n">
-        <v>-2.2392</v>
+        <v>-1.9152</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>0.92</v>
       </c>
       <c r="I293" t="n">
-        <v>-0.1059</v>
+        <v>-0.0917</v>
       </c>
       <c r="J293" t="n">
-        <v>-2.5416</v>
+        <v>-2.2008</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>0.84</v>
       </c>
       <c r="I294" t="n">
-        <v>-0.1954</v>
+        <v>-0.1785</v>
       </c>
       <c r="J294" t="n">
-        <v>-4.6896</v>
+        <v>-4.284</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.72</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.3095</v>
+        <v>-0.2927</v>
       </c>
       <c r="J295" t="n">
-        <v>-7.428</v>
+        <v>-7.0248</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.61</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.4095</v>
+        <v>-0.3987</v>
       </c>
       <c r="J296" t="n">
-        <v>-9.827999999999999</v>
+        <v>-9.5688</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.59</v>
       </c>
       <c r="I297" t="n">
-        <v>1.2178</v>
+        <v>1.2334</v>
       </c>
       <c r="J297" t="n">
-        <v>29.2272</v>
+        <v>29.6016</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.51</v>
       </c>
       <c r="I298" t="n">
-        <v>1.1104</v>
+        <v>1.1222</v>
       </c>
       <c r="J298" t="n">
-        <v>26.6496</v>
+        <v>26.9328</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.23</v>
       </c>
       <c r="I299" t="n">
-        <v>0.6051</v>
+        <v>0.574</v>
       </c>
       <c r="J299" t="n">
-        <v>14.5224</v>
+        <v>13.776</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>1.21</v>
       </c>
       <c r="I300" t="n">
-        <v>0.5631</v>
+        <v>0.5311</v>
       </c>
       <c r="J300" t="n">
-        <v>13.5144</v>
+        <v>12.7464</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.64</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.9745</v>
+        <v>-0.9744</v>
       </c>
       <c r="J301" t="n">
-        <v>-23.388</v>
+        <v>-23.3856</v>
       </c>
     </row>
   </sheetData>
